--- a/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
+++ b/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px20umf\Documents\github\PlotThoseLines\docs\jdt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4867856C-56A7-4626-95B6-414629032E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1F4682-41C6-400C-BEB4-93B12D8EF734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3885" yWindow="1830" windowWidth="21600" windowHeight="13305" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="1380" yWindow="2865" windowWidth="21600" windowHeight="11745" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Journal de travail'!$A$6:$G$6</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="64">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -209,6 +210,30 @@
   </si>
   <si>
     <t>Recherche de fichiers avec les données</t>
+  </si>
+  <si>
+    <t>Information sur les jdt par le chef de travail</t>
+  </si>
+  <si>
+    <t>Implémentation de l'import d'un fichier avec des données</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J'ai implémenté l'import des données d'un fichier .csv, qui parse des colonnes chosis, et créer une DataSerie </t>
+  </si>
+  <si>
+    <t>Recherche d'un source de données gratuit et complet</t>
+  </si>
+  <si>
+    <t>J'ai fini par faire un script avec l'ia qui scrappe les données de yahoo finance, et crée un csv avec un nombre suffisant de données</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correction de champ utilisé </t>
+  </si>
+  <si>
+    <t>Par erreur comme le champ voulu j'ai mis la valeur d'une action et pas la capitalisation totale, que j'ai ensuite corrigé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentation jdt et màj sur github project </t>
   </si>
 </sst>
 </file>
@@ -1216,16 +1241,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>150</c:v>
+                  <c:v>195</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>310</c:v>
+                  <c:v>430</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>70</c:v>
+                  <c:v>85</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -2071,16 +2096,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.28301886792452829</c:v>
+                  <c:v>0.27464788732394368</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.58490566037735847</c:v>
+                  <c:v>0.60563380281690138</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.13207547169811321</c:v>
+                  <c:v>0.11971830985915492</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4315,7 +4340,7 @@
       <c r="B3" s="86"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>8 heures 50 minutes</v>
+        <v>11 heures 50 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4330,15 +4355,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>410</v>
+        <v>530</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>530</v>
+        <v>710</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4567,7 +4592,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="62">
         <f>IF(ISBLANK(B14),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B14))</f>
         <v>36</v>
@@ -4644,7 +4669,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" s="63">
         <f>IF(ISBLANK(B17),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B17))</f>
         <v>36</v>
@@ -4757,7 +4782,7 @@
       </c>
       <c r="G21" s="40"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A22" s="62">
         <f>IF(ISBLANK(B22),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B22))</f>
         <v>37</v>
@@ -4880,75 +4905,131 @@
       <c r="G27" s="40"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="62" t="str">
+      <c r="A28" s="62">
         <f>IF(ISBLANK(B28),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B28))</f>
-        <v/>
-      </c>
-      <c r="B28" s="30"/>
+        <v>38</v>
+      </c>
+      <c r="B28" s="30">
+        <v>46279</v>
+      </c>
       <c r="C28" s="31"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="22"/>
+      <c r="D28" s="32">
+        <v>10</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>56</v>
+      </c>
       <c r="G28" s="39"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="63" t="str">
+      <c r="A29" s="63">
         <f>IF(ISBLANK(B29),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B29))</f>
-        <v/>
-      </c>
-      <c r="B29" s="34"/>
+        <v>38</v>
+      </c>
+      <c r="B29" s="34">
+        <v>46279</v>
+      </c>
       <c r="C29" s="35"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="22"/>
+      <c r="D29" s="36">
+        <v>5</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>41</v>
+      </c>
       <c r="G29" s="40"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="62" t="str">
+    <row r="30" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="62">
         <f>IF(ISBLANK(B30),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B30))</f>
-        <v/>
-      </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="39"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="63" t="str">
+        <v>38</v>
+      </c>
+      <c r="B30" s="30">
+        <v>46279</v>
+      </c>
+      <c r="C30" s="31">
+        <v>1</v>
+      </c>
+      <c r="D30" s="32">
+        <v>50</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="G30" s="39" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="63">
         <f>IF(ISBLANK(B31),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B31))</f>
-        <v/>
-      </c>
-      <c r="B31" s="34"/>
+        <v>38</v>
+      </c>
+      <c r="B31" s="34">
+        <v>46279</v>
+      </c>
       <c r="C31" s="35"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="40"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="62" t="str">
+      <c r="D31" s="36">
+        <v>30</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31" s="40" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="62">
         <f>IF(ISBLANK(B32),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B32))</f>
-        <v/>
-      </c>
-      <c r="B32" s="30"/>
+        <v>38</v>
+      </c>
+      <c r="B32" s="30">
+        <v>46279</v>
+      </c>
       <c r="C32" s="31"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="39"/>
+      <c r="D32" s="32">
+        <v>10</v>
+      </c>
+      <c r="E32" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="G32" s="39" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="63" t="str">
+      <c r="A33" s="63">
         <f>IF(ISBLANK(B33),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B33))</f>
-        <v/>
-      </c>
-      <c r="B33" s="34"/>
+        <v>38</v>
+      </c>
+      <c r="B33" s="34">
+        <v>46279</v>
+      </c>
       <c r="C33" s="35"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="22"/>
+      <c r="D33" s="36">
+        <v>15</v>
+      </c>
+      <c r="E33" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>63</v>
+      </c>
       <c r="G33" s="40"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -11077,11 +11158,11 @@
       </c>
       <c r="B6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$D$7:$D$532)</f>
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C10" si="0">SUM(A6:B6)</f>
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="E6" s="70" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11089,11 +11170,11 @@
       </c>
       <c r="F6" s="71" t="str">
         <f>QUOTIENT(SUM(A6:B6),60)&amp;" h "&amp;TEXT(MOD(SUM(A6:B6),60), "00")&amp;" min"</f>
-        <v>2 h 30 min</v>
+        <v>3 h 15 min</v>
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.28301886792452829</v>
+        <v>0.27464788732394368</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11110,15 +11191,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>310</v>
+        <v>430</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11126,11 +11207,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>5 h 10 min</v>
+        <v>7 h 10 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.58490566037735847</v>
+        <v>0.60563380281690138</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11188,11 +11269,11 @@
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E9" s="77" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11200,11 +11281,11 @@
       </c>
       <c r="F9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>1 h 10 min</v>
+        <v>1 h 25 min</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>0.13207547169811321</v>
+        <v>0.11971830985915492</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11256,26 +11337,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>410</v>
+        <v>530</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>530</v>
+        <v>710</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>29</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>8 h 50 min</v>
+        <v>11 h 50 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>9.8148148148148151E-2</v>
+        <v>0.13148148148148148</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>29</v>

--- a/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
+++ b/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px20umf\Documents\github\PlotThoseLines\docs\jdt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1F4682-41C6-400C-BEB4-93B12D8EF734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A08822-01BB-4CF1-A377-F52ADE7891B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="2865" windowWidth="21600" windowHeight="11745" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="31590" yWindow="1740" windowWidth="21600" windowHeight="11745" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Journal de travail'!$A$6:$G$6</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="77">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -234,6 +233,45 @@
   </si>
   <si>
     <t xml:space="preserve">Documentation jdt et màj sur github project </t>
+  </si>
+  <si>
+    <t>Explication de quelques nuances du projet par le chef de projet</t>
+  </si>
+  <si>
+    <t>Je constate qu'il reste plus beaucoup de temps pour le projet, il faudra avancer plus, et eventuellement abandonner certains aspects du projet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mise en place de menu latéral permetant de masquer ou d'afficher les graphiques ajoutés </t>
+  </si>
+  <si>
+    <t>Le tableau affiche le nom du graphique, et un checkbox à côté, avec lequel on peut choisir quels graphiques on veut voir à un moment précis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback de chef de projet par rapport à l'avancement du projet, et indeces pour le stockage des données </t>
+  </si>
+  <si>
+    <t>Il faudra prévoir une stratégie pour l'ajout des nouveau données (il faudrait mieux prendre en compte les nouvelles données, si elles se mettent sur le même moment au temps). Également il faudra penser à l'indiquation de ces changement à l'utilisateur (un message pop-up qui prouve la réussite et le nombre de changement au minimum, et idéalement une comparaison des deux graphiques)</t>
+  </si>
+  <si>
+    <t>Vérifier si le graphique avec le même nom existe déjà -&gt; si oui afficher une erreur</t>
+  </si>
+  <si>
+    <t>Réaliser la sauvegarde des données</t>
+  </si>
+  <si>
+    <t>Les données sont sauvegardées dans un fichier .json</t>
+  </si>
+  <si>
+    <t>Documentation jdt</t>
+  </si>
+  <si>
+    <t>Transmision de détails pour le projet par le chef de projet</t>
+  </si>
+  <si>
+    <t>le message transmit: pour obtenir une évaluation à 80% du projet, il faut faire une release cette semaine. Il faudra travailler le système de sauvegarde des données et gestion des données répetitives</t>
+  </si>
+  <si>
+    <t>Correction du dossier de sauvegarde</t>
   </si>
 </sst>
 </file>
@@ -1241,16 +1279,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>195</c:v>
+                  <c:v>230</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>430</c:v>
+                  <c:v>605</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>85</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -2096,16 +2134,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.27464788732394368</c:v>
+                  <c:v>0.24864864864864866</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.60563380281690138</c:v>
+                  <c:v>0.65405405405405403</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.11971830985915492</c:v>
+                  <c:v>9.7297297297297303E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4340,7 +4378,7 @@
       <c r="B3" s="86"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>11 heures 50 minutes</v>
+        <v>15 heures 25 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4355,15 +4393,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>530</v>
+        <v>625</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>710</v>
+        <v>925</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -5033,123 +5071,217 @@
       <c r="G33" s="40"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="62" t="str">
+      <c r="A34" s="62">
         <f>IF(ISBLANK(B34),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B34))</f>
-        <v/>
-      </c>
-      <c r="B34" s="30"/>
+        <v>40</v>
+      </c>
+      <c r="B34" s="30">
+        <v>46294</v>
+      </c>
       <c r="C34" s="31"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="22"/>
+      <c r="D34" s="32">
+        <v>5</v>
+      </c>
+      <c r="E34" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>64</v>
+      </c>
       <c r="G34" s="39"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="63" t="str">
+    <row r="35" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="63">
         <f>IF(ISBLANK(B35),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B35))</f>
-        <v/>
-      </c>
-      <c r="B35" s="34"/>
+        <v>40</v>
+      </c>
+      <c r="B35" s="34">
+        <v>46294</v>
+      </c>
       <c r="C35" s="35"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="40"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="62" t="str">
+      <c r="D35" s="36">
+        <v>10</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="G35" s="40" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="62">
         <f>IF(ISBLANK(B36),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B36))</f>
-        <v/>
-      </c>
-      <c r="B36" s="30"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="39"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="63" t="str">
+        <v>40</v>
+      </c>
+      <c r="B36" s="30">
+        <v>46294</v>
+      </c>
+      <c r="C36" s="31">
+        <v>1</v>
+      </c>
+      <c r="D36" s="32">
+        <v>15</v>
+      </c>
+      <c r="E36" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="G36" s="39" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="63">
         <f>IF(ISBLANK(B37),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B37))</f>
-        <v/>
-      </c>
-      <c r="B37" s="34"/>
+        <v>40</v>
+      </c>
+      <c r="B37" s="34">
+        <v>46294</v>
+      </c>
       <c r="C37" s="35"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="40"/>
+      <c r="D37" s="36">
+        <v>15</v>
+      </c>
+      <c r="E37" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="G37" s="40" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="62" t="str">
+      <c r="A38" s="62">
         <f>IF(ISBLANK(B38),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B38))</f>
-        <v/>
-      </c>
-      <c r="B38" s="30"/>
+        <v>40</v>
+      </c>
+      <c r="B38" s="30">
+        <v>46294</v>
+      </c>
       <c r="C38" s="31"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="22"/>
+      <c r="D38" s="32">
+        <v>10</v>
+      </c>
+      <c r="E38" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" s="22" t="s">
+        <v>70</v>
+      </c>
       <c r="G38" s="39"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="63" t="str">
+      <c r="A39" s="63">
         <f>IF(ISBLANK(B39),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B39))</f>
-        <v/>
-      </c>
-      <c r="B39" s="34"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="40"/>
+        <v>40</v>
+      </c>
+      <c r="B39" s="34">
+        <v>46294</v>
+      </c>
+      <c r="C39" s="35">
+        <v>1</v>
+      </c>
+      <c r="D39" s="36">
+        <v>5</v>
+      </c>
+      <c r="E39" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="G39" s="40" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="62" t="str">
+      <c r="A40" s="62">
         <f>IF(ISBLANK(B40),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B40))</f>
-        <v/>
-      </c>
-      <c r="B40" s="30"/>
+        <v>40</v>
+      </c>
+      <c r="B40" s="30">
+        <v>46294</v>
+      </c>
       <c r="C40" s="31"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="22"/>
+      <c r="D40" s="32">
+        <v>5</v>
+      </c>
+      <c r="E40" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="22" t="s">
+        <v>73</v>
+      </c>
       <c r="G40" s="39"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="63" t="str">
+    <row r="41" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A41" s="63">
         <f>IF(ISBLANK(B41),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B41))</f>
-        <v/>
-      </c>
-      <c r="B41" s="34"/>
+        <v>41</v>
+      </c>
+      <c r="B41" s="34">
+        <v>46300</v>
+      </c>
       <c r="C41" s="35"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="40"/>
+      <c r="D41" s="36">
+        <v>5</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="G41" s="40" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="62" t="str">
+      <c r="A42" s="62">
         <f>IF(ISBLANK(B42),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B42))</f>
-        <v/>
-      </c>
-      <c r="B42" s="30"/>
+        <v>41</v>
+      </c>
+      <c r="B42" s="30">
+        <v>46300</v>
+      </c>
       <c r="C42" s="31"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="22"/>
+      <c r="D42" s="32">
+        <v>10</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" s="22" t="s">
+        <v>41</v>
+      </c>
       <c r="G42" s="39"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="63" t="str">
+      <c r="A43" s="63">
         <f>IF(ISBLANK(B43),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B43))</f>
-        <v/>
-      </c>
-      <c r="B43" s="34"/>
+        <v>41</v>
+      </c>
+      <c r="B43" s="34">
+        <v>46300</v>
+      </c>
       <c r="C43" s="35"/>
-      <c r="D43" s="36"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="22"/>
+      <c r="D43" s="36">
+        <v>15</v>
+      </c>
+      <c r="E43" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" s="22" t="s">
+        <v>76</v>
+      </c>
       <c r="G43" s="40"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -11158,11 +11290,11 @@
       </c>
       <c r="B6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$D$7:$D$532)</f>
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C10" si="0">SUM(A6:B6)</f>
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="E6" s="70" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11170,11 +11302,11 @@
       </c>
       <c r="F6" s="71" t="str">
         <f>QUOTIENT(SUM(A6:B6),60)&amp;" h "&amp;TEXT(MOD(SUM(A6:B6),60), "00")&amp;" min"</f>
-        <v>3 h 15 min</v>
+        <v>3 h 50 min</v>
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.27464788732394368</v>
+        <v>0.24864864864864866</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11191,15 +11323,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>430</v>
+        <v>605</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11207,11 +11339,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>7 h 10 min</v>
+        <v>10 h 05 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.60563380281690138</v>
+        <v>0.65405405405405403</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11269,11 +11401,11 @@
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E9" s="77" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11281,11 +11413,11 @@
       </c>
       <c r="F9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>1 h 25 min</v>
+        <v>1 h 30 min</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>0.11971830985915492</v>
+        <v>9.7297297297297303E-2</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11337,26 +11469,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>530</v>
+        <v>625</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>710</v>
+        <v>925</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>29</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>11 h 50 min</v>
+        <v>15 h 25 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>0.13148148148148148</v>
+        <v>0.17129629629629631</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>29</v>

--- a/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
+++ b/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px20umf\Documents\github\PlotThoseLines\docs\jdt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A08822-01BB-4CF1-A377-F52ADE7891B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C817C52D-9788-4A47-B13E-A135D0CB8F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31590" yWindow="1740" windowWidth="21600" windowHeight="11745" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="80">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -272,6 +272,15 @@
   </si>
   <si>
     <t>Correction du dossier de sauvegarde</t>
+  </si>
+  <si>
+    <t>Je commence par l'ajout d'un fichier pour le même graphique, en enchaînant avec la logique de remplacement des anciens points si la nouvelle série contient  des points communs avec l'ancienne.</t>
+  </si>
+  <si>
+    <t>Attribution du nom de graphique par l'accronyme de l'entreprise, implémentation de logique d'ajout d'une autre serie</t>
+  </si>
+  <si>
+    <t>Partie complètement fonctionnelle, si l'ancien et le nouveau graphique ont des données en commun -&gt; celles de dernier sont prises en compte.</t>
   </si>
 </sst>
 </file>
@@ -1282,7 +1291,7 @@
                   <c:v>230</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>605</c:v>
+                  <c:v>675</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2134,16 +2143,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.24864864864864866</c:v>
+                  <c:v>0.23115577889447236</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.65405405405405403</c:v>
+                  <c:v>0.67839195979899503</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.7297297297297303E-2</c:v>
+                  <c:v>9.0452261306532666E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4378,7 +4387,7 @@
       <c r="B3" s="86"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>15 heures 25 minutes</v>
+        <v>16 heures 35 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4393,15 +4402,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>625</v>
+        <v>635</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>925</v>
+        <v>995</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -5244,7 +5253,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A42" s="62">
         <f>IF(ISBLANK(B42),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B42))</f>
         <v>41</v>
@@ -5262,7 +5271,9 @@
       <c r="F42" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="G42" s="39"/>
+      <c r="G42" s="39" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="63">
@@ -5284,17 +5295,29 @@
       </c>
       <c r="G43" s="40"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="62" t="str">
+    <row r="44" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="62">
         <f>IF(ISBLANK(B44),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B44))</f>
-        <v/>
-      </c>
-      <c r="B44" s="30"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="39"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="30">
+        <v>46300</v>
+      </c>
+      <c r="C44" s="31">
+        <v>1</v>
+      </c>
+      <c r="D44" s="32">
+        <v>10</v>
+      </c>
+      <c r="E44" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G44" s="39" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="63" t="str">
@@ -11153,7 +11176,7 @@
       <c r="G532" s="39"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="sC8RJl0M6+wONYXsnCTKmcqXUp1ITAlugv/3BW303r/E9HRpDNWm1EDZcYLBlB50SDN+6uVKCZ+hqkZ4Wju+ZA==" saltValue="fNiMxA6H49sg0PxMFstsLQ==" spinCount="100000" sheet="1" insertHyperlinks="0" selectLockedCells="1" sort="0" autoFilter="0"/>
+  <sheetProtection insertHyperlinks="0" selectLockedCells="1" sort="0" autoFilter="0"/>
   <mergeCells count="4">
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C5:D5"/>
@@ -11306,7 +11329,7 @@
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.24864864864864866</v>
+        <v>0.23115577889447236</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11323,15 +11346,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>605</v>
+        <v>675</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11339,11 +11362,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>10 h 05 min</v>
+        <v>11 h 15 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.65405405405405403</v>
+        <v>0.67839195979899503</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11417,7 +11440,7 @@
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>9.7297297297297303E-2</v>
+        <v>9.0452261306532666E-2</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11469,26 +11492,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>625</v>
+        <v>635</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>925</v>
+        <v>995</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>29</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>15 h 25 min</v>
+        <v>16 h 35 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>0.17129629629629631</v>
+        <v>0.18425925925925926</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>29</v>

--- a/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
+++ b/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px20umf\Documents\github\PlotThoseLines\docs\jdt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C817C52D-9788-4A47-B13E-A135D0CB8F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{399DCDD1-2760-42C0-971C-6654ED47BEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31590" yWindow="1740" windowWidth="21600" windowHeight="11745" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="84">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -281,6 +281,18 @@
   </si>
   <si>
     <t>Partie complètement fonctionnelle, si l'ancien et le nouveau graphique ont des données en commun -&gt; celles de dernier sont prises en compte.</t>
+  </si>
+  <si>
+    <t>Suppresion de série de l'affichage et de la mémoire</t>
+  </si>
+  <si>
+    <t>Boutons pout changer le zoom et exporter le graphique en png</t>
+  </si>
+  <si>
+    <t>Formatage des grands nombres</t>
+  </si>
+  <si>
+    <t>Nombres positifs et négatifs</t>
   </si>
 </sst>
 </file>
@@ -1291,7 +1303,7 @@
                   <c:v>230</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>675</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2143,16 +2155,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.23115577889447236</c:v>
+                  <c:v>0.21495327102803738</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.67839195979899503</c:v>
+                  <c:v>0.7009345794392523</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.0452261306532666E-2</c:v>
+                  <c:v>8.4112149532710276E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4387,7 +4399,7 @@
       <c r="B3" s="86"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>16 heures 35 minutes</v>
+        <v>17 heures 50 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4406,11 +4418,11 @@
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>635</v>
+        <v>710</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>995</v>
+        <v>1070</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -5085,7 +5097,7 @@
         <v>40</v>
       </c>
       <c r="B34" s="30">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C34" s="31"/>
       <c r="D34" s="32">
@@ -5104,8 +5116,8 @@
         <f>IF(ISBLANK(B35),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B35))</f>
         <v>40</v>
       </c>
-      <c r="B35" s="34">
-        <v>46294</v>
+      <c r="B35" s="30">
+        <v>46293</v>
       </c>
       <c r="C35" s="35"/>
       <c r="D35" s="36">
@@ -5127,7 +5139,7 @@
         <v>40</v>
       </c>
       <c r="B36" s="30">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C36" s="31">
         <v>1</v>
@@ -5151,7 +5163,7 @@
         <v>40</v>
       </c>
       <c r="B37" s="34">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C37" s="35"/>
       <c r="D37" s="36">
@@ -5173,7 +5185,7 @@
         <v>40</v>
       </c>
       <c r="B38" s="30">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C38" s="31"/>
       <c r="D38" s="32">
@@ -5193,7 +5205,7 @@
         <v>40</v>
       </c>
       <c r="B39" s="34">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C39" s="35">
         <v>1</v>
@@ -5217,7 +5229,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="30">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="C40" s="31"/>
       <c r="D40" s="32">
@@ -5320,40 +5332,66 @@
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="63" t="str">
+      <c r="A45" s="63">
         <f>IF(ISBLANK(B45),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B45))</f>
-        <v/>
-      </c>
-      <c r="B45" s="34"/>
+        <v>41</v>
+      </c>
+      <c r="B45" s="34">
+        <v>46300</v>
+      </c>
       <c r="C45" s="35"/>
-      <c r="D45" s="36"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="22"/>
+      <c r="D45" s="36">
+        <v>30</v>
+      </c>
+      <c r="E45" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F45" s="22" t="s">
+        <v>80</v>
+      </c>
       <c r="G45" s="40"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="62" t="str">
+      <c r="A46" s="62">
         <f>IF(ISBLANK(B46),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B46))</f>
-        <v/>
-      </c>
-      <c r="B46" s="30"/>
+        <v>41</v>
+      </c>
+      <c r="B46" s="30">
+        <v>46300</v>
+      </c>
       <c r="C46" s="31"/>
-      <c r="D46" s="32"/>
-      <c r="E46" s="33"/>
-      <c r="F46" s="22"/>
+      <c r="D46" s="32">
+        <v>25</v>
+      </c>
+      <c r="E46" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" s="22" t="s">
+        <v>81</v>
+      </c>
       <c r="G46" s="39"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="63" t="str">
+      <c r="A47" s="63">
         <f>IF(ISBLANK(B47),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B47))</f>
-        <v/>
-      </c>
-      <c r="B47" s="34"/>
+        <v>41</v>
+      </c>
+      <c r="B47" s="34">
+        <v>46300</v>
+      </c>
       <c r="C47" s="35"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="40"/>
+      <c r="D47" s="36">
+        <v>20</v>
+      </c>
+      <c r="E47" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" s="40" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="62" t="str">
@@ -11329,7 +11367,7 @@
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.23115577889447236</v>
+        <v>0.21495327102803738</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11350,11 +11388,11 @@
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>675</v>
+        <v>750</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11362,11 +11400,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>11 h 15 min</v>
+        <v>12 h 30 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.67839195979899503</v>
+        <v>0.7009345794392523</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11440,7 +11478,7 @@
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>9.0452261306532666E-2</v>
+        <v>8.4112149532710276E-2</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11496,22 +11534,22 @@
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>635</v>
+        <v>710</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>995</v>
+        <v>1070</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>29</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>16 h 35 min</v>
+        <v>17 h 50 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>0.18425925925925926</v>
+        <v>0.19814814814814816</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>29</v>

--- a/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
+++ b/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px20umf\Documents\github\PlotThoseLines\docs\jdt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{399DCDD1-2760-42C0-971C-6654ED47BEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C012618B-47CD-46C8-82C3-4648B7303650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -40,8 +40,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="85">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -293,6 +315,9 @@
   </si>
   <si>
     <t>Nombres positifs et négatifs</t>
+  </si>
+  <si>
+    <t>Mise à jour du jdt</t>
   </si>
 </sst>
 </file>
@@ -1309,7 +1334,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>90</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -2155,16 +2180,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.21495327102803738</c:v>
+                  <c:v>0.21296296296296297</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.7009345794392523</c:v>
+                  <c:v>0.69444444444444442</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.4112149532710276E-2</c:v>
+                  <c:v>9.2592592592592587E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4399,7 +4424,7 @@
       <c r="B3" s="86"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>17 heures 50 minutes</v>
+        <v>18 heures 0 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4418,11 +4443,11 @@
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4586,6 +4611,13 @@
         <v>34</v>
       </c>
       <c r="G11" s="40"/>
+      <c r="I11" t="str" cm="1">
+        <f t="array" ref="I11">_xlfn.LET(
+  _xlpm.tot, SUM((B$7:B$100=B7) * (IFERROR(SUBSTITUTE(C$7:C$100," h","")*60, 0) + IFERROR(SUBSTITUTE(D$7:D$100," min","")*1, 0))),
+  INT(_xlpm.tot/60) &amp; " h " &amp; TEXT(MOD(_xlpm.tot, 60), "00") &amp; " min"
+)</f>
+        <v>2 h 55 min</v>
+      </c>
       <c r="M11" t="s">
         <v>17</v>
       </c>
@@ -5394,15 +5426,23 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="62" t="str">
+      <c r="A48" s="62">
         <f>IF(ISBLANK(B48),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B48))</f>
-        <v/>
-      </c>
-      <c r="B48" s="30"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="30">
+        <v>46300</v>
+      </c>
       <c r="C48" s="31"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="33"/>
-      <c r="F48" s="22"/>
+      <c r="D48" s="32">
+        <v>10</v>
+      </c>
+      <c r="E48" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="22" t="s">
+        <v>84</v>
+      </c>
       <c r="G48" s="39"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -11367,7 +11407,7 @@
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.21495327102803738</v>
+        <v>0.21296296296296297</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11404,7 +11444,7 @@
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.7009345794392523</v>
+        <v>0.69444444444444442</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11462,11 +11502,11 @@
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E9" s="77" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11474,11 +11514,11 @@
       </c>
       <c r="F9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>1 h 30 min</v>
+        <v>1 h 40 min</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>8.4112149532710276E-2</v>
+        <v>9.2592592592592587E-2</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11534,22 +11574,22 @@
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>29</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>17 h 50 min</v>
+        <v>18 h 00 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>0.19814814814814816</v>
+        <v>0.2</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>29</v>

--- a/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
+++ b/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px20umf\Documents\github\PlotThoseLines\docs\jdt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C012618B-47CD-46C8-82C3-4648B7303650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC344A51-FA54-4887-97EA-4345F68E193F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="31590" yWindow="1740" windowWidth="21600" windowHeight="11745" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="86">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -318,6 +318,9 @@
   </si>
   <si>
     <t>Mise à jour du jdt</t>
+  </si>
+  <si>
+    <t>Analyse de l'avancement du projet, mise à jour des objectifs sur github project</t>
   </si>
 </sst>
 </file>
@@ -1325,7 +1328,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>230</c:v>
+                  <c:v>245</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>750</c:v>
@@ -2180,16 +2183,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.21296296296296297</c:v>
+                  <c:v>0.22374429223744291</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.69444444444444442</c:v>
+                  <c:v>0.68493150684931503</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.2592592592592587E-2</c:v>
+                  <c:v>9.1324200913242004E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4424,7 +4427,7 @@
       <c r="B3" s="86"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>18 heures 0 minutes</v>
+        <v>18 heures 15 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4443,11 +4446,11 @@
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -5446,15 +5449,23 @@
       <c r="G48" s="39"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="63" t="str">
+      <c r="A49" s="63">
         <f>IF(ISBLANK(B49),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B49))</f>
-        <v/>
-      </c>
-      <c r="B49" s="34"/>
+        <v>41</v>
+      </c>
+      <c r="B49" s="34">
+        <v>46302</v>
+      </c>
       <c r="C49" s="35"/>
-      <c r="D49" s="36"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="22"/>
+      <c r="D49" s="36">
+        <v>15</v>
+      </c>
+      <c r="E49" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" s="22" t="s">
+        <v>85</v>
+      </c>
       <c r="G49" s="40"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -11391,11 +11402,11 @@
       </c>
       <c r="B6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$D$7:$D$532)</f>
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C10" si="0">SUM(A6:B6)</f>
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="E6" s="70" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11403,11 +11414,11 @@
       </c>
       <c r="F6" s="71" t="str">
         <f>QUOTIENT(SUM(A6:B6),60)&amp;" h "&amp;TEXT(MOD(SUM(A6:B6),60), "00")&amp;" min"</f>
-        <v>3 h 50 min</v>
+        <v>4 h 05 min</v>
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.21296296296296297</v>
+        <v>0.22374429223744291</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11444,7 +11455,7 @@
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.69444444444444442</v>
+        <v>0.68493150684931503</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11518,7 +11529,7 @@
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>9.2592592592592587E-2</v>
+        <v>9.1324200913242004E-2</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11574,22 +11585,22 @@
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>29</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>18 h 00 min</v>
+        <v>18 h 15 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>0.2</v>
+        <v>0.20277777777777778</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>29</v>
@@ -11630,6 +11641,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B1120F001D1794FAA6F4057E3355991" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="62349bcdb43c26c508700efba1cb50b1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f20a0681-8b2f-4a46-9dab-cf1520193f81" xmlns:ns3="932fafb7-d8e0-4a14-bee3-33aad5c71309" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0e5d6db3f342a25e0e30f4a2965162e1" ns2:_="" ns3:_="">
     <xsd:import namespace="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
@@ -11818,17 +11840,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11839,6 +11850,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1424D28F-D6A9-45ED-AED5-A0D744400EE5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11857,23 +11885,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>

--- a/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
+++ b/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px20umf\Documents\github\PlotThoseLines\docs\jdt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC344A51-FA54-4887-97EA-4345F68E193F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3804CBBE-DD25-40DC-9499-2B51519A47AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31590" yWindow="1740" windowWidth="21600" windowHeight="11745" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -40,30 +40,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="95">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -321,6 +299,33 @@
   </si>
   <si>
     <t>Analyse de l'avancement du projet, mise à jour des objectifs sur github project</t>
+  </si>
+  <si>
+    <t>Temps par jour</t>
+  </si>
+  <si>
+    <t>pour 07.09</t>
+  </si>
+  <si>
+    <t>pour 14.09</t>
+  </si>
+  <si>
+    <t>pour 31.08</t>
+  </si>
+  <si>
+    <t>pour 24.08</t>
+  </si>
+  <si>
+    <t>pour 28.09</t>
+  </si>
+  <si>
+    <t>pour 05.10</t>
+  </si>
+  <si>
+    <t>pour 07.10</t>
+  </si>
+  <si>
+    <t>Date</t>
   </si>
 </sst>
 </file>
@@ -588,7 +593,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -786,11 +791,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
     <dxf>
       <font>
         <color theme="0"/>
@@ -874,6 +880,9 @@
           <bgColor theme="2" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -4171,18 +4180,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F2213DF1-F6B1-174C-AC17-4E96BE96C00D}" name="Table1" displayName="Table1" ref="A6:G532" totalsRowShown="0" headerRowDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A6:G532" xr:uid="{F2213DF1-F6B1-174C-AC17-4E96BE96C00D}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{315BA4B4-9BD9-AB4E-8D40-FABFA0BB2AEA}" name="Semaine" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F2213DF1-F6B1-174C-AC17-4E96BE96C00D}" name="Table1" displayName="Table1" ref="A6:I532" totalsRowShown="0" headerRowDxfId="18" tableBorderDxfId="17">
+  <autoFilter ref="A6:I532" xr:uid="{F2213DF1-F6B1-174C-AC17-4E96BE96C00D}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{315BA4B4-9BD9-AB4E-8D40-FABFA0BB2AEA}" name="Semaine" dataDxfId="16">
       <calculatedColumnFormula>IF(ISBLANK(B7),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B7))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{503C31E9-854D-BF42-85AC-8DFA1376C4D8}" name="Jour" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{B35A0B98-71A0-BA4F-BFAB-00A05EA1F23A}" name="h.      " dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{BE4D837D-FC99-BA48-A82F-B8C8E4CE5BF8}" name="min." dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{A2DCC539-6D2A-B04A-BF8E-6FACE6268D1F}" name="Type" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{4EA406B9-7EF7-D547-AF98-5AD11BE168E9}" name="Description" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{1735360B-2647-6D42-A0E3-3425EE302FFD}" name="Remarques/problèmes" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{503C31E9-854D-BF42-85AC-8DFA1376C4D8}" name="Jour" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{B35A0B98-71A0-BA4F-BFAB-00A05EA1F23A}" name="h.      " dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{BE4D837D-FC99-BA48-A82F-B8C8E4CE5BF8}" name="min." dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{A2DCC539-6D2A-B04A-BF8E-6FACE6268D1F}" name="Type" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{4EA406B9-7EF7-D547-AF98-5AD11BE168E9}" name="Description" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{1735360B-2647-6D42-A0E3-3425EE302FFD}" name="Remarques/problèmes" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{0805C5E8-0F37-48B2-808D-67420148D782}" name="Temps par jour" dataDxfId="9">
+      <calculatedColumnFormula>IF(OR(ISBLANK(B7),B7=""),"",IF(B7=B6,"",INT(((SUMIF(B:B,B7,C:C)*60)+SUMIF(B:B,B7,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B7,C:C)*60)+SUMIF(B:B,B7,D:D),60),"00")&amp;" min"))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{C8A7254A-B147-4422-AE74-504BCBFCC256}" name="Date"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4384,6 +4397,7 @@
     <col min="5" max="5" width="14.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="83.5" customWidth="1"/>
     <col min="7" max="7" width="72.125" customWidth="1"/>
+    <col min="8" max="8" width="18.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.125" bestFit="1" customWidth="1"/>
@@ -4483,6 +4497,12 @@
       <c r="G6" s="14" t="s">
         <v>13</v>
       </c>
+      <c r="H6" s="87" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="61">
@@ -4507,6 +4527,13 @@
       <c r="G7" s="38" t="s">
         <v>49</v>
       </c>
+      <c r="H7" t="str">
+        <f t="shared" ref="H7:H70" si="0">IF(OR(ISBLANK(B7),B7=""),"",IF(B7=B6,"",INT(((SUMIF(B:B,B7,C:C)*60)+SUMIF(B:B,B7,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B7,C:C)*60)+SUMIF(B:B,B7,D:D),60),"00")&amp;" min"))</f>
+        <v>2 h 55 min</v>
+      </c>
+      <c r="I7" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="62">
@@ -4527,6 +4554,10 @@
         <v>32</v>
       </c>
       <c r="G8" s="39"/>
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="M8" t="s">
         <v>14</v>
       </c>
@@ -4556,6 +4587,10 @@
         <v>33</v>
       </c>
       <c r="G9" s="40"/>
+      <c r="H9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="M9" t="s">
         <v>15</v>
       </c>
@@ -4585,6 +4620,10 @@
         <v>36</v>
       </c>
       <c r="G10" s="39"/>
+      <c r="H10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="M10" t="s">
         <v>16</v>
       </c>
@@ -4614,12 +4653,9 @@
         <v>34</v>
       </c>
       <c r="G11" s="40"/>
-      <c r="I11" t="str" cm="1">
-        <f t="array" ref="I11">_xlfn.LET(
-  _xlpm.tot, SUM((B$7:B$100=B7) * (IFERROR(SUBSTITUTE(C$7:C$100," h","")*60, 0) + IFERROR(SUBSTITUTE(D$7:D$100," min","")*1, 0))),
-  INT(_xlpm.tot/60) &amp; " h " &amp; TEXT(MOD(_xlpm.tot, 60), "00") &amp; " min"
-)</f>
-        <v>2 h 55 min</v>
+      <c r="H11" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="M11" t="s">
         <v>17</v>
@@ -4650,6 +4686,13 @@
         <v>50</v>
       </c>
       <c r="G12" s="39"/>
+      <c r="H12" t="str">
+        <f t="shared" si="0"/>
+        <v>3 h 00 min</v>
+      </c>
+      <c r="I12" t="s">
+        <v>89</v>
+      </c>
       <c r="M12" t="s">
         <v>18</v>
       </c>
@@ -4679,6 +4722,10 @@
         <v>41</v>
       </c>
       <c r="G13" s="40"/>
+      <c r="H13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="N13">
         <v>6</v>
       </c>
@@ -4705,6 +4752,10 @@
         <v>35</v>
       </c>
       <c r="G14" s="39"/>
+      <c r="H14" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="N14">
         <v>7</v>
       </c>
@@ -4731,6 +4782,10 @@
         <v>37</v>
       </c>
       <c r="G15" s="40"/>
+      <c r="H15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="N15">
         <v>8</v>
       </c>
@@ -4759,6 +4814,10 @@
       <c r="G16" s="39" t="s">
         <v>38</v>
       </c>
+      <c r="H16" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="O16">
         <v>40</v>
       </c>
@@ -4784,6 +4843,10 @@
       <c r="G17" s="40" t="s">
         <v>40</v>
       </c>
+      <c r="H17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="O17">
         <v>45</v>
       </c>
@@ -4807,6 +4870,13 @@
         <v>47</v>
       </c>
       <c r="G18" s="39"/>
+      <c r="H18" t="str">
+        <f t="shared" si="0"/>
+        <v>2 h 55 min</v>
+      </c>
+      <c r="I18" t="s">
+        <v>87</v>
+      </c>
       <c r="O18">
         <v>50</v>
       </c>
@@ -4832,6 +4902,10 @@
       <c r="G19" s="40" t="s">
         <v>42</v>
       </c>
+      <c r="H19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="O19">
         <v>55</v>
       </c>
@@ -4855,6 +4929,10 @@
         <v>43</v>
       </c>
       <c r="G20" s="39"/>
+      <c r="H20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="63">
@@ -4875,6 +4953,10 @@
         <v>44</v>
       </c>
       <c r="G21" s="40"/>
+      <c r="H21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
     <row r="22" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A22" s="62">
@@ -4897,6 +4979,10 @@
       <c r="G22" s="39" t="s">
         <v>46</v>
       </c>
+      <c r="H22" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="63">
@@ -4917,6 +5003,10 @@
         <v>51</v>
       </c>
       <c r="G23" s="40"/>
+      <c r="H23" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="62">
@@ -4937,6 +5027,10 @@
         <v>52</v>
       </c>
       <c r="G24" s="39"/>
+      <c r="H24" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="63">
@@ -4957,6 +5051,10 @@
         <v>53</v>
       </c>
       <c r="G25" s="40"/>
+      <c r="H25" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="62">
@@ -4977,6 +5075,10 @@
         <v>54</v>
       </c>
       <c r="G26" s="39"/>
+      <c r="H26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="63">
@@ -4997,6 +5099,10 @@
         <v>55</v>
       </c>
       <c r="G27" s="40"/>
+      <c r="H27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="62">
@@ -5017,6 +5123,13 @@
         <v>56</v>
       </c>
       <c r="G28" s="39"/>
+      <c r="H28" t="str">
+        <f t="shared" si="0"/>
+        <v>3 h 00 min</v>
+      </c>
+      <c r="I28" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="63">
@@ -5037,6 +5150,10 @@
         <v>41</v>
       </c>
       <c r="G29" s="40"/>
+      <c r="H29" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
     <row r="30" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A30" s="62">
@@ -5061,6 +5178,10 @@
       <c r="G30" s="39" t="s">
         <v>58</v>
       </c>
+      <c r="H30" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
     <row r="31" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A31" s="63">
@@ -5083,6 +5204,10 @@
       <c r="G31" s="40" t="s">
         <v>60</v>
       </c>
+      <c r="H31" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
     <row r="32" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A32" s="62">
@@ -5105,8 +5230,12 @@
       <c r="G32" s="39" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H32" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="63">
         <f>IF(ISBLANK(B33),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B33))</f>
         <v>38</v>
@@ -5125,8 +5254,12 @@
         <v>63</v>
       </c>
       <c r="G33" s="40"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H33" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="62">
         <f>IF(ISBLANK(B34),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B34))</f>
         <v>40</v>
@@ -5145,8 +5278,15 @@
         <v>64</v>
       </c>
       <c r="G34" s="39"/>
-    </row>
-    <row r="35" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="H34" t="str">
+        <f t="shared" si="0"/>
+        <v>3 h 05 min</v>
+      </c>
+      <c r="I34" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A35" s="63">
         <f>IF(ISBLANK(B35),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B35))</f>
         <v>40</v>
@@ -5167,8 +5307,12 @@
       <c r="G35" s="40" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="H35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A36" s="62">
         <f>IF(ISBLANK(B36),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B36))</f>
         <v>40</v>
@@ -5191,8 +5335,12 @@
       <c r="G36" s="39" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="H36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A37" s="63">
         <f>IF(ISBLANK(B37),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B37))</f>
         <v>40</v>
@@ -5213,8 +5361,12 @@
       <c r="G37" s="40" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="62">
         <f>IF(ISBLANK(B38),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B38))</f>
         <v>40</v>
@@ -5233,8 +5385,12 @@
         <v>70</v>
       </c>
       <c r="G38" s="39"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H38" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="63">
         <f>IF(ISBLANK(B39),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B39))</f>
         <v>40</v>
@@ -5257,8 +5413,12 @@
       <c r="G39" s="40" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H39" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="62">
         <f>IF(ISBLANK(B40),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B40))</f>
         <v>40</v>
@@ -5277,8 +5437,12 @@
         <v>73</v>
       </c>
       <c r="G40" s="39"/>
-    </row>
-    <row r="41" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="H40" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A41" s="63">
         <f>IF(ISBLANK(B41),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B41))</f>
         <v>41</v>
@@ -5299,8 +5463,15 @@
       <c r="G41" s="40" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="H41" t="str">
+        <f t="shared" si="0"/>
+        <v>3 h 05 min</v>
+      </c>
+      <c r="I41" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A42" s="62">
         <f>IF(ISBLANK(B42),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B42))</f>
         <v>41</v>
@@ -5321,8 +5492,12 @@
       <c r="G42" s="39" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H42" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="63">
         <f>IF(ISBLANK(B43),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B43))</f>
         <v>41</v>
@@ -5341,8 +5516,12 @@
         <v>76</v>
       </c>
       <c r="G43" s="40"/>
-    </row>
-    <row r="44" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="H43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A44" s="62">
         <f>IF(ISBLANK(B44),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B44))</f>
         <v>41</v>
@@ -5365,8 +5544,12 @@
       <c r="G44" s="39" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H44" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="63">
         <f>IF(ISBLANK(B45),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B45))</f>
         <v>41</v>
@@ -5385,8 +5568,12 @@
         <v>80</v>
       </c>
       <c r="G45" s="40"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H45" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="62">
         <f>IF(ISBLANK(B46),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B46))</f>
         <v>41</v>
@@ -5405,8 +5592,12 @@
         <v>81</v>
       </c>
       <c r="G46" s="39"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H46" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="63">
         <f>IF(ISBLANK(B47),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B47))</f>
         <v>41</v>
@@ -5427,8 +5618,12 @@
       <c r="G47" s="40" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H47" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="62">
         <f>IF(ISBLANK(B48),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B48))</f>
         <v>41</v>
@@ -5447,8 +5642,12 @@
         <v>84</v>
       </c>
       <c r="G48" s="39"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H48" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="63">
         <f>IF(ISBLANK(B49),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B49))</f>
         <v>41</v>
@@ -5467,8 +5666,15 @@
         <v>85</v>
       </c>
       <c r="G49" s="40"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H49" t="str">
+        <f t="shared" si="0"/>
+        <v>0 h 15 min</v>
+      </c>
+      <c r="I49" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="62" t="str">
         <f>IF(ISBLANK(B50),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B50))</f>
         <v/>
@@ -5479,8 +5685,12 @@
       <c r="E50" s="33"/>
       <c r="F50" s="22"/>
       <c r="G50" s="39"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H50" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="63" t="str">
         <f>IF(ISBLANK(B51),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B51))</f>
         <v/>
@@ -5491,8 +5701,12 @@
       <c r="E51" s="37"/>
       <c r="F51" s="22"/>
       <c r="G51" s="40"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H51" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="62" t="str">
         <f>IF(ISBLANK(B52),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B52))</f>
         <v/>
@@ -5503,8 +5717,12 @@
       <c r="E52" s="33"/>
       <c r="F52" s="22"/>
       <c r="G52" s="39"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H52" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="63" t="str">
         <f>IF(ISBLANK(B53),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B53))</f>
         <v/>
@@ -5515,8 +5733,12 @@
       <c r="E53" s="37"/>
       <c r="F53" s="22"/>
       <c r="G53" s="40"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H53" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="62" t="str">
         <f>IF(ISBLANK(B54),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B54))</f>
         <v/>
@@ -5527,8 +5749,12 @@
       <c r="E54" s="33"/>
       <c r="F54" s="22"/>
       <c r="G54" s="39"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H54" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="63" t="str">
         <f>IF(ISBLANK(B55),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B55))</f>
         <v/>
@@ -5539,8 +5765,12 @@
       <c r="E55" s="37"/>
       <c r="F55" s="22"/>
       <c r="G55" s="40"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H55" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="62" t="str">
         <f>IF(ISBLANK(B56),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B56))</f>
         <v/>
@@ -5551,8 +5781,12 @@
       <c r="E56" s="33"/>
       <c r="F56" s="39"/>
       <c r="G56" s="39"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H56" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="63" t="str">
         <f>IF(ISBLANK(B57),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B57))</f>
         <v/>
@@ -5563,8 +5797,12 @@
       <c r="E57" s="37"/>
       <c r="F57" s="40"/>
       <c r="G57" s="40"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H57" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="62" t="str">
         <f>IF(ISBLANK(B58),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B58))</f>
         <v/>
@@ -5575,8 +5813,12 @@
       <c r="E58" s="33"/>
       <c r="F58" s="39"/>
       <c r="G58" s="39"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H58" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="63" t="str">
         <f>IF(ISBLANK(B59),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B59))</f>
         <v/>
@@ -5587,8 +5829,12 @@
       <c r="E59" s="37"/>
       <c r="F59" s="40"/>
       <c r="G59" s="40"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H59" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="62" t="str">
         <f>IF(ISBLANK(B60),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B60))</f>
         <v/>
@@ -5599,8 +5845,12 @@
       <c r="E60" s="33"/>
       <c r="F60" s="39"/>
       <c r="G60" s="39"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H60" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="63" t="str">
         <f>IF(ISBLANK(B61),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B61))</f>
         <v/>
@@ -5611,8 +5861,12 @@
       <c r="E61" s="37"/>
       <c r="F61" s="40"/>
       <c r="G61" s="40"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H61" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="62" t="str">
         <f>IF(ISBLANK(B62),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B62))</f>
         <v/>
@@ -5623,8 +5877,12 @@
       <c r="E62" s="33"/>
       <c r="F62" s="39"/>
       <c r="G62" s="39"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H62" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="63" t="str">
         <f>IF(ISBLANK(B63),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B63))</f>
         <v/>
@@ -5635,8 +5893,12 @@
       <c r="E63" s="37"/>
       <c r="F63" s="40"/>
       <c r="G63" s="40"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H63" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="62" t="str">
         <f>IF(ISBLANK(B64),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B64))</f>
         <v/>
@@ -5647,8 +5909,12 @@
       <c r="E64" s="33"/>
       <c r="F64" s="39"/>
       <c r="G64" s="39"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H64" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="63" t="str">
         <f>IF(ISBLANK(B65),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B65))</f>
         <v/>
@@ -5659,8 +5925,12 @@
       <c r="E65" s="37"/>
       <c r="F65" s="40"/>
       <c r="G65" s="40"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H65" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="62" t="str">
         <f>IF(ISBLANK(B66),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B66))</f>
         <v/>
@@ -5671,8 +5941,12 @@
       <c r="E66" s="33"/>
       <c r="F66" s="39"/>
       <c r="G66" s="39"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H66" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="63" t="str">
         <f>IF(ISBLANK(B67),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B67))</f>
         <v/>
@@ -5683,8 +5957,12 @@
       <c r="E67" s="37"/>
       <c r="F67" s="40"/>
       <c r="G67" s="40"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H67" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="62" t="str">
         <f>IF(ISBLANK(B68),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B68))</f>
         <v/>
@@ -5695,8 +5973,12 @@
       <c r="E68" s="33"/>
       <c r="F68" s="39"/>
       <c r="G68" s="39"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H68" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="63" t="str">
         <f>IF(ISBLANK(B69),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B69))</f>
         <v/>
@@ -5707,8 +5989,12 @@
       <c r="E69" s="37"/>
       <c r="F69" s="40"/>
       <c r="G69" s="40"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H69" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="62" t="str">
         <f>IF(ISBLANK(B70),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B70))</f>
         <v/>
@@ -5719,8 +6005,12 @@
       <c r="E70" s="33"/>
       <c r="F70" s="39"/>
       <c r="G70" s="39"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H70" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="63" t="str">
         <f>IF(ISBLANK(B71),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B71))</f>
         <v/>
@@ -5731,8 +6021,12 @@
       <c r="E71" s="37"/>
       <c r="F71" s="40"/>
       <c r="G71" s="40"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H71" t="str">
+        <f t="shared" ref="H71:H134" si="1">IF(OR(ISBLANK(B71),B71=""),"",IF(B71=B70,"",INT(((SUMIF(B:B,B71,C:C)*60)+SUMIF(B:B,B71,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B71,C:C)*60)+SUMIF(B:B,B71,D:D),60),"00")&amp;" min"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="62" t="str">
         <f>IF(ISBLANK(B72),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B72))</f>
         <v/>
@@ -5743,8 +6037,12 @@
       <c r="E72" s="33"/>
       <c r="F72" s="39"/>
       <c r="G72" s="39"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H72" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="63" t="str">
         <f>IF(ISBLANK(B73),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B73))</f>
         <v/>
@@ -5755,8 +6053,12 @@
       <c r="E73" s="37"/>
       <c r="F73" s="40"/>
       <c r="G73" s="40"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H73" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="62" t="str">
         <f>IF(ISBLANK(B74),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B74))</f>
         <v/>
@@ -5767,8 +6069,12 @@
       <c r="E74" s="33"/>
       <c r="F74" s="39"/>
       <c r="G74" s="39"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H74" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="63" t="str">
         <f>IF(ISBLANK(B75),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B75))</f>
         <v/>
@@ -5779,8 +6085,12 @@
       <c r="E75" s="37"/>
       <c r="F75" s="40"/>
       <c r="G75" s="40"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H75" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="62" t="str">
         <f>IF(ISBLANK(B76),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B76))</f>
         <v/>
@@ -5791,8 +6101,12 @@
       <c r="E76" s="33"/>
       <c r="F76" s="39"/>
       <c r="G76" s="39"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H76" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="63" t="str">
         <f>IF(ISBLANK(B77),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B77))</f>
         <v/>
@@ -5803,8 +6117,12 @@
       <c r="E77" s="37"/>
       <c r="F77" s="40"/>
       <c r="G77" s="40"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H77" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="62" t="str">
         <f>IF(ISBLANK(B78),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B78))</f>
         <v/>
@@ -5815,8 +6133,12 @@
       <c r="E78" s="33"/>
       <c r="F78" s="39"/>
       <c r="G78" s="39"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H78" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="63" t="str">
         <f>IF(ISBLANK(B79),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B79))</f>
         <v/>
@@ -5827,8 +6149,12 @@
       <c r="E79" s="37"/>
       <c r="F79" s="40"/>
       <c r="G79" s="40"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H79" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="62" t="str">
         <f>IF(ISBLANK(B80),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B80))</f>
         <v/>
@@ -5839,8 +6165,12 @@
       <c r="E80" s="33"/>
       <c r="F80" s="39"/>
       <c r="G80" s="39"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H80" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="63" t="str">
         <f>IF(ISBLANK(B81),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B81))</f>
         <v/>
@@ -5851,8 +6181,12 @@
       <c r="E81" s="37"/>
       <c r="F81" s="40"/>
       <c r="G81" s="40"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H81" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="62" t="str">
         <f>IF(ISBLANK(B82),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B82))</f>
         <v/>
@@ -5863,8 +6197,12 @@
       <c r="E82" s="33"/>
       <c r="F82" s="39"/>
       <c r="G82" s="39"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H82" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="63" t="str">
         <f>IF(ISBLANK(B83),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B83))</f>
         <v/>
@@ -5875,8 +6213,12 @@
       <c r="E83" s="37"/>
       <c r="F83" s="40"/>
       <c r="G83" s="40"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H83" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="62" t="str">
         <f>IF(ISBLANK(B84),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B84))</f>
         <v/>
@@ -5887,8 +6229,12 @@
       <c r="E84" s="33"/>
       <c r="F84" s="39"/>
       <c r="G84" s="39"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H84" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="63" t="str">
         <f>IF(ISBLANK(B85),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B85))</f>
         <v/>
@@ -5899,8 +6245,12 @@
       <c r="E85" s="37"/>
       <c r="F85" s="40"/>
       <c r="G85" s="40"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H85" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="62" t="str">
         <f>IF(ISBLANK(B86),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B86))</f>
         <v/>
@@ -5911,8 +6261,12 @@
       <c r="E86" s="33"/>
       <c r="F86" s="39"/>
       <c r="G86" s="39"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H86" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="63" t="str">
         <f>IF(ISBLANK(B87),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B87))</f>
         <v/>
@@ -5923,8 +6277,12 @@
       <c r="E87" s="37"/>
       <c r="F87" s="40"/>
       <c r="G87" s="40"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H87" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="62" t="str">
         <f>IF(ISBLANK(B88),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B88))</f>
         <v/>
@@ -5935,8 +6293,12 @@
       <c r="E88" s="33"/>
       <c r="F88" s="39"/>
       <c r="G88" s="39"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H88" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="63" t="str">
         <f>IF(ISBLANK(B89),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B89))</f>
         <v/>
@@ -5947,8 +6309,12 @@
       <c r="E89" s="37"/>
       <c r="F89" s="40"/>
       <c r="G89" s="40"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H89" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="62" t="str">
         <f>IF(ISBLANK(B90),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B90))</f>
         <v/>
@@ -5959,8 +6325,12 @@
       <c r="E90" s="33"/>
       <c r="F90" s="39"/>
       <c r="G90" s="39"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H90" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="63" t="str">
         <f>IF(ISBLANK(B91),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B91))</f>
         <v/>
@@ -5971,8 +6341,12 @@
       <c r="E91" s="37"/>
       <c r="F91" s="40"/>
       <c r="G91" s="40"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H91" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="62" t="str">
         <f>IF(ISBLANK(B92),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B92))</f>
         <v/>
@@ -5983,8 +6357,12 @@
       <c r="E92" s="33"/>
       <c r="F92" s="39"/>
       <c r="G92" s="39"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H92" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="63" t="str">
         <f>IF(ISBLANK(B93),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B93))</f>
         <v/>
@@ -5995,8 +6373,12 @@
       <c r="E93" s="37"/>
       <c r="F93" s="40"/>
       <c r="G93" s="40"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H93" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="62" t="str">
         <f>IF(ISBLANK(B94),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B94))</f>
         <v/>
@@ -6007,8 +6389,12 @@
       <c r="E94" s="33"/>
       <c r="F94" s="39"/>
       <c r="G94" s="39"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H94" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="63" t="str">
         <f>IF(ISBLANK(B95),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B95))</f>
         <v/>
@@ -6019,8 +6405,12 @@
       <c r="E95" s="37"/>
       <c r="F95" s="40"/>
       <c r="G95" s="40"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H95" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="62" t="str">
         <f>IF(ISBLANK(B96),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B96))</f>
         <v/>
@@ -6031,8 +6421,12 @@
       <c r="E96" s="33"/>
       <c r="F96" s="39"/>
       <c r="G96" s="39"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H96" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="63" t="str">
         <f>IF(ISBLANK(B97),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B97))</f>
         <v/>
@@ -6043,8 +6437,12 @@
       <c r="E97" s="37"/>
       <c r="F97" s="40"/>
       <c r="G97" s="40"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H97" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="62" t="str">
         <f>IF(ISBLANK(B98),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B98))</f>
         <v/>
@@ -6055,8 +6453,12 @@
       <c r="E98" s="33"/>
       <c r="F98" s="39"/>
       <c r="G98" s="39"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H98" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="63" t="str">
         <f>IF(ISBLANK(B99),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B99))</f>
         <v/>
@@ -6067,8 +6469,12 @@
       <c r="E99" s="37"/>
       <c r="F99" s="40"/>
       <c r="G99" s="40"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H99" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="62" t="str">
         <f>IF(ISBLANK(B100),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B100))</f>
         <v/>
@@ -6079,8 +6485,12 @@
       <c r="E100" s="33"/>
       <c r="F100" s="39"/>
       <c r="G100" s="39"/>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H100" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="63" t="str">
         <f>IF(ISBLANK(B101),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B101))</f>
         <v/>
@@ -6091,8 +6501,12 @@
       <c r="E101" s="37"/>
       <c r="F101" s="40"/>
       <c r="G101" s="40"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H101" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="62" t="str">
         <f>IF(ISBLANK(B102),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B102))</f>
         <v/>
@@ -6103,8 +6517,12 @@
       <c r="E102" s="33"/>
       <c r="F102" s="39"/>
       <c r="G102" s="39"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H102" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="63" t="str">
         <f>IF(ISBLANK(B103),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B103))</f>
         <v/>
@@ -6115,8 +6533,12 @@
       <c r="E103" s="37"/>
       <c r="F103" s="40"/>
       <c r="G103" s="40"/>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H103" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="62" t="str">
         <f>IF(ISBLANK(B104),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B104))</f>
         <v/>
@@ -6127,8 +6549,12 @@
       <c r="E104" s="33"/>
       <c r="F104" s="39"/>
       <c r="G104" s="39"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H104" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="63" t="str">
         <f>IF(ISBLANK(B105),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B105))</f>
         <v/>
@@ -6139,8 +6565,12 @@
       <c r="E105" s="37"/>
       <c r="F105" s="40"/>
       <c r="G105" s="40"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H105" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="62" t="str">
         <f>IF(ISBLANK(B106),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B106))</f>
         <v/>
@@ -6151,8 +6581,12 @@
       <c r="E106" s="33"/>
       <c r="F106" s="39"/>
       <c r="G106" s="39"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H106" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="63" t="str">
         <f>IF(ISBLANK(B107),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B107))</f>
         <v/>
@@ -6163,8 +6597,12 @@
       <c r="E107" s="37"/>
       <c r="F107" s="40"/>
       <c r="G107" s="40"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H107" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="62" t="str">
         <f>IF(ISBLANK(B108),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B108))</f>
         <v/>
@@ -6175,8 +6613,12 @@
       <c r="E108" s="33"/>
       <c r="F108" s="39"/>
       <c r="G108" s="39"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H108" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="63" t="str">
         <f>IF(ISBLANK(B109),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B109))</f>
         <v/>
@@ -6187,8 +6629,12 @@
       <c r="E109" s="37"/>
       <c r="F109" s="40"/>
       <c r="G109" s="40"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H109" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="62" t="str">
         <f>IF(ISBLANK(B110),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B110))</f>
         <v/>
@@ -6199,8 +6645,12 @@
       <c r="E110" s="33"/>
       <c r="F110" s="39"/>
       <c r="G110" s="39"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H110" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="63" t="str">
         <f>IF(ISBLANK(B111),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B111))</f>
         <v/>
@@ -6211,8 +6661,12 @@
       <c r="E111" s="37"/>
       <c r="F111" s="40"/>
       <c r="G111" s="40"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H111" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="62" t="str">
         <f>IF(ISBLANK(B112),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B112))</f>
         <v/>
@@ -6223,8 +6677,12 @@
       <c r="E112" s="33"/>
       <c r="F112" s="39"/>
       <c r="G112" s="39"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H112" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="63" t="str">
         <f>IF(ISBLANK(B113),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B113))</f>
         <v/>
@@ -6235,8 +6693,12 @@
       <c r="E113" s="37"/>
       <c r="F113" s="40"/>
       <c r="G113" s="40"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H113" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="62" t="str">
         <f>IF(ISBLANK(B114),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B114))</f>
         <v/>
@@ -6247,8 +6709,12 @@
       <c r="E114" s="33"/>
       <c r="F114" s="39"/>
       <c r="G114" s="39"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H114" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="63" t="str">
         <f>IF(ISBLANK(B115),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B115))</f>
         <v/>
@@ -6259,8 +6725,12 @@
       <c r="E115" s="37"/>
       <c r="F115" s="40"/>
       <c r="G115" s="40"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H115" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="62" t="str">
         <f>IF(ISBLANK(B116),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B116))</f>
         <v/>
@@ -6271,8 +6741,12 @@
       <c r="E116" s="33"/>
       <c r="F116" s="39"/>
       <c r="G116" s="39"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H116" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="63" t="str">
         <f>IF(ISBLANK(B117),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B117))</f>
         <v/>
@@ -6283,8 +6757,12 @@
       <c r="E117" s="37"/>
       <c r="F117" s="40"/>
       <c r="G117" s="40"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H117" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="62" t="str">
         <f>IF(ISBLANK(B118),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B118))</f>
         <v/>
@@ -6295,8 +6773,12 @@
       <c r="E118" s="33"/>
       <c r="F118" s="39"/>
       <c r="G118" s="39"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H118" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="63" t="str">
         <f>IF(ISBLANK(B119),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B119))</f>
         <v/>
@@ -6307,8 +6789,12 @@
       <c r="E119" s="37"/>
       <c r="F119" s="40"/>
       <c r="G119" s="40"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H119" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="62" t="str">
         <f>IF(ISBLANK(B120),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B120))</f>
         <v/>
@@ -6319,8 +6805,12 @@
       <c r="E120" s="33"/>
       <c r="F120" s="39"/>
       <c r="G120" s="39"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H120" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="63" t="str">
         <f>IF(ISBLANK(B121),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B121))</f>
         <v/>
@@ -6331,8 +6821,12 @@
       <c r="E121" s="37"/>
       <c r="F121" s="40"/>
       <c r="G121" s="40"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H121" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="62" t="str">
         <f>IF(ISBLANK(B122),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B122))</f>
         <v/>
@@ -6343,8 +6837,12 @@
       <c r="E122" s="33"/>
       <c r="F122" s="39"/>
       <c r="G122" s="39"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H122" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="63" t="str">
         <f>IF(ISBLANK(B123),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B123))</f>
         <v/>
@@ -6355,8 +6853,12 @@
       <c r="E123" s="37"/>
       <c r="F123" s="40"/>
       <c r="G123" s="40"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H123" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="62" t="str">
         <f>IF(ISBLANK(B124),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B124))</f>
         <v/>
@@ -6367,8 +6869,12 @@
       <c r="E124" s="33"/>
       <c r="F124" s="39"/>
       <c r="G124" s="39"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H124" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="63" t="str">
         <f>IF(ISBLANK(B125),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B125))</f>
         <v/>
@@ -6379,8 +6885,12 @@
       <c r="E125" s="37"/>
       <c r="F125" s="40"/>
       <c r="G125" s="40"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H125" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="62" t="str">
         <f>IF(ISBLANK(B126),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B126))</f>
         <v/>
@@ -6391,8 +6901,12 @@
       <c r="E126" s="33"/>
       <c r="F126" s="39"/>
       <c r="G126" s="39"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H126" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="63" t="str">
         <f>IF(ISBLANK(B127),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B127))</f>
         <v/>
@@ -6403,8 +6917,12 @@
       <c r="E127" s="37"/>
       <c r="F127" s="40"/>
       <c r="G127" s="40"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H127" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="62" t="str">
         <f>IF(ISBLANK(B128),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B128))</f>
         <v/>
@@ -6415,8 +6933,12 @@
       <c r="E128" s="33"/>
       <c r="F128" s="39"/>
       <c r="G128" s="39"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H128" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="63" t="str">
         <f>IF(ISBLANK(B129),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B129))</f>
         <v/>
@@ -6427,8 +6949,12 @@
       <c r="E129" s="37"/>
       <c r="F129" s="40"/>
       <c r="G129" s="40"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H129" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="62" t="str">
         <f>IF(ISBLANK(B130),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B130))</f>
         <v/>
@@ -6439,8 +6965,12 @@
       <c r="E130" s="33"/>
       <c r="F130" s="39"/>
       <c r="G130" s="39"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H130" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="63" t="str">
         <f>IF(ISBLANK(B131),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B131))</f>
         <v/>
@@ -6451,8 +6981,12 @@
       <c r="E131" s="37"/>
       <c r="F131" s="40"/>
       <c r="G131" s="40"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H131" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="62" t="str">
         <f>IF(ISBLANK(B132),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B132))</f>
         <v/>
@@ -6463,8 +6997,12 @@
       <c r="E132" s="33"/>
       <c r="F132" s="39"/>
       <c r="G132" s="39"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H132" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="63" t="str">
         <f>IF(ISBLANK(B133),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B133))</f>
         <v/>
@@ -6475,8 +7013,12 @@
       <c r="E133" s="37"/>
       <c r="F133" s="40"/>
       <c r="G133" s="40"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="62" t="str">
         <f>IF(ISBLANK(B134),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B134))</f>
         <v/>
@@ -6487,8 +7029,12 @@
       <c r="E134" s="33"/>
       <c r="F134" s="39"/>
       <c r="G134" s="39"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H134" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="63" t="str">
         <f>IF(ISBLANK(B135),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B135))</f>
         <v/>
@@ -6499,8 +7045,12 @@
       <c r="E135" s="37"/>
       <c r="F135" s="40"/>
       <c r="G135" s="40"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H135" t="str">
+        <f t="shared" ref="H135:H198" si="2">IF(OR(ISBLANK(B135),B135=""),"",IF(B135=B134,"",INT(((SUMIF(B:B,B135,C:C)*60)+SUMIF(B:B,B135,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B135,C:C)*60)+SUMIF(B:B,B135,D:D),60),"00")&amp;" min"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="62" t="str">
         <f>IF(ISBLANK(B136),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B136))</f>
         <v/>
@@ -6511,8 +7061,12 @@
       <c r="E136" s="33"/>
       <c r="F136" s="39"/>
       <c r="G136" s="39"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H136" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="63" t="str">
         <f>IF(ISBLANK(B137),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B137))</f>
         <v/>
@@ -6523,8 +7077,12 @@
       <c r="E137" s="37"/>
       <c r="F137" s="40"/>
       <c r="G137" s="40"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H137" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="62" t="str">
         <f>IF(ISBLANK(B138),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B138))</f>
         <v/>
@@ -6535,8 +7093,12 @@
       <c r="E138" s="33"/>
       <c r="F138" s="39"/>
       <c r="G138" s="39"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H138" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="63" t="str">
         <f>IF(ISBLANK(B139),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B139))</f>
         <v/>
@@ -6547,8 +7109,12 @@
       <c r="E139" s="37"/>
       <c r="F139" s="40"/>
       <c r="G139" s="40"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H139" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="62" t="str">
         <f>IF(ISBLANK(B140),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B140))</f>
         <v/>
@@ -6559,8 +7125,12 @@
       <c r="E140" s="33"/>
       <c r="F140" s="39"/>
       <c r="G140" s="39"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H140" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="63" t="str">
         <f>IF(ISBLANK(B141),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B141))</f>
         <v/>
@@ -6571,8 +7141,12 @@
       <c r="E141" s="37"/>
       <c r="F141" s="40"/>
       <c r="G141" s="40"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H141" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="62" t="str">
         <f>IF(ISBLANK(B142),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B142))</f>
         <v/>
@@ -6583,8 +7157,12 @@
       <c r="E142" s="33"/>
       <c r="F142" s="39"/>
       <c r="G142" s="39"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H142" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="63" t="str">
         <f>IF(ISBLANK(B143),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B143))</f>
         <v/>
@@ -6595,8 +7173,12 @@
       <c r="E143" s="37"/>
       <c r="F143" s="40"/>
       <c r="G143" s="40"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H143" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="62" t="str">
         <f>IF(ISBLANK(B144),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B144))</f>
         <v/>
@@ -6607,8 +7189,12 @@
       <c r="E144" s="33"/>
       <c r="F144" s="39"/>
       <c r="G144" s="39"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H144" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="63" t="str">
         <f>IF(ISBLANK(B145),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B145))</f>
         <v/>
@@ -6619,8 +7205,12 @@
       <c r="E145" s="37"/>
       <c r="F145" s="40"/>
       <c r="G145" s="40"/>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H145" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="62" t="str">
         <f>IF(ISBLANK(B146),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B146))</f>
         <v/>
@@ -6631,8 +7221,12 @@
       <c r="E146" s="33"/>
       <c r="F146" s="39"/>
       <c r="G146" s="39"/>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H146" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="63" t="str">
         <f>IF(ISBLANK(B147),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B147))</f>
         <v/>
@@ -6643,8 +7237,12 @@
       <c r="E147" s="37"/>
       <c r="F147" s="40"/>
       <c r="G147" s="40"/>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H147" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="62" t="str">
         <f>IF(ISBLANK(B148),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B148))</f>
         <v/>
@@ -6655,8 +7253,12 @@
       <c r="E148" s="33"/>
       <c r="F148" s="39"/>
       <c r="G148" s="39"/>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="63" t="str">
         <f>IF(ISBLANK(B149),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B149))</f>
         <v/>
@@ -6667,8 +7269,12 @@
       <c r="E149" s="37"/>
       <c r="F149" s="40"/>
       <c r="G149" s="40"/>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H149" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="62" t="str">
         <f>IF(ISBLANK(B150),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B150))</f>
         <v/>
@@ -6679,8 +7285,12 @@
       <c r="E150" s="33"/>
       <c r="F150" s="39"/>
       <c r="G150" s="39"/>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H150" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="63" t="str">
         <f>IF(ISBLANK(B151),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B151))</f>
         <v/>
@@ -6691,8 +7301,12 @@
       <c r="E151" s="37"/>
       <c r="F151" s="40"/>
       <c r="G151" s="40"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H151" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="62" t="str">
         <f>IF(ISBLANK(B152),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B152))</f>
         <v/>
@@ -6703,8 +7317,12 @@
       <c r="E152" s="33"/>
       <c r="F152" s="39"/>
       <c r="G152" s="39"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H152" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="63" t="str">
         <f>IF(ISBLANK(B153),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B153))</f>
         <v/>
@@ -6715,8 +7333,12 @@
       <c r="E153" s="37"/>
       <c r="F153" s="40"/>
       <c r="G153" s="40"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H153" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="62" t="str">
         <f>IF(ISBLANK(B154),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B154))</f>
         <v/>
@@ -6727,8 +7349,12 @@
       <c r="E154" s="33"/>
       <c r="F154" s="39"/>
       <c r="G154" s="39"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H154" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="63" t="str">
         <f>IF(ISBLANK(B155),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B155))</f>
         <v/>
@@ -6739,8 +7365,12 @@
       <c r="E155" s="37"/>
       <c r="F155" s="40"/>
       <c r="G155" s="40"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H155" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="62" t="str">
         <f>IF(ISBLANK(B156),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B156))</f>
         <v/>
@@ -6751,8 +7381,12 @@
       <c r="E156" s="33"/>
       <c r="F156" s="39"/>
       <c r="G156" s="39"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H156" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="63" t="str">
         <f>IF(ISBLANK(B157),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B157))</f>
         <v/>
@@ -6763,8 +7397,12 @@
       <c r="E157" s="37"/>
       <c r="F157" s="40"/>
       <c r="G157" s="40"/>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H157" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="62" t="str">
         <f>IF(ISBLANK(B158),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B158))</f>
         <v/>
@@ -6775,8 +7413,12 @@
       <c r="E158" s="33"/>
       <c r="F158" s="39"/>
       <c r="G158" s="39"/>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H158" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="63" t="str">
         <f>IF(ISBLANK(B159),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B159))</f>
         <v/>
@@ -6787,8 +7429,12 @@
       <c r="E159" s="37"/>
       <c r="F159" s="40"/>
       <c r="G159" s="40"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H159" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="62" t="str">
         <f>IF(ISBLANK(B160),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B160))</f>
         <v/>
@@ -6799,8 +7445,12 @@
       <c r="E160" s="33"/>
       <c r="F160" s="39"/>
       <c r="G160" s="39"/>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H160" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="63" t="str">
         <f>IF(ISBLANK(B161),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B161))</f>
         <v/>
@@ -6811,8 +7461,12 @@
       <c r="E161" s="37"/>
       <c r="F161" s="40"/>
       <c r="G161" s="40"/>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H161" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="62" t="str">
         <f>IF(ISBLANK(B162),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B162))</f>
         <v/>
@@ -6823,8 +7477,12 @@
       <c r="E162" s="33"/>
       <c r="F162" s="39"/>
       <c r="G162" s="39"/>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H162" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="63" t="str">
         <f>IF(ISBLANK(B163),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B163))</f>
         <v/>
@@ -6835,8 +7493,12 @@
       <c r="E163" s="37"/>
       <c r="F163" s="40"/>
       <c r="G163" s="40"/>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H163" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="62" t="str">
         <f>IF(ISBLANK(B164),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B164))</f>
         <v/>
@@ -6847,8 +7509,12 @@
       <c r="E164" s="33"/>
       <c r="F164" s="39"/>
       <c r="G164" s="39"/>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H164" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="63" t="str">
         <f>IF(ISBLANK(B165),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B165))</f>
         <v/>
@@ -6859,8 +7525,12 @@
       <c r="E165" s="37"/>
       <c r="F165" s="40"/>
       <c r="G165" s="40"/>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H165" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="62" t="str">
         <f>IF(ISBLANK(B166),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B166))</f>
         <v/>
@@ -6871,8 +7541,12 @@
       <c r="E166" s="33"/>
       <c r="F166" s="39"/>
       <c r="G166" s="39"/>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H166" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="63" t="str">
         <f>IF(ISBLANK(B167),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B167))</f>
         <v/>
@@ -6883,8 +7557,12 @@
       <c r="E167" s="37"/>
       <c r="F167" s="40"/>
       <c r="G167" s="40"/>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H167" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="62" t="str">
         <f>IF(ISBLANK(B168),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B168))</f>
         <v/>
@@ -6895,8 +7573,12 @@
       <c r="E168" s="33"/>
       <c r="F168" s="39"/>
       <c r="G168" s="39"/>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H168" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="63" t="str">
         <f>IF(ISBLANK(B169),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B169))</f>
         <v/>
@@ -6907,8 +7589,12 @@
       <c r="E169" s="37"/>
       <c r="F169" s="40"/>
       <c r="G169" s="40"/>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H169" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="62" t="str">
         <f>IF(ISBLANK(B170),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B170))</f>
         <v/>
@@ -6919,8 +7605,12 @@
       <c r="E170" s="33"/>
       <c r="F170" s="39"/>
       <c r="G170" s="39"/>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H170" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="63" t="str">
         <f>IF(ISBLANK(B171),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B171))</f>
         <v/>
@@ -6931,8 +7621,12 @@
       <c r="E171" s="37"/>
       <c r="F171" s="40"/>
       <c r="G171" s="40"/>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H171" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="62" t="str">
         <f>IF(ISBLANK(B172),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B172))</f>
         <v/>
@@ -6943,8 +7637,12 @@
       <c r="E172" s="33"/>
       <c r="F172" s="39"/>
       <c r="G172" s="39"/>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H172" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="63" t="str">
         <f>IF(ISBLANK(B173),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B173))</f>
         <v/>
@@ -6955,8 +7653,12 @@
       <c r="E173" s="37"/>
       <c r="F173" s="40"/>
       <c r="G173" s="40"/>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H173" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="62" t="str">
         <f>IF(ISBLANK(B174),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B174))</f>
         <v/>
@@ -6967,8 +7669,12 @@
       <c r="E174" s="33"/>
       <c r="F174" s="39"/>
       <c r="G174" s="39"/>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H174" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="63" t="str">
         <f>IF(ISBLANK(B175),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B175))</f>
         <v/>
@@ -6979,8 +7685,12 @@
       <c r="E175" s="37"/>
       <c r="F175" s="40"/>
       <c r="G175" s="40"/>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H175" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="62" t="str">
         <f>IF(ISBLANK(B176),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B176))</f>
         <v/>
@@ -6991,8 +7701,12 @@
       <c r="E176" s="33"/>
       <c r="F176" s="39"/>
       <c r="G176" s="39"/>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H176" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="63" t="str">
         <f>IF(ISBLANK(B177),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B177))</f>
         <v/>
@@ -7003,8 +7717,12 @@
       <c r="E177" s="37"/>
       <c r="F177" s="40"/>
       <c r="G177" s="40"/>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H177" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="62" t="str">
         <f>IF(ISBLANK(B178),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B178))</f>
         <v/>
@@ -7015,8 +7733,12 @@
       <c r="E178" s="33"/>
       <c r="F178" s="39"/>
       <c r="G178" s="39"/>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H178" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="63" t="str">
         <f>IF(ISBLANK(B179),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B179))</f>
         <v/>
@@ -7027,8 +7749,12 @@
       <c r="E179" s="37"/>
       <c r="F179" s="40"/>
       <c r="G179" s="40"/>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H179" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="62" t="str">
         <f>IF(ISBLANK(B180),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B180))</f>
         <v/>
@@ -7039,8 +7765,12 @@
       <c r="E180" s="33"/>
       <c r="F180" s="39"/>
       <c r="G180" s="39"/>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H180" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="63" t="str">
         <f>IF(ISBLANK(B181),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B181))</f>
         <v/>
@@ -7051,8 +7781,12 @@
       <c r="E181" s="37"/>
       <c r="F181" s="40"/>
       <c r="G181" s="40"/>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H181" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="62" t="str">
         <f>IF(ISBLANK(B182),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B182))</f>
         <v/>
@@ -7063,8 +7797,12 @@
       <c r="E182" s="33"/>
       <c r="F182" s="39"/>
       <c r="G182" s="39"/>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H182" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="63" t="str">
         <f>IF(ISBLANK(B183),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B183))</f>
         <v/>
@@ -7075,8 +7813,12 @@
       <c r="E183" s="37"/>
       <c r="F183" s="40"/>
       <c r="G183" s="40"/>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H183" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="62" t="str">
         <f>IF(ISBLANK(B184),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B184))</f>
         <v/>
@@ -7087,8 +7829,12 @@
       <c r="E184" s="33"/>
       <c r="F184" s="39"/>
       <c r="G184" s="39"/>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H184" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="63" t="str">
         <f>IF(ISBLANK(B185),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B185))</f>
         <v/>
@@ -7099,8 +7845,12 @@
       <c r="E185" s="37"/>
       <c r="F185" s="40"/>
       <c r="G185" s="40"/>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H185" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="62" t="str">
         <f>IF(ISBLANK(B186),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B186))</f>
         <v/>
@@ -7111,8 +7861,12 @@
       <c r="E186" s="33"/>
       <c r="F186" s="39"/>
       <c r="G186" s="39"/>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H186" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="63" t="str">
         <f>IF(ISBLANK(B187),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B187))</f>
         <v/>
@@ -7123,8 +7877,12 @@
       <c r="E187" s="37"/>
       <c r="F187" s="40"/>
       <c r="G187" s="40"/>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H187" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="62" t="str">
         <f>IF(ISBLANK(B188),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B188))</f>
         <v/>
@@ -7135,8 +7893,12 @@
       <c r="E188" s="33"/>
       <c r="F188" s="39"/>
       <c r="G188" s="39"/>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H188" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="63" t="str">
         <f>IF(ISBLANK(B189),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B189))</f>
         <v/>
@@ -7147,8 +7909,12 @@
       <c r="E189" s="37"/>
       <c r="F189" s="40"/>
       <c r="G189" s="40"/>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H189" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="62" t="str">
         <f>IF(ISBLANK(B190),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B190))</f>
         <v/>
@@ -7159,8 +7925,12 @@
       <c r="E190" s="33"/>
       <c r="F190" s="39"/>
       <c r="G190" s="39"/>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H190" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="63" t="str">
         <f>IF(ISBLANK(B191),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B191))</f>
         <v/>
@@ -7171,8 +7941,12 @@
       <c r="E191" s="37"/>
       <c r="F191" s="40"/>
       <c r="G191" s="40"/>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H191" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="62" t="str">
         <f>IF(ISBLANK(B192),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B192))</f>
         <v/>
@@ -7183,8 +7957,12 @@
       <c r="E192" s="33"/>
       <c r="F192" s="39"/>
       <c r="G192" s="39"/>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H192" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="63" t="str">
         <f>IF(ISBLANK(B193),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B193))</f>
         <v/>
@@ -7195,8 +7973,12 @@
       <c r="E193" s="37"/>
       <c r="F193" s="40"/>
       <c r="G193" s="40"/>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H193" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="62" t="str">
         <f>IF(ISBLANK(B194),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B194))</f>
         <v/>
@@ -7207,8 +7989,12 @@
       <c r="E194" s="33"/>
       <c r="F194" s="39"/>
       <c r="G194" s="39"/>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H194" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="63" t="str">
         <f>IF(ISBLANK(B195),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B195))</f>
         <v/>
@@ -7219,8 +8005,12 @@
       <c r="E195" s="37"/>
       <c r="F195" s="40"/>
       <c r="G195" s="40"/>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H195" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="62" t="str">
         <f>IF(ISBLANK(B196),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B196))</f>
         <v/>
@@ -7231,8 +8021,12 @@
       <c r="E196" s="33"/>
       <c r="F196" s="39"/>
       <c r="G196" s="39"/>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H196" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="63" t="str">
         <f>IF(ISBLANK(B197),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B197))</f>
         <v/>
@@ -7243,8 +8037,12 @@
       <c r="E197" s="37"/>
       <c r="F197" s="40"/>
       <c r="G197" s="40"/>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H197" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="62" t="str">
         <f>IF(ISBLANK(B198),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B198))</f>
         <v/>
@@ -7255,8 +8053,12 @@
       <c r="E198" s="33"/>
       <c r="F198" s="39"/>
       <c r="G198" s="39"/>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H198" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="63" t="str">
         <f>IF(ISBLANK(B199),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B199))</f>
         <v/>
@@ -7267,8 +8069,12 @@
       <c r="E199" s="37"/>
       <c r="F199" s="40"/>
       <c r="G199" s="40"/>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H199" t="str">
+        <f t="shared" ref="H199:H262" si="3">IF(OR(ISBLANK(B199),B199=""),"",IF(B199=B198,"",INT(((SUMIF(B:B,B199,C:C)*60)+SUMIF(B:B,B199,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B199,C:C)*60)+SUMIF(B:B,B199,D:D),60),"00")&amp;" min"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="62" t="str">
         <f>IF(ISBLANK(B200),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B200))</f>
         <v/>
@@ -7279,8 +8085,12 @@
       <c r="E200" s="33"/>
       <c r="F200" s="39"/>
       <c r="G200" s="39"/>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H200" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="63" t="str">
         <f>IF(ISBLANK(B201),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B201))</f>
         <v/>
@@ -7291,8 +8101,12 @@
       <c r="E201" s="37"/>
       <c r="F201" s="40"/>
       <c r="G201" s="40"/>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H201" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="62" t="str">
         <f>IF(ISBLANK(B202),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B202))</f>
         <v/>
@@ -7303,8 +8117,12 @@
       <c r="E202" s="33"/>
       <c r="F202" s="39"/>
       <c r="G202" s="39"/>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H202" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="63" t="str">
         <f>IF(ISBLANK(B203),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B203))</f>
         <v/>
@@ -7315,8 +8133,12 @@
       <c r="E203" s="37"/>
       <c r="F203" s="40"/>
       <c r="G203" s="40"/>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H203" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="62" t="str">
         <f>IF(ISBLANK(B204),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B204))</f>
         <v/>
@@ -7327,8 +8149,12 @@
       <c r="E204" s="33"/>
       <c r="F204" s="39"/>
       <c r="G204" s="39"/>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H204" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="63" t="str">
         <f>IF(ISBLANK(B205),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B205))</f>
         <v/>
@@ -7339,8 +8165,12 @@
       <c r="E205" s="37"/>
       <c r="F205" s="40"/>
       <c r="G205" s="40"/>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H205" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="62" t="str">
         <f>IF(ISBLANK(B206),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B206))</f>
         <v/>
@@ -7351,8 +8181,12 @@
       <c r="E206" s="33"/>
       <c r="F206" s="39"/>
       <c r="G206" s="39"/>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H206" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="63" t="str">
         <f>IF(ISBLANK(B207),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B207))</f>
         <v/>
@@ -7363,8 +8197,12 @@
       <c r="E207" s="37"/>
       <c r="F207" s="40"/>
       <c r="G207" s="40"/>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H207" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="62" t="str">
         <f>IF(ISBLANK(B208),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B208))</f>
         <v/>
@@ -7375,8 +8213,12 @@
       <c r="E208" s="33"/>
       <c r="F208" s="39"/>
       <c r="G208" s="39"/>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H208" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="63" t="str">
         <f>IF(ISBLANK(B209),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B209))</f>
         <v/>
@@ -7387,8 +8229,12 @@
       <c r="E209" s="37"/>
       <c r="F209" s="40"/>
       <c r="G209" s="40"/>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H209" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="62" t="str">
         <f>IF(ISBLANK(B210),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B210))</f>
         <v/>
@@ -7399,8 +8245,12 @@
       <c r="E210" s="33"/>
       <c r="F210" s="39"/>
       <c r="G210" s="39"/>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H210" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="63" t="str">
         <f>IF(ISBLANK(B211),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B211))</f>
         <v/>
@@ -7411,8 +8261,12 @@
       <c r="E211" s="37"/>
       <c r="F211" s="40"/>
       <c r="G211" s="40"/>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H211" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="62" t="str">
         <f>IF(ISBLANK(B212),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B212))</f>
         <v/>
@@ -7423,8 +8277,12 @@
       <c r="E212" s="33"/>
       <c r="F212" s="39"/>
       <c r="G212" s="39"/>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H212" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="63" t="str">
         <f>IF(ISBLANK(B213),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B213))</f>
         <v/>
@@ -7435,8 +8293,12 @@
       <c r="E213" s="37"/>
       <c r="F213" s="40"/>
       <c r="G213" s="40"/>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H213" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="62" t="str">
         <f>IF(ISBLANK(B214),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B214))</f>
         <v/>
@@ -7447,8 +8309,12 @@
       <c r="E214" s="33"/>
       <c r="F214" s="39"/>
       <c r="G214" s="39"/>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H214" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="63" t="str">
         <f>IF(ISBLANK(B215),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B215))</f>
         <v/>
@@ -7459,8 +8325,12 @@
       <c r="E215" s="37"/>
       <c r="F215" s="40"/>
       <c r="G215" s="40"/>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H215" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="62" t="str">
         <f>IF(ISBLANK(B216),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B216))</f>
         <v/>
@@ -7471,8 +8341,12 @@
       <c r="E216" s="33"/>
       <c r="F216" s="39"/>
       <c r="G216" s="39"/>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H216" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="63" t="str">
         <f>IF(ISBLANK(B217),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B217))</f>
         <v/>
@@ -7483,8 +8357,12 @@
       <c r="E217" s="37"/>
       <c r="F217" s="40"/>
       <c r="G217" s="40"/>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H217" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="62" t="str">
         <f>IF(ISBLANK(B218),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B218))</f>
         <v/>
@@ -7495,8 +8373,12 @@
       <c r="E218" s="33"/>
       <c r="F218" s="39"/>
       <c r="G218" s="39"/>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H218" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="63" t="str">
         <f>IF(ISBLANK(B219),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B219))</f>
         <v/>
@@ -7507,8 +8389,12 @@
       <c r="E219" s="37"/>
       <c r="F219" s="40"/>
       <c r="G219" s="40"/>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H219" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="62" t="str">
         <f>IF(ISBLANK(B220),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B220))</f>
         <v/>
@@ -7519,8 +8405,12 @@
       <c r="E220" s="33"/>
       <c r="F220" s="39"/>
       <c r="G220" s="39"/>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H220" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="63" t="str">
         <f>IF(ISBLANK(B221),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B221))</f>
         <v/>
@@ -7531,8 +8421,12 @@
       <c r="E221" s="37"/>
       <c r="F221" s="40"/>
       <c r="G221" s="40"/>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H221" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="62" t="str">
         <f>IF(ISBLANK(B222),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B222))</f>
         <v/>
@@ -7543,8 +8437,12 @@
       <c r="E222" s="33"/>
       <c r="F222" s="39"/>
       <c r="G222" s="39"/>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H222" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="63" t="str">
         <f>IF(ISBLANK(B223),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B223))</f>
         <v/>
@@ -7555,8 +8453,12 @@
       <c r="E223" s="37"/>
       <c r="F223" s="40"/>
       <c r="G223" s="40"/>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H223" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="62" t="str">
         <f>IF(ISBLANK(B224),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B224))</f>
         <v/>
@@ -7567,8 +8469,12 @@
       <c r="E224" s="33"/>
       <c r="F224" s="39"/>
       <c r="G224" s="39"/>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H224" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="63" t="str">
         <f>IF(ISBLANK(B225),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B225))</f>
         <v/>
@@ -7579,8 +8485,12 @@
       <c r="E225" s="37"/>
       <c r="F225" s="40"/>
       <c r="G225" s="40"/>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H225" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="62" t="str">
         <f>IF(ISBLANK(B226),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B226))</f>
         <v/>
@@ -7591,8 +8501,12 @@
       <c r="E226" s="33"/>
       <c r="F226" s="39"/>
       <c r="G226" s="39"/>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H226" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="63" t="str">
         <f>IF(ISBLANK(B227),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B227))</f>
         <v/>
@@ -7603,8 +8517,12 @@
       <c r="E227" s="37"/>
       <c r="F227" s="40"/>
       <c r="G227" s="40"/>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H227" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="62" t="str">
         <f>IF(ISBLANK(B228),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B228))</f>
         <v/>
@@ -7615,8 +8533,12 @@
       <c r="E228" s="33"/>
       <c r="F228" s="39"/>
       <c r="G228" s="39"/>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H228" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="63" t="str">
         <f>IF(ISBLANK(B229),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B229))</f>
         <v/>
@@ -7627,8 +8549,12 @@
       <c r="E229" s="37"/>
       <c r="F229" s="40"/>
       <c r="G229" s="40"/>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H229" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="62" t="str">
         <f>IF(ISBLANK(B230),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B230))</f>
         <v/>
@@ -7639,8 +8565,12 @@
       <c r="E230" s="33"/>
       <c r="F230" s="39"/>
       <c r="G230" s="39"/>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H230" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="63" t="str">
         <f>IF(ISBLANK(B231),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B231))</f>
         <v/>
@@ -7651,8 +8581,12 @@
       <c r="E231" s="37"/>
       <c r="F231" s="40"/>
       <c r="G231" s="40"/>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H231" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="62" t="str">
         <f>IF(ISBLANK(B232),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B232))</f>
         <v/>
@@ -7663,8 +8597,12 @@
       <c r="E232" s="33"/>
       <c r="F232" s="39"/>
       <c r="G232" s="39"/>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H232" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="63" t="str">
         <f>IF(ISBLANK(B233),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B233))</f>
         <v/>
@@ -7675,8 +8613,12 @@
       <c r="E233" s="37"/>
       <c r="F233" s="40"/>
       <c r="G233" s="40"/>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H233" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="62" t="str">
         <f>IF(ISBLANK(B234),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B234))</f>
         <v/>
@@ -7687,8 +8629,12 @@
       <c r="E234" s="33"/>
       <c r="F234" s="39"/>
       <c r="G234" s="39"/>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H234" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="63" t="str">
         <f>IF(ISBLANK(B235),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B235))</f>
         <v/>
@@ -7699,8 +8645,12 @@
       <c r="E235" s="37"/>
       <c r="F235" s="40"/>
       <c r="G235" s="40"/>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H235" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="62" t="str">
         <f>IF(ISBLANK(B236),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B236))</f>
         <v/>
@@ -7711,8 +8661,12 @@
       <c r="E236" s="33"/>
       <c r="F236" s="39"/>
       <c r="G236" s="39"/>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H236" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="63" t="str">
         <f>IF(ISBLANK(B237),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B237))</f>
         <v/>
@@ -7723,8 +8677,12 @@
       <c r="E237" s="37"/>
       <c r="F237" s="40"/>
       <c r="G237" s="40"/>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H237" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="62" t="str">
         <f>IF(ISBLANK(B238),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B238))</f>
         <v/>
@@ -7735,8 +8693,12 @@
       <c r="E238" s="33"/>
       <c r="F238" s="39"/>
       <c r="G238" s="39"/>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H238" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="63" t="str">
         <f>IF(ISBLANK(B239),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B239))</f>
         <v/>
@@ -7747,8 +8709,12 @@
       <c r="E239" s="37"/>
       <c r="F239" s="40"/>
       <c r="G239" s="40"/>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H239" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="62" t="str">
         <f>IF(ISBLANK(B240),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B240))</f>
         <v/>
@@ -7759,8 +8725,12 @@
       <c r="E240" s="33"/>
       <c r="F240" s="39"/>
       <c r="G240" s="39"/>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H240" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="63" t="str">
         <f>IF(ISBLANK(B241),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B241))</f>
         <v/>
@@ -7771,8 +8741,12 @@
       <c r="E241" s="37"/>
       <c r="F241" s="40"/>
       <c r="G241" s="40"/>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H241" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="62" t="str">
         <f>IF(ISBLANK(B242),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B242))</f>
         <v/>
@@ -7783,8 +8757,12 @@
       <c r="E242" s="33"/>
       <c r="F242" s="39"/>
       <c r="G242" s="39"/>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H242" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="63" t="str">
         <f>IF(ISBLANK(B243),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B243))</f>
         <v/>
@@ -7795,8 +8773,12 @@
       <c r="E243" s="37"/>
       <c r="F243" s="40"/>
       <c r="G243" s="40"/>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H243" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="62" t="str">
         <f>IF(ISBLANK(B244),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B244))</f>
         <v/>
@@ -7807,8 +8789,12 @@
       <c r="E244" s="33"/>
       <c r="F244" s="39"/>
       <c r="G244" s="39"/>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H244" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="63" t="str">
         <f>IF(ISBLANK(B245),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B245))</f>
         <v/>
@@ -7819,8 +8805,12 @@
       <c r="E245" s="37"/>
       <c r="F245" s="40"/>
       <c r="G245" s="40"/>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H245" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="62" t="str">
         <f>IF(ISBLANK(B246),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B246))</f>
         <v/>
@@ -7831,8 +8821,12 @@
       <c r="E246" s="33"/>
       <c r="F246" s="39"/>
       <c r="G246" s="39"/>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H246" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="63" t="str">
         <f>IF(ISBLANK(B247),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B247))</f>
         <v/>
@@ -7843,8 +8837,12 @@
       <c r="E247" s="37"/>
       <c r="F247" s="40"/>
       <c r="G247" s="40"/>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H247" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="62" t="str">
         <f>IF(ISBLANK(B248),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B248))</f>
         <v/>
@@ -7855,8 +8853,12 @@
       <c r="E248" s="33"/>
       <c r="F248" s="39"/>
       <c r="G248" s="39"/>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H248" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="63" t="str">
         <f>IF(ISBLANK(B249),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B249))</f>
         <v/>
@@ -7867,8 +8869,12 @@
       <c r="E249" s="37"/>
       <c r="F249" s="40"/>
       <c r="G249" s="40"/>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H249" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="62" t="str">
         <f>IF(ISBLANK(B250),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B250))</f>
         <v/>
@@ -7879,8 +8885,12 @@
       <c r="E250" s="33"/>
       <c r="F250" s="39"/>
       <c r="G250" s="39"/>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H250" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="63" t="str">
         <f>IF(ISBLANK(B251),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B251))</f>
         <v/>
@@ -7891,8 +8901,12 @@
       <c r="E251" s="37"/>
       <c r="F251" s="40"/>
       <c r="G251" s="40"/>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H251" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="62" t="str">
         <f>IF(ISBLANK(B252),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B252))</f>
         <v/>
@@ -7903,8 +8917,12 @@
       <c r="E252" s="33"/>
       <c r="F252" s="39"/>
       <c r="G252" s="39"/>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H252" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="63" t="str">
         <f>IF(ISBLANK(B253),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B253))</f>
         <v/>
@@ -7915,8 +8933,12 @@
       <c r="E253" s="37"/>
       <c r="F253" s="40"/>
       <c r="G253" s="40"/>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H253" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="62" t="str">
         <f>IF(ISBLANK(B254),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B254))</f>
         <v/>
@@ -7927,8 +8949,12 @@
       <c r="E254" s="33"/>
       <c r="F254" s="39"/>
       <c r="G254" s="39"/>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H254" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="63" t="str">
         <f>IF(ISBLANK(B255),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B255))</f>
         <v/>
@@ -7939,8 +8965,12 @@
       <c r="E255" s="37"/>
       <c r="F255" s="40"/>
       <c r="G255" s="40"/>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H255" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="62" t="str">
         <f>IF(ISBLANK(B256),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B256))</f>
         <v/>
@@ -7951,8 +8981,12 @@
       <c r="E256" s="33"/>
       <c r="F256" s="39"/>
       <c r="G256" s="39"/>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H256" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="63" t="str">
         <f>IF(ISBLANK(B257),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B257))</f>
         <v/>
@@ -7963,8 +8997,12 @@
       <c r="E257" s="37"/>
       <c r="F257" s="40"/>
       <c r="G257" s="40"/>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H257" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="62" t="str">
         <f>IF(ISBLANK(B258),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B258))</f>
         <v/>
@@ -7975,8 +9013,12 @@
       <c r="E258" s="33"/>
       <c r="F258" s="39"/>
       <c r="G258" s="39"/>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H258" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="63" t="str">
         <f>IF(ISBLANK(B259),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B259))</f>
         <v/>
@@ -7987,8 +9029,12 @@
       <c r="E259" s="37"/>
       <c r="F259" s="40"/>
       <c r="G259" s="40"/>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H259" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="62" t="str">
         <f>IF(ISBLANK(B260),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B260))</f>
         <v/>
@@ -7999,8 +9045,12 @@
       <c r="E260" s="33"/>
       <c r="F260" s="39"/>
       <c r="G260" s="39"/>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H260" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="63" t="str">
         <f>IF(ISBLANK(B261),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B261))</f>
         <v/>
@@ -8011,8 +9061,12 @@
       <c r="E261" s="37"/>
       <c r="F261" s="40"/>
       <c r="G261" s="40"/>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H261" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="62" t="str">
         <f>IF(ISBLANK(B262),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B262))</f>
         <v/>
@@ -8023,8 +9077,12 @@
       <c r="E262" s="33"/>
       <c r="F262" s="39"/>
       <c r="G262" s="39"/>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H262" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="63" t="str">
         <f>IF(ISBLANK(B263),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B263))</f>
         <v/>
@@ -8035,8 +9093,12 @@
       <c r="E263" s="37"/>
       <c r="F263" s="40"/>
       <c r="G263" s="40"/>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H263" t="str">
+        <f t="shared" ref="H263:H326" si="4">IF(OR(ISBLANK(B263),B263=""),"",IF(B263=B262,"",INT(((SUMIF(B:B,B263,C:C)*60)+SUMIF(B:B,B263,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B263,C:C)*60)+SUMIF(B:B,B263,D:D),60),"00")&amp;" min"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="62" t="str">
         <f>IF(ISBLANK(B264),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B264))</f>
         <v/>
@@ -8047,8 +9109,12 @@
       <c r="E264" s="33"/>
       <c r="F264" s="39"/>
       <c r="G264" s="39"/>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H264" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="63" t="str">
         <f>IF(ISBLANK(B265),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B265))</f>
         <v/>
@@ -8059,8 +9125,12 @@
       <c r="E265" s="37"/>
       <c r="F265" s="40"/>
       <c r="G265" s="40"/>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H265" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="62" t="str">
         <f>IF(ISBLANK(B266),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B266))</f>
         <v/>
@@ -8071,8 +9141,12 @@
       <c r="E266" s="33"/>
       <c r="F266" s="39"/>
       <c r="G266" s="39"/>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H266" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="63" t="str">
         <f>IF(ISBLANK(B267),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B267))</f>
         <v/>
@@ -8083,8 +9157,12 @@
       <c r="E267" s="37"/>
       <c r="F267" s="40"/>
       <c r="G267" s="40"/>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H267" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" s="62" t="str">
         <f>IF(ISBLANK(B268),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B268))</f>
         <v/>
@@ -8095,8 +9173,12 @@
       <c r="E268" s="33"/>
       <c r="F268" s="39"/>
       <c r="G268" s="39"/>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H268" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" s="63" t="str">
         <f>IF(ISBLANK(B269),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B269))</f>
         <v/>
@@ -8107,8 +9189,12 @@
       <c r="E269" s="37"/>
       <c r="F269" s="40"/>
       <c r="G269" s="40"/>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H269" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" s="62" t="str">
         <f>IF(ISBLANK(B270),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B270))</f>
         <v/>
@@ -8119,8 +9205,12 @@
       <c r="E270" s="33"/>
       <c r="F270" s="39"/>
       <c r="G270" s="39"/>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H270" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="63" t="str">
         <f>IF(ISBLANK(B271),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B271))</f>
         <v/>
@@ -8131,8 +9221,12 @@
       <c r="E271" s="37"/>
       <c r="F271" s="40"/>
       <c r="G271" s="40"/>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H271" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="62" t="str">
         <f>IF(ISBLANK(B272),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B272))</f>
         <v/>
@@ -8143,8 +9237,12 @@
       <c r="E272" s="33"/>
       <c r="F272" s="39"/>
       <c r="G272" s="39"/>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H272" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" s="63" t="str">
         <f>IF(ISBLANK(B273),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B273))</f>
         <v/>
@@ -8155,8 +9253,12 @@
       <c r="E273" s="37"/>
       <c r="F273" s="40"/>
       <c r="G273" s="40"/>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H273" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" s="62" t="str">
         <f>IF(ISBLANK(B274),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B274))</f>
         <v/>
@@ -8167,8 +9269,12 @@
       <c r="E274" s="33"/>
       <c r="F274" s="39"/>
       <c r="G274" s="39"/>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H274" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" s="63" t="str">
         <f>IF(ISBLANK(B275),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B275))</f>
         <v/>
@@ -8179,8 +9285,12 @@
       <c r="E275" s="37"/>
       <c r="F275" s="40"/>
       <c r="G275" s="40"/>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H275" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" s="62" t="str">
         <f>IF(ISBLANK(B276),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B276))</f>
         <v/>
@@ -8191,8 +9301,12 @@
       <c r="E276" s="33"/>
       <c r="F276" s="39"/>
       <c r="G276" s="39"/>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H276" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" s="63" t="str">
         <f>IF(ISBLANK(B277),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B277))</f>
         <v/>
@@ -8203,8 +9317,12 @@
       <c r="E277" s="37"/>
       <c r="F277" s="40"/>
       <c r="G277" s="40"/>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H277" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="62" t="str">
         <f>IF(ISBLANK(B278),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B278))</f>
         <v/>
@@ -8215,8 +9333,12 @@
       <c r="E278" s="33"/>
       <c r="F278" s="39"/>
       <c r="G278" s="39"/>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H278" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" s="63" t="str">
         <f>IF(ISBLANK(B279),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B279))</f>
         <v/>
@@ -8227,8 +9349,12 @@
       <c r="E279" s="37"/>
       <c r="F279" s="40"/>
       <c r="G279" s="40"/>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H279" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="62" t="str">
         <f>IF(ISBLANK(B280),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B280))</f>
         <v/>
@@ -8239,8 +9365,12 @@
       <c r="E280" s="33"/>
       <c r="F280" s="39"/>
       <c r="G280" s="39"/>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H280" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="63" t="str">
         <f>IF(ISBLANK(B281),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B281))</f>
         <v/>
@@ -8251,8 +9381,12 @@
       <c r="E281" s="37"/>
       <c r="F281" s="40"/>
       <c r="G281" s="40"/>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H281" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="62" t="str">
         <f>IF(ISBLANK(B282),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B282))</f>
         <v/>
@@ -8263,8 +9397,12 @@
       <c r="E282" s="33"/>
       <c r="F282" s="39"/>
       <c r="G282" s="39"/>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H282" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="63" t="str">
         <f>IF(ISBLANK(B283),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B283))</f>
         <v/>
@@ -8275,8 +9413,12 @@
       <c r="E283" s="37"/>
       <c r="F283" s="40"/>
       <c r="G283" s="40"/>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H283" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="62" t="str">
         <f>IF(ISBLANK(B284),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B284))</f>
         <v/>
@@ -8287,8 +9429,12 @@
       <c r="E284" s="33"/>
       <c r="F284" s="39"/>
       <c r="G284" s="39"/>
-    </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H284" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="63" t="str">
         <f>IF(ISBLANK(B285),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B285))</f>
         <v/>
@@ -8299,8 +9445,12 @@
       <c r="E285" s="37"/>
       <c r="F285" s="40"/>
       <c r="G285" s="40"/>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H285" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="62" t="str">
         <f>IF(ISBLANK(B286),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B286))</f>
         <v/>
@@ -8311,8 +9461,12 @@
       <c r="E286" s="33"/>
       <c r="F286" s="39"/>
       <c r="G286" s="39"/>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H286" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="63" t="str">
         <f>IF(ISBLANK(B287),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B287))</f>
         <v/>
@@ -8323,8 +9477,12 @@
       <c r="E287" s="37"/>
       <c r="F287" s="40"/>
       <c r="G287" s="40"/>
-    </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H287" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="62" t="str">
         <f>IF(ISBLANK(B288),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B288))</f>
         <v/>
@@ -8335,8 +9493,12 @@
       <c r="E288" s="33"/>
       <c r="F288" s="39"/>
       <c r="G288" s="39"/>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H288" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="63" t="str">
         <f>IF(ISBLANK(B289),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B289))</f>
         <v/>
@@ -8347,8 +9509,12 @@
       <c r="E289" s="37"/>
       <c r="F289" s="40"/>
       <c r="G289" s="40"/>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H289" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="62" t="str">
         <f>IF(ISBLANK(B290),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B290))</f>
         <v/>
@@ -8359,8 +9525,12 @@
       <c r="E290" s="33"/>
       <c r="F290" s="39"/>
       <c r="G290" s="39"/>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H290" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="63" t="str">
         <f>IF(ISBLANK(B291),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B291))</f>
         <v/>
@@ -8371,8 +9541,12 @@
       <c r="E291" s="37"/>
       <c r="F291" s="40"/>
       <c r="G291" s="40"/>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H291" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="62" t="str">
         <f>IF(ISBLANK(B292),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B292))</f>
         <v/>
@@ -8383,8 +9557,12 @@
       <c r="E292" s="33"/>
       <c r="F292" s="39"/>
       <c r="G292" s="39"/>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H292" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="63" t="str">
         <f>IF(ISBLANK(B293),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B293))</f>
         <v/>
@@ -8395,8 +9573,12 @@
       <c r="E293" s="37"/>
       <c r="F293" s="40"/>
       <c r="G293" s="40"/>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H293" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="62" t="str">
         <f>IF(ISBLANK(B294),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B294))</f>
         <v/>
@@ -8407,8 +9589,12 @@
       <c r="E294" s="33"/>
       <c r="F294" s="39"/>
       <c r="G294" s="39"/>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H294" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="63" t="str">
         <f>IF(ISBLANK(B295),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B295))</f>
         <v/>
@@ -8419,8 +9605,12 @@
       <c r="E295" s="37"/>
       <c r="F295" s="40"/>
       <c r="G295" s="40"/>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H295" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="62" t="str">
         <f>IF(ISBLANK(B296),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B296))</f>
         <v/>
@@ -8431,8 +9621,12 @@
       <c r="E296" s="33"/>
       <c r="F296" s="39"/>
       <c r="G296" s="39"/>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H296" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="63" t="str">
         <f>IF(ISBLANK(B297),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B297))</f>
         <v/>
@@ -8443,8 +9637,12 @@
       <c r="E297" s="37"/>
       <c r="F297" s="40"/>
       <c r="G297" s="40"/>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H297" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="62" t="str">
         <f>IF(ISBLANK(B298),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B298))</f>
         <v/>
@@ -8455,8 +9653,12 @@
       <c r="E298" s="33"/>
       <c r="F298" s="39"/>
       <c r="G298" s="39"/>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H298" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="63" t="str">
         <f>IF(ISBLANK(B299),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B299))</f>
         <v/>
@@ -8467,8 +9669,12 @@
       <c r="E299" s="37"/>
       <c r="F299" s="40"/>
       <c r="G299" s="40"/>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H299" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="62" t="str">
         <f>IF(ISBLANK(B300),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B300))</f>
         <v/>
@@ -8479,8 +9685,12 @@
       <c r="E300" s="33"/>
       <c r="F300" s="39"/>
       <c r="G300" s="39"/>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H300" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" s="63" t="str">
         <f>IF(ISBLANK(B301),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B301))</f>
         <v/>
@@ -8491,8 +9701,12 @@
       <c r="E301" s="37"/>
       <c r="F301" s="40"/>
       <c r="G301" s="40"/>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H301" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="62" t="str">
         <f>IF(ISBLANK(B302),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B302))</f>
         <v/>
@@ -8503,8 +9717,12 @@
       <c r="E302" s="33"/>
       <c r="F302" s="39"/>
       <c r="G302" s="39"/>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H302" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="63" t="str">
         <f>IF(ISBLANK(B303),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B303))</f>
         <v/>
@@ -8515,8 +9733,12 @@
       <c r="E303" s="37"/>
       <c r="F303" s="40"/>
       <c r="G303" s="40"/>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H303" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" s="62" t="str">
         <f>IF(ISBLANK(B304),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B304))</f>
         <v/>
@@ -8527,8 +9749,12 @@
       <c r="E304" s="33"/>
       <c r="F304" s="39"/>
       <c r="G304" s="39"/>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H304" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="63" t="str">
         <f>IF(ISBLANK(B305),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B305))</f>
         <v/>
@@ -8539,8 +9765,12 @@
       <c r="E305" s="37"/>
       <c r="F305" s="40"/>
       <c r="G305" s="40"/>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H305" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" s="62" t="str">
         <f>IF(ISBLANK(B306),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B306))</f>
         <v/>
@@ -8551,8 +9781,12 @@
       <c r="E306" s="33"/>
       <c r="F306" s="39"/>
       <c r="G306" s="39"/>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H306" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="63" t="str">
         <f>IF(ISBLANK(B307),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B307))</f>
         <v/>
@@ -8563,8 +9797,12 @@
       <c r="E307" s="37"/>
       <c r="F307" s="40"/>
       <c r="G307" s="40"/>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H307" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" s="62" t="str">
         <f>IF(ISBLANK(B308),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B308))</f>
         <v/>
@@ -8575,8 +9813,12 @@
       <c r="E308" s="33"/>
       <c r="F308" s="39"/>
       <c r="G308" s="39"/>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H308" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="63" t="str">
         <f>IF(ISBLANK(B309),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B309))</f>
         <v/>
@@ -8587,8 +9829,12 @@
       <c r="E309" s="37"/>
       <c r="F309" s="40"/>
       <c r="G309" s="40"/>
-    </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H309" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="62" t="str">
         <f>IF(ISBLANK(B310),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B310))</f>
         <v/>
@@ -8599,8 +9845,12 @@
       <c r="E310" s="33"/>
       <c r="F310" s="39"/>
       <c r="G310" s="39"/>
-    </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H310" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="63" t="str">
         <f>IF(ISBLANK(B311),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B311))</f>
         <v/>
@@ -8611,8 +9861,12 @@
       <c r="E311" s="37"/>
       <c r="F311" s="40"/>
       <c r="G311" s="40"/>
-    </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H311" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" s="62" t="str">
         <f>IF(ISBLANK(B312),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B312))</f>
         <v/>
@@ -8623,8 +9877,12 @@
       <c r="E312" s="33"/>
       <c r="F312" s="39"/>
       <c r="G312" s="39"/>
-    </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H312" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="63" t="str">
         <f>IF(ISBLANK(B313),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B313))</f>
         <v/>
@@ -8635,8 +9893,12 @@
       <c r="E313" s="37"/>
       <c r="F313" s="40"/>
       <c r="G313" s="40"/>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H313" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" s="62" t="str">
         <f>IF(ISBLANK(B314),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B314))</f>
         <v/>
@@ -8647,8 +9909,12 @@
       <c r="E314" s="33"/>
       <c r="F314" s="39"/>
       <c r="G314" s="39"/>
-    </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H314" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="63" t="str">
         <f>IF(ISBLANK(B315),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B315))</f>
         <v/>
@@ -8659,8 +9925,12 @@
       <c r="E315" s="37"/>
       <c r="F315" s="40"/>
       <c r="G315" s="40"/>
-    </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H315" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="62" t="str">
         <f>IF(ISBLANK(B316),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B316))</f>
         <v/>
@@ -8671,8 +9941,12 @@
       <c r="E316" s="33"/>
       <c r="F316" s="39"/>
       <c r="G316" s="39"/>
-    </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H316" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" s="63" t="str">
         <f>IF(ISBLANK(B317),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B317))</f>
         <v/>
@@ -8683,8 +9957,12 @@
       <c r="E317" s="37"/>
       <c r="F317" s="40"/>
       <c r="G317" s="40"/>
-    </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H317" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="62" t="str">
         <f>IF(ISBLANK(B318),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B318))</f>
         <v/>
@@ -8695,8 +9973,12 @@
       <c r="E318" s="33"/>
       <c r="F318" s="39"/>
       <c r="G318" s="39"/>
-    </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H318" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="63" t="str">
         <f>IF(ISBLANK(B319),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B319))</f>
         <v/>
@@ -8707,8 +9989,12 @@
       <c r="E319" s="37"/>
       <c r="F319" s="40"/>
       <c r="G319" s="40"/>
-    </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H319" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" s="62" t="str">
         <f>IF(ISBLANK(B320),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B320))</f>
         <v/>
@@ -8719,8 +10005,12 @@
       <c r="E320" s="33"/>
       <c r="F320" s="39"/>
       <c r="G320" s="39"/>
-    </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H320" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" s="63" t="str">
         <f>IF(ISBLANK(B321),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B321))</f>
         <v/>
@@ -8731,8 +10021,12 @@
       <c r="E321" s="37"/>
       <c r="F321" s="40"/>
       <c r="G321" s="40"/>
-    </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H321" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" s="62" t="str">
         <f>IF(ISBLANK(B322),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B322))</f>
         <v/>
@@ -8743,8 +10037,12 @@
       <c r="E322" s="33"/>
       <c r="F322" s="39"/>
       <c r="G322" s="39"/>
-    </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H322" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" s="63" t="str">
         <f>IF(ISBLANK(B323),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B323))</f>
         <v/>
@@ -8755,8 +10053,12 @@
       <c r="E323" s="37"/>
       <c r="F323" s="40"/>
       <c r="G323" s="40"/>
-    </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H323" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" s="62" t="str">
         <f>IF(ISBLANK(B324),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B324))</f>
         <v/>
@@ -8767,8 +10069,12 @@
       <c r="E324" s="33"/>
       <c r="F324" s="39"/>
       <c r="G324" s="39"/>
-    </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H324" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" s="63" t="str">
         <f>IF(ISBLANK(B325),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B325))</f>
         <v/>
@@ -8779,8 +10085,12 @@
       <c r="E325" s="37"/>
       <c r="F325" s="40"/>
       <c r="G325" s="40"/>
-    </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H325" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" s="62" t="str">
         <f>IF(ISBLANK(B326),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B326))</f>
         <v/>
@@ -8791,8 +10101,12 @@
       <c r="E326" s="33"/>
       <c r="F326" s="39"/>
       <c r="G326" s="39"/>
-    </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H326" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" s="63" t="str">
         <f>IF(ISBLANK(B327),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B327))</f>
         <v/>
@@ -8803,8 +10117,12 @@
       <c r="E327" s="37"/>
       <c r="F327" s="40"/>
       <c r="G327" s="40"/>
-    </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H327" t="str">
+        <f t="shared" ref="H327:H390" si="5">IF(OR(ISBLANK(B327),B327=""),"",IF(B327=B326,"",INT(((SUMIF(B:B,B327,C:C)*60)+SUMIF(B:B,B327,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B327,C:C)*60)+SUMIF(B:B,B327,D:D),60),"00")&amp;" min"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" s="62" t="str">
         <f>IF(ISBLANK(B328),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B328))</f>
         <v/>
@@ -8815,8 +10133,12 @@
       <c r="E328" s="33"/>
       <c r="F328" s="39"/>
       <c r="G328" s="39"/>
-    </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H328" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" s="63" t="str">
         <f>IF(ISBLANK(B329),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B329))</f>
         <v/>
@@ -8827,8 +10149,12 @@
       <c r="E329" s="37"/>
       <c r="F329" s="40"/>
       <c r="G329" s="40"/>
-    </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H329" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" s="62" t="str">
         <f>IF(ISBLANK(B330),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B330))</f>
         <v/>
@@ -8839,8 +10165,12 @@
       <c r="E330" s="33"/>
       <c r="F330" s="39"/>
       <c r="G330" s="39"/>
-    </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H330" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" s="63" t="str">
         <f>IF(ISBLANK(B331),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B331))</f>
         <v/>
@@ -8851,8 +10181,12 @@
       <c r="E331" s="37"/>
       <c r="F331" s="40"/>
       <c r="G331" s="40"/>
-    </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H331" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" s="62" t="str">
         <f>IF(ISBLANK(B332),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B332))</f>
         <v/>
@@ -8863,8 +10197,12 @@
       <c r="E332" s="33"/>
       <c r="F332" s="39"/>
       <c r="G332" s="39"/>
-    </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H332" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" s="63" t="str">
         <f>IF(ISBLANK(B333),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B333))</f>
         <v/>
@@ -8875,8 +10213,12 @@
       <c r="E333" s="37"/>
       <c r="F333" s="40"/>
       <c r="G333" s="40"/>
-    </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H333" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" s="62" t="str">
         <f>IF(ISBLANK(B334),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B334))</f>
         <v/>
@@ -8887,8 +10229,12 @@
       <c r="E334" s="33"/>
       <c r="F334" s="39"/>
       <c r="G334" s="39"/>
-    </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H334" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" s="63" t="str">
         <f>IF(ISBLANK(B335),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B335))</f>
         <v/>
@@ -8899,8 +10245,12 @@
       <c r="E335" s="37"/>
       <c r="F335" s="40"/>
       <c r="G335" s="40"/>
-    </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H335" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" s="62" t="str">
         <f>IF(ISBLANK(B336),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B336))</f>
         <v/>
@@ -8911,8 +10261,12 @@
       <c r="E336" s="33"/>
       <c r="F336" s="39"/>
       <c r="G336" s="39"/>
-    </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H336" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" s="63" t="str">
         <f>IF(ISBLANK(B337),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B337))</f>
         <v/>
@@ -8923,8 +10277,12 @@
       <c r="E337" s="37"/>
       <c r="F337" s="40"/>
       <c r="G337" s="40"/>
-    </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H337" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" s="62" t="str">
         <f>IF(ISBLANK(B338),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B338))</f>
         <v/>
@@ -8935,8 +10293,12 @@
       <c r="E338" s="33"/>
       <c r="F338" s="39"/>
       <c r="G338" s="39"/>
-    </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H338" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" s="63" t="str">
         <f>IF(ISBLANK(B339),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B339))</f>
         <v/>
@@ -8947,8 +10309,12 @@
       <c r="E339" s="37"/>
       <c r="F339" s="40"/>
       <c r="G339" s="40"/>
-    </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H339" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" s="62" t="str">
         <f>IF(ISBLANK(B340),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B340))</f>
         <v/>
@@ -8959,8 +10325,12 @@
       <c r="E340" s="33"/>
       <c r="F340" s="39"/>
       <c r="G340" s="39"/>
-    </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H340" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" s="63" t="str">
         <f>IF(ISBLANK(B341),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B341))</f>
         <v/>
@@ -8971,8 +10341,12 @@
       <c r="E341" s="37"/>
       <c r="F341" s="40"/>
       <c r="G341" s="40"/>
-    </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H341" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" s="62" t="str">
         <f>IF(ISBLANK(B342),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B342))</f>
         <v/>
@@ -8983,8 +10357,12 @@
       <c r="E342" s="33"/>
       <c r="F342" s="39"/>
       <c r="G342" s="39"/>
-    </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H342" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" s="63" t="str">
         <f>IF(ISBLANK(B343),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B343))</f>
         <v/>
@@ -8995,8 +10373,12 @@
       <c r="E343" s="37"/>
       <c r="F343" s="40"/>
       <c r="G343" s="40"/>
-    </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H343" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" s="62" t="str">
         <f>IF(ISBLANK(B344),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B344))</f>
         <v/>
@@ -9007,8 +10389,12 @@
       <c r="E344" s="33"/>
       <c r="F344" s="39"/>
       <c r="G344" s="39"/>
-    </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H344" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" s="63" t="str">
         <f>IF(ISBLANK(B345),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B345))</f>
         <v/>
@@ -9019,8 +10405,12 @@
       <c r="E345" s="37"/>
       <c r="F345" s="40"/>
       <c r="G345" s="40"/>
-    </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H345" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" s="62" t="str">
         <f>IF(ISBLANK(B346),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B346))</f>
         <v/>
@@ -9031,8 +10421,12 @@
       <c r="E346" s="33"/>
       <c r="F346" s="39"/>
       <c r="G346" s="39"/>
-    </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H346" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" s="63" t="str">
         <f>IF(ISBLANK(B347),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B347))</f>
         <v/>
@@ -9043,8 +10437,12 @@
       <c r="E347" s="37"/>
       <c r="F347" s="40"/>
       <c r="G347" s="40"/>
-    </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H347" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" s="62" t="str">
         <f>IF(ISBLANK(B348),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B348))</f>
         <v/>
@@ -9055,8 +10453,12 @@
       <c r="E348" s="33"/>
       <c r="F348" s="39"/>
       <c r="G348" s="39"/>
-    </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H348" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" s="63" t="str">
         <f>IF(ISBLANK(B349),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B349))</f>
         <v/>
@@ -9067,8 +10469,12 @@
       <c r="E349" s="37"/>
       <c r="F349" s="40"/>
       <c r="G349" s="40"/>
-    </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H349" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" s="62" t="str">
         <f>IF(ISBLANK(B350),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B350))</f>
         <v/>
@@ -9079,8 +10485,12 @@
       <c r="E350" s="33"/>
       <c r="F350" s="39"/>
       <c r="G350" s="39"/>
-    </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H350" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" s="63" t="str">
         <f>IF(ISBLANK(B351),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B351))</f>
         <v/>
@@ -9091,8 +10501,12 @@
       <c r="E351" s="37"/>
       <c r="F351" s="40"/>
       <c r="G351" s="40"/>
-    </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H351" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" s="62" t="str">
         <f>IF(ISBLANK(B352),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B352))</f>
         <v/>
@@ -9103,8 +10517,12 @@
       <c r="E352" s="33"/>
       <c r="F352" s="39"/>
       <c r="G352" s="39"/>
-    </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H352" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" s="63" t="str">
         <f>IF(ISBLANK(B353),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B353))</f>
         <v/>
@@ -9115,8 +10533,12 @@
       <c r="E353" s="37"/>
       <c r="F353" s="40"/>
       <c r="G353" s="40"/>
-    </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H353" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" s="62" t="str">
         <f>IF(ISBLANK(B354),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B354))</f>
         <v/>
@@ -9127,8 +10549,12 @@
       <c r="E354" s="33"/>
       <c r="F354" s="39"/>
       <c r="G354" s="39"/>
-    </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H354" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" s="63" t="str">
         <f>IF(ISBLANK(B355),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B355))</f>
         <v/>
@@ -9139,8 +10565,12 @@
       <c r="E355" s="37"/>
       <c r="F355" s="40"/>
       <c r="G355" s="40"/>
-    </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H355" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" s="62" t="str">
         <f>IF(ISBLANK(B356),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B356))</f>
         <v/>
@@ -9151,8 +10581,12 @@
       <c r="E356" s="33"/>
       <c r="F356" s="39"/>
       <c r="G356" s="39"/>
-    </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H356" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" s="63" t="str">
         <f>IF(ISBLANK(B357),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B357))</f>
         <v/>
@@ -9163,8 +10597,12 @@
       <c r="E357" s="37"/>
       <c r="F357" s="40"/>
       <c r="G357" s="40"/>
-    </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H357" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" s="62" t="str">
         <f>IF(ISBLANK(B358),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B358))</f>
         <v/>
@@ -9175,8 +10613,12 @@
       <c r="E358" s="33"/>
       <c r="F358" s="39"/>
       <c r="G358" s="39"/>
-    </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H358" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" s="63" t="str">
         <f>IF(ISBLANK(B359),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B359))</f>
         <v/>
@@ -9187,8 +10629,12 @@
       <c r="E359" s="37"/>
       <c r="F359" s="40"/>
       <c r="G359" s="40"/>
-    </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H359" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" s="62" t="str">
         <f>IF(ISBLANK(B360),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B360))</f>
         <v/>
@@ -9199,8 +10645,12 @@
       <c r="E360" s="33"/>
       <c r="F360" s="39"/>
       <c r="G360" s="39"/>
-    </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H360" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" s="63" t="str">
         <f>IF(ISBLANK(B361),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B361))</f>
         <v/>
@@ -9211,8 +10661,12 @@
       <c r="E361" s="37"/>
       <c r="F361" s="40"/>
       <c r="G361" s="40"/>
-    </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H361" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" s="62" t="str">
         <f>IF(ISBLANK(B362),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B362))</f>
         <v/>
@@ -9223,8 +10677,12 @@
       <c r="E362" s="33"/>
       <c r="F362" s="39"/>
       <c r="G362" s="39"/>
-    </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H362" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" s="63" t="str">
         <f>IF(ISBLANK(B363),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B363))</f>
         <v/>
@@ -9235,8 +10693,12 @@
       <c r="E363" s="37"/>
       <c r="F363" s="40"/>
       <c r="G363" s="40"/>
-    </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H363" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" s="62" t="str">
         <f>IF(ISBLANK(B364),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B364))</f>
         <v/>
@@ -9247,8 +10709,12 @@
       <c r="E364" s="33"/>
       <c r="F364" s="39"/>
       <c r="G364" s="39"/>
-    </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H364" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" s="63" t="str">
         <f>IF(ISBLANK(B365),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B365))</f>
         <v/>
@@ -9259,8 +10725,12 @@
       <c r="E365" s="37"/>
       <c r="F365" s="40"/>
       <c r="G365" s="40"/>
-    </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H365" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" s="62" t="str">
         <f>IF(ISBLANK(B366),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B366))</f>
         <v/>
@@ -9271,8 +10741,12 @@
       <c r="E366" s="33"/>
       <c r="F366" s="39"/>
       <c r="G366" s="39"/>
-    </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H366" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" s="63" t="str">
         <f>IF(ISBLANK(B367),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B367))</f>
         <v/>
@@ -9283,8 +10757,12 @@
       <c r="E367" s="37"/>
       <c r="F367" s="40"/>
       <c r="G367" s="40"/>
-    </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H367" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" s="62" t="str">
         <f>IF(ISBLANK(B368),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B368))</f>
         <v/>
@@ -9295,8 +10773,12 @@
       <c r="E368" s="33"/>
       <c r="F368" s="39"/>
       <c r="G368" s="39"/>
-    </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H368" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" s="63" t="str">
         <f>IF(ISBLANK(B369),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B369))</f>
         <v/>
@@ -9307,8 +10789,12 @@
       <c r="E369" s="37"/>
       <c r="F369" s="40"/>
       <c r="G369" s="40"/>
-    </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H369" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" s="62" t="str">
         <f>IF(ISBLANK(B370),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B370))</f>
         <v/>
@@ -9319,8 +10805,12 @@
       <c r="E370" s="33"/>
       <c r="F370" s="39"/>
       <c r="G370" s="39"/>
-    </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H370" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" s="63" t="str">
         <f>IF(ISBLANK(B371),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B371))</f>
         <v/>
@@ -9331,8 +10821,12 @@
       <c r="E371" s="37"/>
       <c r="F371" s="40"/>
       <c r="G371" s="40"/>
-    </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H371" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" s="62" t="str">
         <f>IF(ISBLANK(B372),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B372))</f>
         <v/>
@@ -9343,8 +10837,12 @@
       <c r="E372" s="33"/>
       <c r="F372" s="39"/>
       <c r="G372" s="39"/>
-    </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H372" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" s="63" t="str">
         <f>IF(ISBLANK(B373),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B373))</f>
         <v/>
@@ -9355,8 +10853,12 @@
       <c r="E373" s="37"/>
       <c r="F373" s="40"/>
       <c r="G373" s="40"/>
-    </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H373" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" s="62" t="str">
         <f>IF(ISBLANK(B374),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B374))</f>
         <v/>
@@ -9367,8 +10869,12 @@
       <c r="E374" s="33"/>
       <c r="F374" s="39"/>
       <c r="G374" s="39"/>
-    </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H374" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" s="63" t="str">
         <f>IF(ISBLANK(B375),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B375))</f>
         <v/>
@@ -9379,8 +10885,12 @@
       <c r="E375" s="37"/>
       <c r="F375" s="40"/>
       <c r="G375" s="40"/>
-    </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H375" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" s="62" t="str">
         <f>IF(ISBLANK(B376),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B376))</f>
         <v/>
@@ -9391,8 +10901,12 @@
       <c r="E376" s="33"/>
       <c r="F376" s="39"/>
       <c r="G376" s="39"/>
-    </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H376" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" s="63" t="str">
         <f>IF(ISBLANK(B377),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B377))</f>
         <v/>
@@ -9403,8 +10917,12 @@
       <c r="E377" s="37"/>
       <c r="F377" s="40"/>
       <c r="G377" s="40"/>
-    </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H377" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" s="62" t="str">
         <f>IF(ISBLANK(B378),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B378))</f>
         <v/>
@@ -9415,8 +10933,12 @@
       <c r="E378" s="33"/>
       <c r="F378" s="39"/>
       <c r="G378" s="39"/>
-    </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H378" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" s="63" t="str">
         <f>IF(ISBLANK(B379),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B379))</f>
         <v/>
@@ -9427,8 +10949,12 @@
       <c r="E379" s="37"/>
       <c r="F379" s="40"/>
       <c r="G379" s="40"/>
-    </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H379" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" s="62" t="str">
         <f>IF(ISBLANK(B380),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B380))</f>
         <v/>
@@ -9439,8 +10965,12 @@
       <c r="E380" s="33"/>
       <c r="F380" s="39"/>
       <c r="G380" s="39"/>
-    </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H380" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" s="63" t="str">
         <f>IF(ISBLANK(B381),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B381))</f>
         <v/>
@@ -9451,8 +10981,12 @@
       <c r="E381" s="37"/>
       <c r="F381" s="40"/>
       <c r="G381" s="40"/>
-    </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H381" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" s="62" t="str">
         <f>IF(ISBLANK(B382),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B382))</f>
         <v/>
@@ -9463,8 +10997,12 @@
       <c r="E382" s="33"/>
       <c r="F382" s="39"/>
       <c r="G382" s="39"/>
-    </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H382" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" s="63" t="str">
         <f>IF(ISBLANK(B383),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B383))</f>
         <v/>
@@ -9475,8 +11013,12 @@
       <c r="E383" s="37"/>
       <c r="F383" s="40"/>
       <c r="G383" s="40"/>
-    </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H383" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" s="62" t="str">
         <f>IF(ISBLANK(B384),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B384))</f>
         <v/>
@@ -9487,8 +11029,12 @@
       <c r="E384" s="33"/>
       <c r="F384" s="39"/>
       <c r="G384" s="39"/>
-    </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H384" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" s="63" t="str">
         <f>IF(ISBLANK(B385),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B385))</f>
         <v/>
@@ -9499,8 +11045,12 @@
       <c r="E385" s="37"/>
       <c r="F385" s="40"/>
       <c r="G385" s="40"/>
-    </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H385" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" s="62" t="str">
         <f>IF(ISBLANK(B386),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B386))</f>
         <v/>
@@ -9511,8 +11061,12 @@
       <c r="E386" s="33"/>
       <c r="F386" s="39"/>
       <c r="G386" s="39"/>
-    </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H386" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" s="63" t="str">
         <f>IF(ISBLANK(B387),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B387))</f>
         <v/>
@@ -9523,8 +11077,12 @@
       <c r="E387" s="37"/>
       <c r="F387" s="40"/>
       <c r="G387" s="40"/>
-    </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H387" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" s="62" t="str">
         <f>IF(ISBLANK(B388),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B388))</f>
         <v/>
@@ -9535,8 +11093,12 @@
       <c r="E388" s="33"/>
       <c r="F388" s="39"/>
       <c r="G388" s="39"/>
-    </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H388" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" s="63" t="str">
         <f>IF(ISBLANK(B389),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B389))</f>
         <v/>
@@ -9547,8 +11109,12 @@
       <c r="E389" s="37"/>
       <c r="F389" s="40"/>
       <c r="G389" s="40"/>
-    </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H389" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" s="62" t="str">
         <f>IF(ISBLANK(B390),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B390))</f>
         <v/>
@@ -9559,8 +11125,12 @@
       <c r="E390" s="33"/>
       <c r="F390" s="39"/>
       <c r="G390" s="39"/>
-    </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H390" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" s="63" t="str">
         <f>IF(ISBLANK(B391),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B391))</f>
         <v/>
@@ -9571,8 +11141,12 @@
       <c r="E391" s="37"/>
       <c r="F391" s="40"/>
       <c r="G391" s="40"/>
-    </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H391" t="str">
+        <f t="shared" ref="H391:H454" si="6">IF(OR(ISBLANK(B391),B391=""),"",IF(B391=B390,"",INT(((SUMIF(B:B,B391,C:C)*60)+SUMIF(B:B,B391,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B391,C:C)*60)+SUMIF(B:B,B391,D:D),60),"00")&amp;" min"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" s="62" t="str">
         <f>IF(ISBLANK(B392),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B392))</f>
         <v/>
@@ -9583,8 +11157,12 @@
       <c r="E392" s="33"/>
       <c r="F392" s="39"/>
       <c r="G392" s="39"/>
-    </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H392" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" s="63" t="str">
         <f>IF(ISBLANK(B393),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B393))</f>
         <v/>
@@ -9595,8 +11173,12 @@
       <c r="E393" s="37"/>
       <c r="F393" s="40"/>
       <c r="G393" s="40"/>
-    </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H393" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" s="62" t="str">
         <f>IF(ISBLANK(B394),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B394))</f>
         <v/>
@@ -9607,8 +11189,12 @@
       <c r="E394" s="33"/>
       <c r="F394" s="39"/>
       <c r="G394" s="39"/>
-    </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H394" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" s="63" t="str">
         <f>IF(ISBLANK(B395),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B395))</f>
         <v/>
@@ -9619,8 +11205,12 @@
       <c r="E395" s="37"/>
       <c r="F395" s="40"/>
       <c r="G395" s="40"/>
-    </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H395" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" s="62" t="str">
         <f>IF(ISBLANK(B396),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B396))</f>
         <v/>
@@ -9631,8 +11221,12 @@
       <c r="E396" s="33"/>
       <c r="F396" s="39"/>
       <c r="G396" s="39"/>
-    </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H396" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" s="63" t="str">
         <f>IF(ISBLANK(B397),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B397))</f>
         <v/>
@@ -9643,8 +11237,12 @@
       <c r="E397" s="37"/>
       <c r="F397" s="40"/>
       <c r="G397" s="40"/>
-    </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H397" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" s="62" t="str">
         <f>IF(ISBLANK(B398),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B398))</f>
         <v/>
@@ -9655,8 +11253,12 @@
       <c r="E398" s="33"/>
       <c r="F398" s="39"/>
       <c r="G398" s="39"/>
-    </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H398" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" s="63" t="str">
         <f>IF(ISBLANK(B399),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B399))</f>
         <v/>
@@ -9667,8 +11269,12 @@
       <c r="E399" s="37"/>
       <c r="F399" s="40"/>
       <c r="G399" s="40"/>
-    </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H399" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" s="62" t="str">
         <f>IF(ISBLANK(B400),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B400))</f>
         <v/>
@@ -9679,8 +11285,12 @@
       <c r="E400" s="33"/>
       <c r="F400" s="39"/>
       <c r="G400" s="39"/>
-    </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H400" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" s="63" t="str">
         <f>IF(ISBLANK(B401),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B401))</f>
         <v/>
@@ -9691,8 +11301,12 @@
       <c r="E401" s="37"/>
       <c r="F401" s="40"/>
       <c r="G401" s="40"/>
-    </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H401" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" s="62" t="str">
         <f>IF(ISBLANK(B402),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B402))</f>
         <v/>
@@ -9703,8 +11317,12 @@
       <c r="E402" s="33"/>
       <c r="F402" s="39"/>
       <c r="G402" s="39"/>
-    </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H402" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" s="63" t="str">
         <f>IF(ISBLANK(B403),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B403))</f>
         <v/>
@@ -9715,8 +11333,12 @@
       <c r="E403" s="37"/>
       <c r="F403" s="40"/>
       <c r="G403" s="40"/>
-    </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H403" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" s="62" t="str">
         <f>IF(ISBLANK(B404),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B404))</f>
         <v/>
@@ -9727,8 +11349,12 @@
       <c r="E404" s="33"/>
       <c r="F404" s="39"/>
       <c r="G404" s="39"/>
-    </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H404" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" s="63" t="str">
         <f>IF(ISBLANK(B405),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B405))</f>
         <v/>
@@ -9739,8 +11365,12 @@
       <c r="E405" s="37"/>
       <c r="F405" s="40"/>
       <c r="G405" s="40"/>
-    </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H405" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" s="62" t="str">
         <f>IF(ISBLANK(B406),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B406))</f>
         <v/>
@@ -9751,8 +11381,12 @@
       <c r="E406" s="33"/>
       <c r="F406" s="39"/>
       <c r="G406" s="39"/>
-    </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H406" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" s="63" t="str">
         <f>IF(ISBLANK(B407),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B407))</f>
         <v/>
@@ -9763,8 +11397,12 @@
       <c r="E407" s="37"/>
       <c r="F407" s="40"/>
       <c r="G407" s="40"/>
-    </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H407" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" s="62" t="str">
         <f>IF(ISBLANK(B408),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B408))</f>
         <v/>
@@ -9775,8 +11413,12 @@
       <c r="E408" s="33"/>
       <c r="F408" s="39"/>
       <c r="G408" s="39"/>
-    </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H408" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" s="63" t="str">
         <f>IF(ISBLANK(B409),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B409))</f>
         <v/>
@@ -9787,8 +11429,12 @@
       <c r="E409" s="37"/>
       <c r="F409" s="40"/>
       <c r="G409" s="40"/>
-    </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H409" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" s="62" t="str">
         <f>IF(ISBLANK(B410),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B410))</f>
         <v/>
@@ -9799,8 +11445,12 @@
       <c r="E410" s="33"/>
       <c r="F410" s="39"/>
       <c r="G410" s="39"/>
-    </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H410" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" s="63" t="str">
         <f>IF(ISBLANK(B411),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B411))</f>
         <v/>
@@ -9811,8 +11461,12 @@
       <c r="E411" s="37"/>
       <c r="F411" s="40"/>
       <c r="G411" s="40"/>
-    </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H411" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" s="62" t="str">
         <f>IF(ISBLANK(B412),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B412))</f>
         <v/>
@@ -9823,8 +11477,12 @@
       <c r="E412" s="33"/>
       <c r="F412" s="39"/>
       <c r="G412" s="39"/>
-    </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H412" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" s="63" t="str">
         <f>IF(ISBLANK(B413),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B413))</f>
         <v/>
@@ -9835,8 +11493,12 @@
       <c r="E413" s="37"/>
       <c r="F413" s="40"/>
       <c r="G413" s="40"/>
-    </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H413" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" s="62" t="str">
         <f>IF(ISBLANK(B414),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B414))</f>
         <v/>
@@ -9847,8 +11509,12 @@
       <c r="E414" s="33"/>
       <c r="F414" s="39"/>
       <c r="G414" s="39"/>
-    </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H414" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" s="63" t="str">
         <f>IF(ISBLANK(B415),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B415))</f>
         <v/>
@@ -9859,8 +11525,12 @@
       <c r="E415" s="37"/>
       <c r="F415" s="40"/>
       <c r="G415" s="40"/>
-    </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H415" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" s="62" t="str">
         <f>IF(ISBLANK(B416),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B416))</f>
         <v/>
@@ -9871,8 +11541,12 @@
       <c r="E416" s="33"/>
       <c r="F416" s="39"/>
       <c r="G416" s="39"/>
-    </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H416" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" s="63" t="str">
         <f>IF(ISBLANK(B417),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B417))</f>
         <v/>
@@ -9883,8 +11557,12 @@
       <c r="E417" s="37"/>
       <c r="F417" s="40"/>
       <c r="G417" s="40"/>
-    </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H417" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A418" s="62" t="str">
         <f>IF(ISBLANK(B418),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B418))</f>
         <v/>
@@ -9895,8 +11573,12 @@
       <c r="E418" s="33"/>
       <c r="F418" s="39"/>
       <c r="G418" s="39"/>
-    </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H418" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" s="63" t="str">
         <f>IF(ISBLANK(B419),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B419))</f>
         <v/>
@@ -9907,8 +11589,12 @@
       <c r="E419" s="37"/>
       <c r="F419" s="40"/>
       <c r="G419" s="40"/>
-    </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H419" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" s="62" t="str">
         <f>IF(ISBLANK(B420),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B420))</f>
         <v/>
@@ -9919,8 +11605,12 @@
       <c r="E420" s="33"/>
       <c r="F420" s="39"/>
       <c r="G420" s="39"/>
-    </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H420" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" s="63" t="str">
         <f>IF(ISBLANK(B421),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B421))</f>
         <v/>
@@ -9931,8 +11621,12 @@
       <c r="E421" s="37"/>
       <c r="F421" s="40"/>
       <c r="G421" s="40"/>
-    </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H421" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" s="62" t="str">
         <f>IF(ISBLANK(B422),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B422))</f>
         <v/>
@@ -9943,8 +11637,12 @@
       <c r="E422" s="33"/>
       <c r="F422" s="39"/>
       <c r="G422" s="39"/>
-    </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H422" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" s="63" t="str">
         <f>IF(ISBLANK(B423),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B423))</f>
         <v/>
@@ -9955,8 +11653,12 @@
       <c r="E423" s="37"/>
       <c r="F423" s="40"/>
       <c r="G423" s="40"/>
-    </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H423" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" s="62" t="str">
         <f>IF(ISBLANK(B424),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B424))</f>
         <v/>
@@ -9967,8 +11669,12 @@
       <c r="E424" s="33"/>
       <c r="F424" s="39"/>
       <c r="G424" s="39"/>
-    </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H424" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" s="63" t="str">
         <f>IF(ISBLANK(B425),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B425))</f>
         <v/>
@@ -9979,8 +11685,12 @@
       <c r="E425" s="37"/>
       <c r="F425" s="40"/>
       <c r="G425" s="40"/>
-    </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H425" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" s="62" t="str">
         <f>IF(ISBLANK(B426),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B426))</f>
         <v/>
@@ -9991,8 +11701,12 @@
       <c r="E426" s="33"/>
       <c r="F426" s="39"/>
       <c r="G426" s="39"/>
-    </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H426" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" s="63" t="str">
         <f>IF(ISBLANK(B427),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B427))</f>
         <v/>
@@ -10003,8 +11717,12 @@
       <c r="E427" s="37"/>
       <c r="F427" s="40"/>
       <c r="G427" s="40"/>
-    </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H427" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" s="62" t="str">
         <f>IF(ISBLANK(B428),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B428))</f>
         <v/>
@@ -10015,8 +11733,12 @@
       <c r="E428" s="33"/>
       <c r="F428" s="39"/>
       <c r="G428" s="39"/>
-    </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H428" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" s="63" t="str">
         <f>IF(ISBLANK(B429),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B429))</f>
         <v/>
@@ -10027,8 +11749,12 @@
       <c r="E429" s="37"/>
       <c r="F429" s="40"/>
       <c r="G429" s="40"/>
-    </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H429" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" s="62" t="str">
         <f>IF(ISBLANK(B430),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B430))</f>
         <v/>
@@ -10039,8 +11765,12 @@
       <c r="E430" s="33"/>
       <c r="F430" s="39"/>
       <c r="G430" s="39"/>
-    </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H430" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" s="63" t="str">
         <f>IF(ISBLANK(B431),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B431))</f>
         <v/>
@@ -10051,8 +11781,12 @@
       <c r="E431" s="37"/>
       <c r="F431" s="40"/>
       <c r="G431" s="40"/>
-    </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H431" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" s="62" t="str">
         <f>IF(ISBLANK(B432),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B432))</f>
         <v/>
@@ -10063,8 +11797,12 @@
       <c r="E432" s="33"/>
       <c r="F432" s="39"/>
       <c r="G432" s="39"/>
-    </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H432" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A433" s="63" t="str">
         <f>IF(ISBLANK(B433),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B433))</f>
         <v/>
@@ -10075,8 +11813,12 @@
       <c r="E433" s="37"/>
       <c r="F433" s="40"/>
       <c r="G433" s="40"/>
-    </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H433" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A434" s="62" t="str">
         <f>IF(ISBLANK(B434),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B434))</f>
         <v/>
@@ -10087,8 +11829,12 @@
       <c r="E434" s="33"/>
       <c r="F434" s="39"/>
       <c r="G434" s="39"/>
-    </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H434" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" s="63" t="str">
         <f>IF(ISBLANK(B435),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B435))</f>
         <v/>
@@ -10099,8 +11845,12 @@
       <c r="E435" s="37"/>
       <c r="F435" s="40"/>
       <c r="G435" s="40"/>
-    </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H435" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" s="62" t="str">
         <f>IF(ISBLANK(B436),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B436))</f>
         <v/>
@@ -10111,8 +11861,12 @@
       <c r="E436" s="33"/>
       <c r="F436" s="39"/>
       <c r="G436" s="39"/>
-    </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H436" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A437" s="63" t="str">
         <f>IF(ISBLANK(B437),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B437))</f>
         <v/>
@@ -10123,8 +11877,12 @@
       <c r="E437" s="37"/>
       <c r="F437" s="40"/>
       <c r="G437" s="40"/>
-    </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H437" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A438" s="62" t="str">
         <f>IF(ISBLANK(B438),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B438))</f>
         <v/>
@@ -10135,8 +11893,12 @@
       <c r="E438" s="33"/>
       <c r="F438" s="39"/>
       <c r="G438" s="39"/>
-    </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H438" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" s="63" t="str">
         <f>IF(ISBLANK(B439),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B439))</f>
         <v/>
@@ -10147,8 +11909,12 @@
       <c r="E439" s="37"/>
       <c r="F439" s="40"/>
       <c r="G439" s="40"/>
-    </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H439" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" s="62" t="str">
         <f>IF(ISBLANK(B440),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B440))</f>
         <v/>
@@ -10159,8 +11925,12 @@
       <c r="E440" s="33"/>
       <c r="F440" s="39"/>
       <c r="G440" s="39"/>
-    </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H440" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" s="63" t="str">
         <f>IF(ISBLANK(B441),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B441))</f>
         <v/>
@@ -10171,8 +11941,12 @@
       <c r="E441" s="37"/>
       <c r="F441" s="40"/>
       <c r="G441" s="40"/>
-    </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H441" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" s="62" t="str">
         <f>IF(ISBLANK(B442),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B442))</f>
         <v/>
@@ -10183,8 +11957,12 @@
       <c r="E442" s="33"/>
       <c r="F442" s="39"/>
       <c r="G442" s="39"/>
-    </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H442" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" s="63" t="str">
         <f>IF(ISBLANK(B443),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B443))</f>
         <v/>
@@ -10195,8 +11973,12 @@
       <c r="E443" s="37"/>
       <c r="F443" s="40"/>
       <c r="G443" s="40"/>
-    </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H443" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" s="62" t="str">
         <f>IF(ISBLANK(B444),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B444))</f>
         <v/>
@@ -10207,8 +11989,12 @@
       <c r="E444" s="33"/>
       <c r="F444" s="39"/>
       <c r="G444" s="39"/>
-    </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H444" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" s="63" t="str">
         <f>IF(ISBLANK(B445),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B445))</f>
         <v/>
@@ -10219,8 +12005,12 @@
       <c r="E445" s="37"/>
       <c r="F445" s="40"/>
       <c r="G445" s="40"/>
-    </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H445" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A446" s="62" t="str">
         <f>IF(ISBLANK(B446),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B446))</f>
         <v/>
@@ -10231,8 +12021,12 @@
       <c r="E446" s="33"/>
       <c r="F446" s="39"/>
       <c r="G446" s="39"/>
-    </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H446" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A447" s="63" t="str">
         <f>IF(ISBLANK(B447),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B447))</f>
         <v/>
@@ -10243,8 +12037,12 @@
       <c r="E447" s="37"/>
       <c r="F447" s="40"/>
       <c r="G447" s="40"/>
-    </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H447" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" s="62" t="str">
         <f>IF(ISBLANK(B448),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B448))</f>
         <v/>
@@ -10255,8 +12053,12 @@
       <c r="E448" s="33"/>
       <c r="F448" s="39"/>
       <c r="G448" s="39"/>
-    </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H448" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" s="63" t="str">
         <f>IF(ISBLANK(B449),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B449))</f>
         <v/>
@@ -10267,8 +12069,12 @@
       <c r="E449" s="37"/>
       <c r="F449" s="40"/>
       <c r="G449" s="40"/>
-    </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H449" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" s="62" t="str">
         <f>IF(ISBLANK(B450),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B450))</f>
         <v/>
@@ -10279,8 +12085,12 @@
       <c r="E450" s="33"/>
       <c r="F450" s="39"/>
       <c r="G450" s="39"/>
-    </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H450" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" s="63" t="str">
         <f>IF(ISBLANK(B451),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B451))</f>
         <v/>
@@ -10291,8 +12101,12 @@
       <c r="E451" s="37"/>
       <c r="F451" s="40"/>
       <c r="G451" s="40"/>
-    </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H451" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" s="62" t="str">
         <f>IF(ISBLANK(B452),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B452))</f>
         <v/>
@@ -10303,8 +12117,12 @@
       <c r="E452" s="33"/>
       <c r="F452" s="39"/>
       <c r="G452" s="39"/>
-    </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H452" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" s="63" t="str">
         <f>IF(ISBLANK(B453),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B453))</f>
         <v/>
@@ -10315,8 +12133,12 @@
       <c r="E453" s="37"/>
       <c r="F453" s="40"/>
       <c r="G453" s="40"/>
-    </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H453" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" s="62" t="str">
         <f>IF(ISBLANK(B454),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B454))</f>
         <v/>
@@ -10327,8 +12149,12 @@
       <c r="E454" s="33"/>
       <c r="F454" s="39"/>
       <c r="G454" s="39"/>
-    </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H454" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" s="63" t="str">
         <f>IF(ISBLANK(B455),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B455))</f>
         <v/>
@@ -10339,8 +12165,12 @@
       <c r="E455" s="37"/>
       <c r="F455" s="40"/>
       <c r="G455" s="40"/>
-    </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H455" t="str">
+        <f t="shared" ref="H455:H518" si="7">IF(OR(ISBLANK(B455),B455=""),"",IF(B455=B454,"",INT(((SUMIF(B:B,B455,C:C)*60)+SUMIF(B:B,B455,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B455,C:C)*60)+SUMIF(B:B,B455,D:D),60),"00")&amp;" min"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" s="62" t="str">
         <f>IF(ISBLANK(B456),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B456))</f>
         <v/>
@@ -10351,8 +12181,12 @@
       <c r="E456" s="33"/>
       <c r="F456" s="39"/>
       <c r="G456" s="39"/>
-    </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H456" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" s="63" t="str">
         <f>IF(ISBLANK(B457),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B457))</f>
         <v/>
@@ -10363,8 +12197,12 @@
       <c r="E457" s="37"/>
       <c r="F457" s="40"/>
       <c r="G457" s="40"/>
-    </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H457" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" s="62" t="str">
         <f>IF(ISBLANK(B458),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B458))</f>
         <v/>
@@ -10375,8 +12213,12 @@
       <c r="E458" s="33"/>
       <c r="F458" s="39"/>
       <c r="G458" s="39"/>
-    </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H458" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" s="63" t="str">
         <f>IF(ISBLANK(B459),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B459))</f>
         <v/>
@@ -10387,8 +12229,12 @@
       <c r="E459" s="37"/>
       <c r="F459" s="40"/>
       <c r="G459" s="40"/>
-    </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H459" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" s="62" t="str">
         <f>IF(ISBLANK(B460),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B460))</f>
         <v/>
@@ -10399,8 +12245,12 @@
       <c r="E460" s="33"/>
       <c r="F460" s="39"/>
       <c r="G460" s="39"/>
-    </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H460" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" s="63" t="str">
         <f>IF(ISBLANK(B461),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B461))</f>
         <v/>
@@ -10411,8 +12261,12 @@
       <c r="E461" s="37"/>
       <c r="F461" s="40"/>
       <c r="G461" s="40"/>
-    </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H461" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" s="62" t="str">
         <f>IF(ISBLANK(B462),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B462))</f>
         <v/>
@@ -10423,8 +12277,12 @@
       <c r="E462" s="33"/>
       <c r="F462" s="39"/>
       <c r="G462" s="39"/>
-    </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H462" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" s="63" t="str">
         <f>IF(ISBLANK(B463),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B463))</f>
         <v/>
@@ -10435,8 +12293,12 @@
       <c r="E463" s="37"/>
       <c r="F463" s="40"/>
       <c r="G463" s="40"/>
-    </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H463" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" s="62" t="str">
         <f>IF(ISBLANK(B464),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B464))</f>
         <v/>
@@ -10447,8 +12309,12 @@
       <c r="E464" s="33"/>
       <c r="F464" s="39"/>
       <c r="G464" s="39"/>
-    </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H464" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" s="63" t="str">
         <f>IF(ISBLANK(B465),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B465))</f>
         <v/>
@@ -10459,8 +12325,12 @@
       <c r="E465" s="37"/>
       <c r="F465" s="40"/>
       <c r="G465" s="40"/>
-    </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H465" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" s="62" t="str">
         <f>IF(ISBLANK(B466),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B466))</f>
         <v/>
@@ -10471,8 +12341,12 @@
       <c r="E466" s="33"/>
       <c r="F466" s="39"/>
       <c r="G466" s="39"/>
-    </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H466" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" s="63" t="str">
         <f>IF(ISBLANK(B467),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B467))</f>
         <v/>
@@ -10483,8 +12357,12 @@
       <c r="E467" s="37"/>
       <c r="F467" s="40"/>
       <c r="G467" s="40"/>
-    </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H467" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" s="62" t="str">
         <f>IF(ISBLANK(B468),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B468))</f>
         <v/>
@@ -10495,8 +12373,12 @@
       <c r="E468" s="33"/>
       <c r="F468" s="39"/>
       <c r="G468" s="39"/>
-    </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H468" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" s="63" t="str">
         <f>IF(ISBLANK(B469),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B469))</f>
         <v/>
@@ -10507,8 +12389,12 @@
       <c r="E469" s="37"/>
       <c r="F469" s="40"/>
       <c r="G469" s="40"/>
-    </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H469" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" s="62" t="str">
         <f>IF(ISBLANK(B470),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B470))</f>
         <v/>
@@ -10519,8 +12405,12 @@
       <c r="E470" s="33"/>
       <c r="F470" s="39"/>
       <c r="G470" s="39"/>
-    </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H470" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" s="63" t="str">
         <f>IF(ISBLANK(B471),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B471))</f>
         <v/>
@@ -10531,8 +12421,12 @@
       <c r="E471" s="37"/>
       <c r="F471" s="40"/>
       <c r="G471" s="40"/>
-    </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H471" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" s="62" t="str">
         <f>IF(ISBLANK(B472),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B472))</f>
         <v/>
@@ -10543,8 +12437,12 @@
       <c r="E472" s="33"/>
       <c r="F472" s="39"/>
       <c r="G472" s="39"/>
-    </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H472" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" s="63" t="str">
         <f>IF(ISBLANK(B473),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B473))</f>
         <v/>
@@ -10555,8 +12453,12 @@
       <c r="E473" s="37"/>
       <c r="F473" s="40"/>
       <c r="G473" s="40"/>
-    </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H473" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A474" s="62" t="str">
         <f>IF(ISBLANK(B474),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B474))</f>
         <v/>
@@ -10567,8 +12469,12 @@
       <c r="E474" s="33"/>
       <c r="F474" s="39"/>
       <c r="G474" s="39"/>
-    </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H474" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A475" s="63" t="str">
         <f>IF(ISBLANK(B475),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B475))</f>
         <v/>
@@ -10579,8 +12485,12 @@
       <c r="E475" s="37"/>
       <c r="F475" s="40"/>
       <c r="G475" s="40"/>
-    </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H475" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" s="62" t="str">
         <f>IF(ISBLANK(B476),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B476))</f>
         <v/>
@@ -10591,8 +12501,12 @@
       <c r="E476" s="33"/>
       <c r="F476" s="39"/>
       <c r="G476" s="39"/>
-    </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H476" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A477" s="63" t="str">
         <f>IF(ISBLANK(B477),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B477))</f>
         <v/>
@@ -10603,8 +12517,12 @@
       <c r="E477" s="37"/>
       <c r="F477" s="40"/>
       <c r="G477" s="40"/>
-    </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H477" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" s="62" t="str">
         <f>IF(ISBLANK(B478),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B478))</f>
         <v/>
@@ -10615,8 +12533,12 @@
       <c r="E478" s="33"/>
       <c r="F478" s="39"/>
       <c r="G478" s="39"/>
-    </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H478" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" s="63" t="str">
         <f>IF(ISBLANK(B479),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B479))</f>
         <v/>
@@ -10627,8 +12549,12 @@
       <c r="E479" s="37"/>
       <c r="F479" s="40"/>
       <c r="G479" s="40"/>
-    </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H479" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" s="62" t="str">
         <f>IF(ISBLANK(B480),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B480))</f>
         <v/>
@@ -10639,8 +12565,12 @@
       <c r="E480" s="33"/>
       <c r="F480" s="39"/>
       <c r="G480" s="39"/>
-    </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H480" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" s="63" t="str">
         <f>IF(ISBLANK(B481),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B481))</f>
         <v/>
@@ -10651,8 +12581,12 @@
       <c r="E481" s="37"/>
       <c r="F481" s="40"/>
       <c r="G481" s="40"/>
-    </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H481" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" s="62" t="str">
         <f>IF(ISBLANK(B482),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B482))</f>
         <v/>
@@ -10663,8 +12597,12 @@
       <c r="E482" s="33"/>
       <c r="F482" s="39"/>
       <c r="G482" s="39"/>
-    </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H482" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" s="63" t="str">
         <f>IF(ISBLANK(B483),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B483))</f>
         <v/>
@@ -10675,8 +12613,12 @@
       <c r="E483" s="37"/>
       <c r="F483" s="40"/>
       <c r="G483" s="40"/>
-    </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H483" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" s="62" t="str">
         <f>IF(ISBLANK(B484),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B484))</f>
         <v/>
@@ -10687,8 +12629,12 @@
       <c r="E484" s="33"/>
       <c r="F484" s="39"/>
       <c r="G484" s="39"/>
-    </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H484" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" s="63" t="str">
         <f>IF(ISBLANK(B485),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B485))</f>
         <v/>
@@ -10699,8 +12645,12 @@
       <c r="E485" s="37"/>
       <c r="F485" s="40"/>
       <c r="G485" s="40"/>
-    </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H485" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" s="62" t="str">
         <f>IF(ISBLANK(B486),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B486))</f>
         <v/>
@@ -10711,8 +12661,12 @@
       <c r="E486" s="33"/>
       <c r="F486" s="39"/>
       <c r="G486" s="39"/>
-    </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H486" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" s="63" t="str">
         <f>IF(ISBLANK(B487),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B487))</f>
         <v/>
@@ -10723,8 +12677,12 @@
       <c r="E487" s="37"/>
       <c r="F487" s="40"/>
       <c r="G487" s="40"/>
-    </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H487" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" s="62" t="str">
         <f>IF(ISBLANK(B488),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B488))</f>
         <v/>
@@ -10735,8 +12693,12 @@
       <c r="E488" s="33"/>
       <c r="F488" s="39"/>
       <c r="G488" s="39"/>
-    </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H488" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" s="63" t="str">
         <f>IF(ISBLANK(B489),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B489))</f>
         <v/>
@@ -10747,8 +12709,12 @@
       <c r="E489" s="37"/>
       <c r="F489" s="40"/>
       <c r="G489" s="40"/>
-    </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H489" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" s="62" t="str">
         <f>IF(ISBLANK(B490),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B490))</f>
         <v/>
@@ -10759,8 +12725,12 @@
       <c r="E490" s="33"/>
       <c r="F490" s="39"/>
       <c r="G490" s="39"/>
-    </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H490" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" s="63" t="str">
         <f>IF(ISBLANK(B491),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B491))</f>
         <v/>
@@ -10771,8 +12741,12 @@
       <c r="E491" s="37"/>
       <c r="F491" s="40"/>
       <c r="G491" s="40"/>
-    </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H491" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A492" s="62" t="str">
         <f>IF(ISBLANK(B492),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B492))</f>
         <v/>
@@ -10783,8 +12757,12 @@
       <c r="E492" s="33"/>
       <c r="F492" s="39"/>
       <c r="G492" s="39"/>
-    </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H492" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A493" s="63" t="str">
         <f>IF(ISBLANK(B493),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B493))</f>
         <v/>
@@ -10795,8 +12773,12 @@
       <c r="E493" s="37"/>
       <c r="F493" s="40"/>
       <c r="G493" s="40"/>
-    </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H493" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" s="62" t="str">
         <f>IF(ISBLANK(B494),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B494))</f>
         <v/>
@@ -10807,8 +12789,12 @@
       <c r="E494" s="33"/>
       <c r="F494" s="39"/>
       <c r="G494" s="39"/>
-    </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H494" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" s="63" t="str">
         <f>IF(ISBLANK(B495),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B495))</f>
         <v/>
@@ -10819,8 +12805,12 @@
       <c r="E495" s="37"/>
       <c r="F495" s="40"/>
       <c r="G495" s="40"/>
-    </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H495" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" s="62" t="str">
         <f>IF(ISBLANK(B496),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B496))</f>
         <v/>
@@ -10831,8 +12821,12 @@
       <c r="E496" s="33"/>
       <c r="F496" s="39"/>
       <c r="G496" s="39"/>
-    </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H496" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" s="63" t="str">
         <f>IF(ISBLANK(B497),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B497))</f>
         <v/>
@@ -10843,8 +12837,12 @@
       <c r="E497" s="37"/>
       <c r="F497" s="40"/>
       <c r="G497" s="40"/>
-    </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H497" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" s="62" t="str">
         <f>IF(ISBLANK(B498),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B498))</f>
         <v/>
@@ -10855,8 +12853,12 @@
       <c r="E498" s="33"/>
       <c r="F498" s="39"/>
       <c r="G498" s="39"/>
-    </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H498" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" s="63" t="str">
         <f>IF(ISBLANK(B499),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B499))</f>
         <v/>
@@ -10867,8 +12869,12 @@
       <c r="E499" s="37"/>
       <c r="F499" s="40"/>
       <c r="G499" s="40"/>
-    </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H499" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A500" s="62" t="str">
         <f>IF(ISBLANK(B500),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B500))</f>
         <v/>
@@ -10879,8 +12885,12 @@
       <c r="E500" s="33"/>
       <c r="F500" s="39"/>
       <c r="G500" s="39"/>
-    </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H500" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A501" s="63" t="str">
         <f>IF(ISBLANK(B501),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B501))</f>
         <v/>
@@ -10891,8 +12901,12 @@
       <c r="E501" s="37"/>
       <c r="F501" s="40"/>
       <c r="G501" s="40"/>
-    </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H501" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A502" s="62" t="str">
         <f>IF(ISBLANK(B502),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B502))</f>
         <v/>
@@ -10903,8 +12917,12 @@
       <c r="E502" s="33"/>
       <c r="F502" s="39"/>
       <c r="G502" s="39"/>
-    </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H502" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A503" s="63" t="str">
         <f>IF(ISBLANK(B503),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B503))</f>
         <v/>
@@ -10915,8 +12933,12 @@
       <c r="E503" s="37"/>
       <c r="F503" s="40"/>
       <c r="G503" s="40"/>
-    </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H503" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A504" s="62" t="str">
         <f>IF(ISBLANK(B504),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B504))</f>
         <v/>
@@ -10927,8 +12949,12 @@
       <c r="E504" s="33"/>
       <c r="F504" s="39"/>
       <c r="G504" s="39"/>
-    </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H504" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A505" s="63" t="str">
         <f>IF(ISBLANK(B505),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B505))</f>
         <v/>
@@ -10939,8 +12965,12 @@
       <c r="E505" s="37"/>
       <c r="F505" s="40"/>
       <c r="G505" s="40"/>
-    </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H505" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A506" s="62" t="str">
         <f>IF(ISBLANK(B506),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B506))</f>
         <v/>
@@ -10951,8 +12981,12 @@
       <c r="E506" s="33"/>
       <c r="F506" s="39"/>
       <c r="G506" s="39"/>
-    </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H506" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A507" s="63" t="str">
         <f>IF(ISBLANK(B507),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B507))</f>
         <v/>
@@ -10963,8 +12997,12 @@
       <c r="E507" s="37"/>
       <c r="F507" s="40"/>
       <c r="G507" s="40"/>
-    </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H507" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A508" s="62" t="str">
         <f>IF(ISBLANK(B508),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B508))</f>
         <v/>
@@ -10975,8 +13013,12 @@
       <c r="E508" s="33"/>
       <c r="F508" s="39"/>
       <c r="G508" s="39"/>
-    </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H508" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A509" s="63" t="str">
         <f>IF(ISBLANK(B509),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B509))</f>
         <v/>
@@ -10987,8 +13029,12 @@
       <c r="E509" s="37"/>
       <c r="F509" s="40"/>
       <c r="G509" s="40"/>
-    </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H509" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A510" s="62" t="str">
         <f>IF(ISBLANK(B510),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B510))</f>
         <v/>
@@ -10999,8 +13045,12 @@
       <c r="E510" s="33"/>
       <c r="F510" s="39"/>
       <c r="G510" s="39"/>
-    </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H510" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A511" s="63" t="str">
         <f>IF(ISBLANK(B511),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B511))</f>
         <v/>
@@ -11011,8 +13061,12 @@
       <c r="E511" s="37"/>
       <c r="F511" s="40"/>
       <c r="G511" s="40"/>
-    </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H511" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A512" s="62" t="str">
         <f>IF(ISBLANK(B512),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B512))</f>
         <v/>
@@ -11023,8 +13077,12 @@
       <c r="E512" s="33"/>
       <c r="F512" s="39"/>
       <c r="G512" s="39"/>
-    </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H512" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" s="63" t="str">
         <f>IF(ISBLANK(B513),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B513))</f>
         <v/>
@@ -11035,8 +13093,12 @@
       <c r="E513" s="37"/>
       <c r="F513" s="40"/>
       <c r="G513" s="40"/>
-    </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H513" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" s="62" t="str">
         <f>IF(ISBLANK(B514),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B514))</f>
         <v/>
@@ -11047,8 +13109,12 @@
       <c r="E514" s="33"/>
       <c r="F514" s="39"/>
       <c r="G514" s="39"/>
-    </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H514" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" s="63" t="str">
         <f>IF(ISBLANK(B515),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B515))</f>
         <v/>
@@ -11059,8 +13125,12 @@
       <c r="E515" s="37"/>
       <c r="F515" s="40"/>
       <c r="G515" s="40"/>
-    </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H515" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" s="62" t="str">
         <f>IF(ISBLANK(B516),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B516))</f>
         <v/>
@@ -11071,8 +13141,12 @@
       <c r="E516" s="33"/>
       <c r="F516" s="39"/>
       <c r="G516" s="39"/>
-    </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H516" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" s="63" t="str">
         <f>IF(ISBLANK(B517),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B517))</f>
         <v/>
@@ -11083,8 +13157,12 @@
       <c r="E517" s="37"/>
       <c r="F517" s="40"/>
       <c r="G517" s="40"/>
-    </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H517" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" s="62" t="str">
         <f>IF(ISBLANK(B518),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B518))</f>
         <v/>
@@ -11095,8 +13173,12 @@
       <c r="E518" s="33"/>
       <c r="F518" s="39"/>
       <c r="G518" s="39"/>
-    </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H518" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" s="63" t="str">
         <f>IF(ISBLANK(B519),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B519))</f>
         <v/>
@@ -11107,8 +13189,12 @@
       <c r="E519" s="37"/>
       <c r="F519" s="40"/>
       <c r="G519" s="40"/>
-    </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H519" t="str">
+        <f t="shared" ref="H519:H532" si="8">IF(OR(ISBLANK(B519),B519=""),"",IF(B519=B518,"",INT(((SUMIF(B:B,B519,C:C)*60)+SUMIF(B:B,B519,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B519,C:C)*60)+SUMIF(B:B,B519,D:D),60),"00")&amp;" min"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" s="62" t="str">
         <f>IF(ISBLANK(B520),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B520))</f>
         <v/>
@@ -11119,8 +13205,12 @@
       <c r="E520" s="33"/>
       <c r="F520" s="39"/>
       <c r="G520" s="39"/>
-    </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H520" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" s="63" t="str">
         <f>IF(ISBLANK(B521),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B521))</f>
         <v/>
@@ -11131,8 +13221,12 @@
       <c r="E521" s="37"/>
       <c r="F521" s="40"/>
       <c r="G521" s="40"/>
-    </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H521" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" s="62" t="str">
         <f>IF(ISBLANK(B522),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B522))</f>
         <v/>
@@ -11143,8 +13237,12 @@
       <c r="E522" s="33"/>
       <c r="F522" s="39"/>
       <c r="G522" s="39"/>
-    </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H522" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" s="63" t="str">
         <f>IF(ISBLANK(B523),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B523))</f>
         <v/>
@@ -11155,8 +13253,12 @@
       <c r="E523" s="37"/>
       <c r="F523" s="40"/>
       <c r="G523" s="40"/>
-    </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H523" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" s="62" t="str">
         <f>IF(ISBLANK(B524),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B524))</f>
         <v/>
@@ -11167,8 +13269,12 @@
       <c r="E524" s="33"/>
       <c r="F524" s="39"/>
       <c r="G524" s="39"/>
-    </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H524" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" s="63" t="str">
         <f>IF(ISBLANK(B525),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B525))</f>
         <v/>
@@ -11179,8 +13285,12 @@
       <c r="E525" s="37"/>
       <c r="F525" s="40"/>
       <c r="G525" s="40"/>
-    </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H525" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" s="62" t="str">
         <f>IF(ISBLANK(B526),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B526))</f>
         <v/>
@@ -11191,8 +13301,12 @@
       <c r="E526" s="33"/>
       <c r="F526" s="39"/>
       <c r="G526" s="39"/>
-    </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H526" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" s="63" t="str">
         <f>IF(ISBLANK(B527),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B527))</f>
         <v/>
@@ -11203,8 +13317,12 @@
       <c r="E527" s="37"/>
       <c r="F527" s="40"/>
       <c r="G527" s="40"/>
-    </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H527" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" s="62" t="str">
         <f>IF(ISBLANK(B528),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B528))</f>
         <v/>
@@ -11215,8 +13333,12 @@
       <c r="E528" s="33"/>
       <c r="F528" s="39"/>
       <c r="G528" s="39"/>
-    </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H528" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" s="63" t="str">
         <f>IF(ISBLANK(B529),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B529))</f>
         <v/>
@@ -11227,8 +13349,12 @@
       <c r="E529" s="37"/>
       <c r="F529" s="40"/>
       <c r="G529" s="40"/>
-    </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H529" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" s="62" t="str">
         <f>IF(ISBLANK(B530),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B530))</f>
         <v/>
@@ -11239,8 +13365,12 @@
       <c r="E530" s="33"/>
       <c r="F530" s="39"/>
       <c r="G530" s="39"/>
-    </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H530" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" s="63" t="str">
         <f>IF(ISBLANK(B531),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B531))</f>
         <v/>
@@ -11251,8 +13381,12 @@
       <c r="E531" s="37"/>
       <c r="F531" s="40"/>
       <c r="G531" s="40"/>
-    </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H531" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" s="62" t="str">
         <f>IF(ISBLANK(B532),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B532))</f>
         <v/>
@@ -11263,6 +13397,10 @@
       <c r="E532" s="33"/>
       <c r="F532" s="39"/>
       <c r="G532" s="39"/>
+      <c r="H532" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <sheetProtection insertHyperlinks="0" selectLockedCells="1" sort="0" autoFilter="0"/>
@@ -11301,7 +13439,7 @@
       <formula>$E7="Implémentation"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:C532" xr:uid="{9D52E29F-610D-40B2-B3CC-F94A741DD978}">
       <formula1>$N$7:$N$15</formula1>
     </dataValidation>
@@ -11313,7 +13451,10 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="52" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="45" orientation="landscape" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="50" max="16383" man="1"/>
+  </rowBreaks>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -11641,6 +13782,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
@@ -11651,7 +13801,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B1120F001D1794FAA6F4057E3355991" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="62349bcdb43c26c508700efba1cb50b1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f20a0681-8b2f-4a46-9dab-cf1520193f81" xmlns:ns3="932fafb7-d8e0-4a14-bee3-33aad5c71309" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0e5d6db3f342a25e0e30f4a2965162e1" ns2:_="" ns3:_="">
     <xsd:import namespace="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
@@ -11840,16 +13990,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -11866,7 +14015,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1424D28F-D6A9-45ED-AED5-A0D744400EE5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11883,12 +14032,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
+++ b/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="98">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>Création de logo et son utilisation dans le projet</t>
+  </si>
+  <si>
+    <t>Ajout de légendes pour chaque axe du graphique</t>
   </si>
   <si>
     <t>Total heures TPI</t>
@@ -891,7 +894,7 @@
                   <c:v>245</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>805</c:v>
+                  <c:v>830</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1167,16 +1170,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.21304347826086956</c:v>
+                  <c:v>0.20851063829787234</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.7</c:v>
+                  <c:v>0.7063829787234043</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.08695652173913043</c:v>
+                  <c:v>0.0851063829787234</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -1255,7 +1258,7 @@
       <xdr:col>10</xdr:col>
       <xdr:colOff>203200</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>185836</xdr:rowOff>
+      <xdr:rowOff>185790</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1264,7 +1267,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="5499100" cy="5708604"/>
+        <a:ext cx="5499100" cy="5708558"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1285,7 +1288,7 @@
       <xdr:col>17</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>173136</xdr:rowOff>
+      <xdr:rowOff>173090</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1294,7 +1297,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="5572125" cy="5702254"/>
+        <a:ext cx="5572125" cy="5702208"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1534,7 +1537,7 @@
       <c r="B3" s="5"/>
       <c r="C3" s="65" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>19 heures 10 minutes</v>
+        <v>19 heures 35 minutes</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="3"/>
@@ -1553,11 +1556,11 @@
       </c>
       <c r="D4" s="16">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>790</v>
+        <v>815</v>
       </c>
       <c r="E4" s="16">
         <f>SUM(C4:D4)</f>
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -2816,19 +2819,27 @@
       </c>
     </row>
     <row r="52" ht="17.18">
-      <c r="A52" s="60" t="str">
+      <c r="A52" s="60">
         <f>IF(ISBLANK(B52),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B52))</f>
-        <v/>
-      </c>
-      <c r="B52" s="28"/>
+        <v>4</v>
+      </c>
+      <c r="B52" s="28">
+        <v>25.1</v>
+      </c>
       <c r="C52" s="29"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="21"/>
+      <c r="D52" s="30">
+        <v>25</v>
+      </c>
+      <c r="E52" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="F52" s="21" t="s">
+        <v>86</v>
+      </c>
       <c r="G52" s="37"/>
       <c r="H52" t="str">
         <f>IF(OR(ISBLANK(B52),B52=""),"",IF(B52=B51,"",INT(((SUMIF(B:B,B52,C:C)*60)+SUMIF(B:B,B52,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B52,C:C)*60)+SUMIF(B:B,B52,D:D),60),"00")&amp;" min"))</f>
-        <v/>
+        <v>0 h 25 min</v>
       </c>
     </row>
     <row r="53" ht="17.18">
@@ -10602,13 +10613,13 @@
   <sheetData>
     <row r="2" ht="27.27">
       <c r="E2" s="64" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F2" s="66">
         <v>90</v>
       </c>
       <c r="G2" s="64" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L2" s="17"/>
       <c r="M2" s="42"/>
@@ -10621,42 +10632,42 @@
     </row>
     <row r="4" ht="27.27">
       <c r="E4" s="64" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L4" s="64" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M4" s="39"/>
       <c r="N4" s="18"/>
     </row>
     <row r="5" ht="23.86">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" s="40"/>
       <c r="E5" s="43" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F5" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="L5" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="G5" s="45" t="s">
+      <c r="M5" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="L5" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="M5" s="47" t="s">
-        <v>94</v>
-      </c>
       <c r="N5" s="48" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" ht="23.86">
@@ -10682,7 +10693,7 @@
       </c>
       <c r="G6" s="70">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.21304347826086956</v>
+        <v>0.20851063829787234</v>
       </c>
       <c r="L6" s="49" t="str">
         <f>'Journal de travail'!M8</f>
@@ -10703,11 +10714,11 @@
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>505</v>
+        <v>530</v>
       </c>
       <c r="C7">
         <f>SUM(A7:B7)</f>
-        <v>805</v>
+        <v>830</v>
       </c>
       <c r="E7" s="71" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10715,11 +10726,11 @@
       </c>
       <c r="F7" s="72" t="str">
         <f>QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60),"00")&amp;" min"</f>
-        <v>13 h 25 min</v>
+        <v>13 h 50 min</v>
       </c>
       <c r="G7" s="73">
         <f>SUM(A7:B7)/$C$11</f>
-        <v>0.7</v>
+        <v>0.7063829787234043</v>
       </c>
       <c r="L7" s="51" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10793,7 +10804,7 @@
       </c>
       <c r="G9" s="73">
         <f>SUM(A9:B9)/$C$11</f>
-        <v>0.08695652173913043</v>
+        <v>0.0851063829787234</v>
       </c>
       <c r="L9" s="53" t="str">
         <f>'Journal de travail'!M11</f>
@@ -10849,25 +10860,25 @@
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>790</v>
+        <v>815</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="E11" s="79" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F11" s="69" t="str">
         <f>QUOTIENT(SUM(A11:B11),60)&amp;" h "&amp;TEXT(MOD(SUM(A11:B11),60),"00")&amp;" min"</f>
-        <v>19 h 10 min</v>
+        <v>19 h 35 min</v>
       </c>
       <c r="G11" s="80">
         <f>C11/C12</f>
-        <v>0.21296296296296297</v>
+        <v>0.2175925925925926</v>
       </c>
       <c r="L11" s="54" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M11" s="55"/>
       <c r="N11" s="58">

--- a/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
+++ b/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="102">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -290,6 +290,18 @@
   </si>
   <si>
     <t>Ajout de légendes pour chaque axe du graphique</t>
+  </si>
+  <si>
+    <t>Analyse du feedback du chef de projet</t>
+  </si>
+  <si>
+    <t>Je me suis un peu trop concentré sur l'intéraction et le visuel du programme, en oubliant certains point critiques, comme l'ajout des tests, utilisation de LINQ et une bonne organisation des méthodes (il faut créer des classes séparées pour chaque méthode important)</t>
+  </si>
+  <si>
+    <t>Transformation des boucles foreach en méthodes LINQ</t>
+  </si>
+  <si>
+    <t>Déplacement de la logique de parser des csv dans une classe séparée</t>
   </si>
   <si>
     <t>Total heures TPI</t>
@@ -891,10 +903,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>245</c:v>
+                  <c:v>265</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>830</c:v>
+                  <c:v>910</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1170,16 +1182,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.20851063829787234</c:v>
+                  <c:v>0.20784313725490197</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.7063829787234043</c:v>
+                  <c:v>0.7137254901960784</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0851063829787234</c:v>
+                  <c:v>0.0784313725490196</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -1258,7 +1270,7 @@
       <xdr:col>10</xdr:col>
       <xdr:colOff>203200</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>185790</xdr:rowOff>
+      <xdr:rowOff>185744</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1267,7 +1279,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="5499100" cy="5708558"/>
+        <a:ext cx="5499100" cy="5708512"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1288,7 +1300,7 @@
       <xdr:col>17</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>173090</xdr:rowOff>
+      <xdr:rowOff>173044</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1297,7 +1309,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="5572125" cy="5702208"/>
+        <a:ext cx="5572125" cy="5702162"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1537,7 +1549,7 @@
       <c r="B3" s="5"/>
       <c r="C3" s="65" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>19 heures 35 minutes</v>
+        <v>21 heures 15 minutes</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="3"/>
@@ -1556,11 +1568,11 @@
       </c>
       <c r="D4" s="16">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>815</v>
+        <v>915</v>
       </c>
       <c r="E4" s="16">
         <f>SUM(C4:D4)</f>
-        <v>1175</v>
+        <v>1275</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -2821,10 +2833,10 @@
     <row r="52" ht="17.18">
       <c r="A52" s="60">
         <f>IF(ISBLANK(B52),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B52))</f>
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="B52" s="28">
-        <v>25.1</v>
+        <v>46320</v>
       </c>
       <c r="C52" s="29"/>
       <c r="D52" s="30">
@@ -2839,35 +2851,53 @@
       <c r="G52" s="37"/>
       <c r="H52" t="str">
         <f>IF(OR(ISBLANK(B52),B52=""),"",IF(B52=B51,"",INT(((SUMIF(B:B,B52,C:C)*60)+SUMIF(B:B,B52,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B52,C:C)*60)+SUMIF(B:B,B52,D:D),60),"00")&amp;" min"))</f>
-        <v>0 h 25 min</v>
-      </c>
-    </row>
-    <row r="53" ht="17.18">
-      <c r="A53" s="61" t="str">
+        <v>2 h 05 min</v>
+      </c>
+    </row>
+    <row r="53" ht="77.25">
+      <c r="A53" s="61">
         <f>IF(ISBLANK(B53),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B53))</f>
-        <v/>
-      </c>
-      <c r="B53" s="32"/>
+        <v>43</v>
+      </c>
+      <c r="B53" s="28">
+        <v>46320</v>
+      </c>
       <c r="C53" s="33"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="35"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="38"/>
+      <c r="D53" s="34">
+        <v>20</v>
+      </c>
+      <c r="E53" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="G53" s="38" t="s">
+        <v>88</v>
+      </c>
       <c r="H53" t="str">
         <f>IF(OR(ISBLANK(B53),B53=""),"",IF(B53=B52,"",INT(((SUMIF(B:B,B53,C:C)*60)+SUMIF(B:B,B53,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B53,C:C)*60)+SUMIF(B:B,B53,D:D),60),"00")&amp;" min"))</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="17.18">
-      <c r="A54" s="60" t="str">
+      <c r="A54" s="60">
         <f>IF(ISBLANK(B54),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B54))</f>
-        <v/>
-      </c>
-      <c r="B54" s="28"/>
+        <v>43</v>
+      </c>
+      <c r="B54" s="28">
+        <v>46320</v>
+      </c>
       <c r="C54" s="29"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="31"/>
-      <c r="F54" s="21"/>
+      <c r="D54" s="30">
+        <v>50</v>
+      </c>
+      <c r="E54" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="F54" s="21" t="s">
+        <v>89</v>
+      </c>
       <c r="G54" s="37"/>
       <c r="H54" t="str">
         <f>IF(OR(ISBLANK(B54),B54=""),"",IF(B54=B53,"",INT(((SUMIF(B:B,B54,C:C)*60)+SUMIF(B:B,B54,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B54,C:C)*60)+SUMIF(B:B,B54,D:D),60),"00")&amp;" min"))</f>
@@ -2875,15 +2905,23 @@
       </c>
     </row>
     <row r="55" ht="17.18">
-      <c r="A55" s="61" t="str">
+      <c r="A55" s="61">
         <f>IF(ISBLANK(B55),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B55))</f>
-        <v/>
-      </c>
-      <c r="B55" s="32"/>
+        <v>43</v>
+      </c>
+      <c r="B55" s="28">
+        <v>46320</v>
+      </c>
       <c r="C55" s="33"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="21"/>
+      <c r="D55" s="34">
+        <v>30</v>
+      </c>
+      <c r="E55" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>90</v>
+      </c>
       <c r="G55" s="38"/>
       <c r="H55" t="str">
         <f>IF(OR(ISBLANK(B55),B55=""),"",IF(B55=B54,"",INT(((SUMIF(B:B,B55,C:C)*60)+SUMIF(B:B,B55,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B55,C:C)*60)+SUMIF(B:B,B55,D:D),60),"00")&amp;" min"))</f>
@@ -10574,15 +10612,24 @@
       <formula>$E7="Implémentation"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:C532">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:C53 C55:C532">
       <formula1>$N$7:$N$15</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D532">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D53 D55:D532">
       <formula1>$O$7:$O$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7:E532">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7:E53 E55:E532">
       <formula1>$M$7:$M$12</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E54">
+      <formula1>$M$7:$M$12</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C54">
+      <formula1>$N$7:$N$15</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D54">
+      <formula1>$O$7:$O$19</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
@@ -10613,13 +10660,13 @@
   <sheetData>
     <row r="2" ht="27.27">
       <c r="E2" s="64" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F2" s="66">
         <v>90</v>
       </c>
       <c r="G2" s="64" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="L2" s="17"/>
       <c r="M2" s="42"/>
@@ -10632,42 +10679,42 @@
     </row>
     <row r="4" ht="27.27">
       <c r="E4" s="64" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="L4" s="64" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M4" s="39"/>
       <c r="N4" s="18"/>
     </row>
     <row r="5" ht="23.86">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D5" s="40"/>
       <c r="E5" s="43" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G5" s="45" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L5" s="46" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="M5" s="47" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="N5" s="48" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" ht="23.86">
@@ -10677,11 +10724,11 @@
       </c>
       <c r="B6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$D$7:$D$532)</f>
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C6">
         <f>SUM(A6:B6)</f>
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="E6" s="68" t="str">
         <f>'Journal de travail'!M8</f>
@@ -10689,11 +10736,11 @@
       </c>
       <c r="F6" s="69" t="str">
         <f>QUOTIENT(SUM(A6:B6),60)&amp;" h "&amp;TEXT(MOD(SUM(A6:B6),60),"00")&amp;" min"</f>
-        <v>4 h 05 min</v>
+        <v>4 h 25 min</v>
       </c>
       <c r="G6" s="70">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.20851063829787234</v>
+        <v>0.20784313725490197</v>
       </c>
       <c r="L6" s="49" t="str">
         <f>'Journal de travail'!M8</f>
@@ -10714,11 +10761,11 @@
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>530</v>
+        <v>610</v>
       </c>
       <c r="C7">
         <f>SUM(A7:B7)</f>
-        <v>830</v>
+        <v>910</v>
       </c>
       <c r="E7" s="71" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10726,11 +10773,11 @@
       </c>
       <c r="F7" s="72" t="str">
         <f>QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60),"00")&amp;" min"</f>
-        <v>13 h 50 min</v>
+        <v>15 h 10 min</v>
       </c>
       <c r="G7" s="73">
         <f>SUM(A7:B7)/$C$11</f>
-        <v>0.7063829787234043</v>
+        <v>0.7137254901960784</v>
       </c>
       <c r="L7" s="51" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10804,7 +10851,7 @@
       </c>
       <c r="G9" s="73">
         <f>SUM(A9:B9)/$C$11</f>
-        <v>0.0851063829787234</v>
+        <v>0.0784313725490196</v>
       </c>
       <c r="L9" s="53" t="str">
         <f>'Journal de travail'!M11</f>
@@ -10860,25 +10907,25 @@
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>815</v>
+        <v>915</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>1175</v>
+        <v>1275</v>
       </c>
       <c r="E11" s="79" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F11" s="69" t="str">
         <f>QUOTIENT(SUM(A11:B11),60)&amp;" h "&amp;TEXT(MOD(SUM(A11:B11),60),"00")&amp;" min"</f>
-        <v>19 h 35 min</v>
+        <v>21 h 15 min</v>
       </c>
       <c r="G11" s="80">
         <f>C11/C12</f>
-        <v>0.2175925925925926</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="L11" s="54" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="M11" s="55"/>
       <c r="N11" s="58">

--- a/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
+++ b/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="103">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>Déplacement de la logique de parser des csv dans une classe séparée</t>
+  </si>
+  <si>
+    <t>Déplacement de la logique de transformation des nombres dans une classe séparée</t>
   </si>
   <si>
     <t>Total heures TPI</t>
@@ -906,7 +909,7 @@
                   <c:v>265</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>910</c:v>
+                  <c:v>915</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1182,16 +1185,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.20784313725490197</c:v>
+                  <c:v>0.20703125</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.7137254901960784</c:v>
+                  <c:v>0.71484375</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0784313725490196</c:v>
+                  <c:v>0.078125</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -1549,7 +1552,7 @@
       <c r="B3" s="5"/>
       <c r="C3" s="65" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>21 heures 15 minutes</v>
+        <v>21 heures 20 minutes</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="3"/>
@@ -1568,11 +1571,11 @@
       </c>
       <c r="D4" s="16">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="E4" s="16">
         <f>SUM(C4:D4)</f>
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -2851,7 +2854,7 @@
       <c r="G52" s="37"/>
       <c r="H52" t="str">
         <f>IF(OR(ISBLANK(B52),B52=""),"",IF(B52=B51,"",INT(((SUMIF(B:B,B52,C:C)*60)+SUMIF(B:B,B52,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B52,C:C)*60)+SUMIF(B:B,B52,D:D),60),"00")&amp;" min"))</f>
-        <v>2 h 05 min</v>
+        <v>2 h 10 min</v>
       </c>
     </row>
     <row r="53" ht="77.25">
@@ -2929,15 +2932,23 @@
       </c>
     </row>
     <row r="56" ht="17.18">
-      <c r="A56" s="60" t="str">
+      <c r="A56" s="60">
         <f>IF(ISBLANK(B56),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B56))</f>
-        <v/>
-      </c>
-      <c r="B56" s="28"/>
+        <v>43</v>
+      </c>
+      <c r="B56" s="28">
+        <v>46320</v>
+      </c>
       <c r="C56" s="29"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="31"/>
-      <c r="F56" s="37"/>
+      <c r="D56" s="30">
+        <v>5</v>
+      </c>
+      <c r="E56" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>91</v>
+      </c>
       <c r="G56" s="37"/>
       <c r="H56" t="str">
         <f>IF(OR(ISBLANK(B56),B56=""),"",IF(B56=B55,"",INT(((SUMIF(B:B,B56,C:C)*60)+SUMIF(B:B,B56,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B56,C:C)*60)+SUMIF(B:B,B56,D:D),60),"00")&amp;" min"))</f>
@@ -10660,13 +10671,13 @@
   <sheetData>
     <row r="2" ht="27.27">
       <c r="E2" s="64" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F2" s="66">
         <v>90</v>
       </c>
       <c r="G2" s="64" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L2" s="17"/>
       <c r="M2" s="42"/>
@@ -10679,42 +10690,42 @@
     </row>
     <row r="4" ht="27.27">
       <c r="E4" s="64" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L4" s="64" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M4" s="39"/>
       <c r="N4" s="18"/>
     </row>
     <row r="5" ht="23.86">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D5" s="40"/>
       <c r="E5" s="43" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F5" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="L5" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="G5" s="45" t="s">
+      <c r="M5" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="L5" s="46" t="s">
-        <v>98</v>
-      </c>
-      <c r="M5" s="47" t="s">
-        <v>99</v>
-      </c>
       <c r="N5" s="48" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" ht="23.86">
@@ -10740,7 +10751,7 @@
       </c>
       <c r="G6" s="70">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.20784313725490197</v>
+        <v>0.20703125</v>
       </c>
       <c r="L6" s="49" t="str">
         <f>'Journal de travail'!M8</f>
@@ -10761,11 +10772,11 @@
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="C7">
         <f>SUM(A7:B7)</f>
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="E7" s="71" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10773,11 +10784,11 @@
       </c>
       <c r="F7" s="72" t="str">
         <f>QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60),"00")&amp;" min"</f>
-        <v>15 h 10 min</v>
+        <v>15 h 15 min</v>
       </c>
       <c r="G7" s="73">
         <f>SUM(A7:B7)/$C$11</f>
-        <v>0.7137254901960784</v>
+        <v>0.71484375</v>
       </c>
       <c r="L7" s="51" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10851,7 +10862,7 @@
       </c>
       <c r="G9" s="73">
         <f>SUM(A9:B9)/$C$11</f>
-        <v>0.0784313725490196</v>
+        <v>0.078125</v>
       </c>
       <c r="L9" s="53" t="str">
         <f>'Journal de travail'!M11</f>
@@ -10907,25 +10918,25 @@
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="E11" s="79" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F11" s="69" t="str">
         <f>QUOTIENT(SUM(A11:B11),60)&amp;" h "&amp;TEXT(MOD(SUM(A11:B11),60),"00")&amp;" min"</f>
-        <v>21 h 15 min</v>
+        <v>21 h 20 min</v>
       </c>
       <c r="G11" s="80">
         <f>C11/C12</f>
-        <v>0.2361111111111111</v>
+        <v>0.23703703703703705</v>
       </c>
       <c r="L11" s="54" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M11" s="55"/>
       <c r="N11" s="58">

--- a/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
+++ b/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="104">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t>Déplacement de la logique de transformation des nombres dans une classe séparée</t>
+  </si>
+  <si>
+    <t>Déplacement de la logique de merge des séries dans une classe séparée</t>
   </si>
   <si>
     <t>Total heures TPI</t>
@@ -909,7 +912,7 @@
                   <c:v>265</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>915</c:v>
+                  <c:v>945</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1185,16 +1188,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.20703125</c:v>
+                  <c:v>0.20229007633587787</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.71484375</c:v>
+                  <c:v>0.7213740458015268</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.078125</c:v>
+                  <c:v>0.07633587786259542</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -1552,7 +1555,7 @@
       <c r="B3" s="5"/>
       <c r="C3" s="65" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>21 heures 20 minutes</v>
+        <v>21 heures 50 minutes</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="3"/>
@@ -1571,11 +1574,11 @@
       </c>
       <c r="D4" s="16">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>920</v>
+        <v>950</v>
       </c>
       <c r="E4" s="16">
         <f>SUM(C4:D4)</f>
-        <v>1280</v>
+        <v>1310</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -2854,7 +2857,7 @@
       <c r="G52" s="37"/>
       <c r="H52" t="str">
         <f>IF(OR(ISBLANK(B52),B52=""),"",IF(B52=B51,"",INT(((SUMIF(B:B,B52,C:C)*60)+SUMIF(B:B,B52,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B52,C:C)*60)+SUMIF(B:B,B52,D:D),60),"00")&amp;" min"))</f>
-        <v>2 h 10 min</v>
+        <v>2 h 40 min</v>
       </c>
     </row>
     <row r="53" ht="77.25">
@@ -2956,15 +2959,23 @@
       </c>
     </row>
     <row r="57" ht="17.18">
-      <c r="A57" s="61" t="str">
+      <c r="A57" s="61">
         <f>IF(ISBLANK(B57),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B57))</f>
-        <v/>
-      </c>
-      <c r="B57" s="32"/>
+        <v>43</v>
+      </c>
+      <c r="B57" s="28">
+        <v>46320</v>
+      </c>
       <c r="C57" s="33"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="38"/>
+      <c r="D57" s="34">
+        <v>30</v>
+      </c>
+      <c r="E57" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="F57" s="21" t="s">
+        <v>92</v>
+      </c>
       <c r="G57" s="38"/>
       <c r="H57" t="str">
         <f>IF(OR(ISBLANK(B57),B57=""),"",IF(B57=B56,"",INT(((SUMIF(B:B,B57,C:C)*60)+SUMIF(B:B,B57,D:D))/60)&amp;" h "&amp;TEXT(MOD((SUMIF(B:B,B57,C:C)*60)+SUMIF(B:B,B57,D:D),60),"00")&amp;" min"))</f>
@@ -10623,14 +10634,14 @@
       <formula>$E7="Implémentation"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:C53 C55:C532">
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:C53 C55:C56 C58:C532">
       <formula1>$N$7:$N$15</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D53 D55:D532">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D53 D55:D56 D58:D532">
       <formula1>$O$7:$O$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7:E53 E55:E532">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7:E53 E55:E56 E58:E532">
       <formula1>$M$7:$M$12</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E54">
@@ -10641,6 +10652,15 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D54">
       <formula1>$O$7:$O$19</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C57">
+      <formula1>$N$7:$N$15</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D57">
+      <formula1>$O$7:$O$19</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E57">
+      <formula1>$M$7:$M$12</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
@@ -10671,13 +10691,13 @@
   <sheetData>
     <row r="2" ht="27.27">
       <c r="E2" s="64" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F2" s="66">
         <v>90</v>
       </c>
       <c r="G2" s="64" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L2" s="17"/>
       <c r="M2" s="42"/>
@@ -10690,42 +10710,42 @@
     </row>
     <row r="4" ht="27.27">
       <c r="E4" s="64" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L4" s="64" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M4" s="39"/>
       <c r="N4" s="18"/>
     </row>
     <row r="5" ht="23.86">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D5" s="40"/>
       <c r="E5" s="43" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F5" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="L5" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="G5" s="45" t="s">
+      <c r="M5" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="46" t="s">
-        <v>99</v>
-      </c>
-      <c r="M5" s="47" t="s">
-        <v>100</v>
-      </c>
       <c r="N5" s="48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" ht="23.86">
@@ -10751,7 +10771,7 @@
       </c>
       <c r="G6" s="70">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.20703125</v>
+        <v>0.20229007633587787</v>
       </c>
       <c r="L6" s="49" t="str">
         <f>'Journal de travail'!M8</f>
@@ -10772,11 +10792,11 @@
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>615</v>
+        <v>645</v>
       </c>
       <c r="C7">
         <f>SUM(A7:B7)</f>
-        <v>915</v>
+        <v>945</v>
       </c>
       <c r="E7" s="71" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10784,11 +10804,11 @@
       </c>
       <c r="F7" s="72" t="str">
         <f>QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60),"00")&amp;" min"</f>
-        <v>15 h 15 min</v>
+        <v>15 h 45 min</v>
       </c>
       <c r="G7" s="73">
         <f>SUM(A7:B7)/$C$11</f>
-        <v>0.71484375</v>
+        <v>0.7213740458015268</v>
       </c>
       <c r="L7" s="51" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10862,7 +10882,7 @@
       </c>
       <c r="G9" s="73">
         <f>SUM(A9:B9)/$C$11</f>
-        <v>0.078125</v>
+        <v>0.07633587786259542</v>
       </c>
       <c r="L9" s="53" t="str">
         <f>'Journal de travail'!M11</f>
@@ -10918,25 +10938,25 @@
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>920</v>
+        <v>950</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>1280</v>
+        <v>1310</v>
       </c>
       <c r="E11" s="79" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F11" s="69" t="str">
         <f>QUOTIENT(SUM(A11:B11),60)&amp;" h "&amp;TEXT(MOD(SUM(A11:B11),60),"00")&amp;" min"</f>
-        <v>21 h 20 min</v>
+        <v>21 h 50 min</v>
       </c>
       <c r="G11" s="80">
         <f>C11/C12</f>
-        <v>0.23703703703703705</v>
+        <v>0.24259259259259258</v>
       </c>
       <c r="L11" s="54" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M11" s="55"/>
       <c r="N11" s="58">

--- a/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
+++ b/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px20umf\Documents\github\PlotThoseLines\docs\jdt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C2DBAE-5E4F-49C1-931A-8B4B87546635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85DB7A06-2284-4737-B7B8-E09F3D9F734E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32235" yWindow="2025" windowWidth="21600" windowHeight="11745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4725" yWindow="1155" windowWidth="21600" windowHeight="11745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="Initiale VS Effective" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="115">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -366,6 +365,21 @@
   </si>
   <si>
     <t>pour 26.10</t>
+  </si>
+  <si>
+    <t>Création des tests pour le Parser et le SeriesMerger</t>
+  </si>
+  <si>
+    <t>Disscution sur l'avancement du projet et sur certaines parties du code avec le chef de projet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mise à jour du rapport </t>
+  </si>
+  <si>
+    <t>Analyse des points restants, il faut encore finir le rapport</t>
+  </si>
+  <si>
+    <t>J'ai completé les bilans dans le rapport</t>
   </si>
 </sst>
 </file>
@@ -1262,16 +1276,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.19354838709677419</c:v>
+                  <c:v>0.18471337579617833</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.73476702508960579</c:v>
+                  <c:v>0.75159235668789814</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.1684587813620068E-2</c:v>
+                  <c:v>6.3694267515923567E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1655,7 +1669,7 @@
       <c r="B3" s="85"/>
       <c r="C3" s="65" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>23 heures 15 minutes</v>
+        <v>26 heures 10 minutes</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="3"/>
@@ -1670,15 +1684,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="16">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="D4" s="16">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>975</v>
+        <v>1090</v>
       </c>
       <c r="E4" s="16">
         <f>SUM(C4:D4)</f>
-        <v>1395</v>
+        <v>1570</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -3109,7 +3123,7 @@
       <c r="G58" s="37"/>
       <c r="H58" t="str">
         <f t="shared" si="0"/>
-        <v>1 h 25 min</v>
+        <v>3 h 00 min</v>
       </c>
       <c r="I58" t="s">
         <v>109</v>
@@ -3144,15 +3158,23 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="60" t="str">
+      <c r="A60" s="60">
         <f>IF(ISBLANK(B60),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B60))</f>
-        <v/>
-      </c>
-      <c r="B60" s="28"/>
+        <v>44</v>
+      </c>
+      <c r="B60" s="28">
+        <v>46321</v>
+      </c>
       <c r="C60" s="29"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="31"/>
-      <c r="F60" s="37"/>
+      <c r="D60" s="30">
+        <v>30</v>
+      </c>
+      <c r="E60" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="F60" s="37" t="s">
+        <v>110</v>
+      </c>
       <c r="G60" s="37"/>
       <c r="H60" t="str">
         <f t="shared" si="0"/>
@@ -3160,15 +3182,23 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="61" t="str">
+      <c r="A61" s="61">
         <f>IF(ISBLANK(B61),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B61))</f>
-        <v/>
-      </c>
-      <c r="B61" s="32"/>
+        <v>44</v>
+      </c>
+      <c r="B61" s="32">
+        <v>46321</v>
+      </c>
       <c r="C61" s="33"/>
-      <c r="D61" s="34"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="38"/>
+      <c r="D61" s="34">
+        <v>10</v>
+      </c>
+      <c r="E61" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" s="38" t="s">
+        <v>111</v>
+      </c>
       <c r="G61" s="38"/>
       <c r="H61" t="str">
         <f t="shared" si="0"/>
@@ -3176,15 +3206,23 @@
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="60" t="str">
+      <c r="A62" s="60">
         <f>IF(ISBLANK(B62),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B62))</f>
-        <v/>
-      </c>
-      <c r="B62" s="28"/>
+        <v>44</v>
+      </c>
+      <c r="B62" s="28">
+        <v>46321</v>
+      </c>
       <c r="C62" s="29"/>
-      <c r="D62" s="30"/>
-      <c r="E62" s="31"/>
-      <c r="F62" s="37"/>
+      <c r="D62" s="30">
+        <v>50</v>
+      </c>
+      <c r="E62" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="F62" s="37" t="s">
+        <v>112</v>
+      </c>
       <c r="G62" s="37"/>
       <c r="H62" t="str">
         <f t="shared" si="0"/>
@@ -3192,15 +3230,23 @@
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="61" t="str">
+      <c r="A63" s="61">
         <f>IF(ISBLANK(B63),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B63))</f>
-        <v/>
-      </c>
-      <c r="B63" s="32"/>
+        <v>44</v>
+      </c>
+      <c r="B63" s="32">
+        <v>46321</v>
+      </c>
       <c r="C63" s="33"/>
-      <c r="D63" s="34"/>
-      <c r="E63" s="35"/>
-      <c r="F63" s="38"/>
+      <c r="D63" s="34">
+        <v>5</v>
+      </c>
+      <c r="E63" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="F63" s="38" t="s">
+        <v>81</v>
+      </c>
       <c r="G63" s="38"/>
       <c r="H63" t="str">
         <f t="shared" si="0"/>
@@ -3208,32 +3254,54 @@
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="60" t="str">
+      <c r="A64" s="60">
         <f>IF(ISBLANK(B64),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B64))</f>
-        <v/>
-      </c>
-      <c r="B64" s="28"/>
+        <v>44</v>
+      </c>
+      <c r="B64" s="28">
+        <v>46323</v>
+      </c>
       <c r="C64" s="29"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="31"/>
-      <c r="F64" s="37"/>
-      <c r="G64" s="37"/>
+      <c r="D64" s="30">
+        <v>10</v>
+      </c>
+      <c r="E64" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F64" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G64" s="37" t="s">
+        <v>113</v>
+      </c>
       <c r="H64" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1 h 20 min</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="61" t="str">
+      <c r="A65" s="61">
         <f>IF(ISBLANK(B65),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B65))</f>
-        <v/>
-      </c>
-      <c r="B65" s="32"/>
-      <c r="C65" s="33"/>
-      <c r="D65" s="34"/>
-      <c r="E65" s="35"/>
-      <c r="F65" s="38"/>
-      <c r="G65" s="38"/>
+        <v>44</v>
+      </c>
+      <c r="B65" s="32">
+        <v>46323</v>
+      </c>
+      <c r="C65" s="33">
+        <v>1</v>
+      </c>
+      <c r="D65" s="34">
+        <v>10</v>
+      </c>
+      <c r="E65" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="F65" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="G65" s="38" t="s">
+        <v>114</v>
+      </c>
       <c r="H65" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -10850,11 +10918,11 @@
       </c>
       <c r="B6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$D$7:$D$532)</f>
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C11" si="0">SUM(A6:B6)</f>
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="E6" s="68" t="str">
         <f>'Journal de travail'!M8</f>
@@ -10862,11 +10930,11 @@
       </c>
       <c r="F6" s="69" t="str">
         <f t="shared" ref="F6:F11" si="1">QUOTIENT(SUM(A6:B6),60)&amp;" h "&amp;TEXT(MOD(SUM(A6:B6),60),"00")&amp;" min"</f>
-        <v>4 h 30 min</v>
+        <v>4 h 50 min</v>
       </c>
       <c r="G6" s="70">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.19354838709677419</v>
+        <v>0.18471337579617833</v>
       </c>
       <c r="L6" s="49" t="str">
         <f>'Journal de travail'!M8</f>
@@ -10883,15 +10951,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>665</v>
+        <v>760</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>1025</v>
+        <v>1180</v>
       </c>
       <c r="E7" s="71" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10899,11 +10967,11 @@
       </c>
       <c r="F7" s="72" t="str">
         <f t="shared" si="1"/>
-        <v>17 h 05 min</v>
+        <v>19 h 40 min</v>
       </c>
       <c r="G7" s="73">
         <f>SUM(A7:B7)/$C$11</f>
-        <v>0.73476702508960579</v>
+        <v>0.75159235668789814</v>
       </c>
       <c r="L7" s="51" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10977,7 +11045,7 @@
       </c>
       <c r="G9" s="73">
         <f>SUM(A9:B9)/$C$11</f>
-        <v>7.1684587813620068E-2</v>
+        <v>6.3694267515923567E-2</v>
       </c>
       <c r="L9" s="53" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11029,26 +11097,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>975</v>
+        <v>1090</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
-        <v>1395</v>
+        <v>1570</v>
       </c>
       <c r="E11" s="79" t="s">
         <v>103</v>
       </c>
       <c r="F11" s="69" t="str">
         <f t="shared" si="1"/>
-        <v>23 h 15 min</v>
+        <v>26 h 10 min</v>
       </c>
       <c r="G11" s="80">
         <f>C11/C12</f>
-        <v>0.25833333333333336</v>
+        <v>0.29074074074074074</v>
       </c>
       <c r="L11" s="54" t="s">
         <v>103</v>
@@ -11089,17 +11157,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B1120F001D1794FAA6F4057E3355991" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="62349bcdb43c26c508700efba1cb50b1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f20a0681-8b2f-4a46-9dab-cf1520193f81" xmlns:ns3="932fafb7-d8e0-4a14-bee3-33aad5c71309" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0e5d6db3f342a25e0e30f4a2965162e1" ns2:_="" ns3:_="">
     <xsd:import namespace="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
@@ -11288,6 +11345,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11298,23 +11366,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1424D28F-D6A9-45ED-AED5-A0D744400EE5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11333,6 +11384,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>

--- a/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
+++ b/docs/jdt/Journal-de-Travail_BorminKiril.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px20umf\Documents\github\PlotThoseLines\docs\jdt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85DB7A06-2284-4737-B7B8-E09F3D9F734E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F330880-6A18-4B0C-9A91-F356F0AA43D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4725" yWindow="1155" windowWidth="21600" windowHeight="11745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1650" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="118">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -292,12 +292,18 @@
     <t>Correction d'affichage pour les écrans de haute résolution</t>
   </si>
   <si>
+    <t>pour 20.10</t>
+  </si>
+  <si>
     <t>Création de logo et son utilisation dans le projet</t>
   </si>
   <si>
     <t>Ajout de légendes pour chaque axe du graphique</t>
   </si>
   <si>
+    <t>pour 25.10</t>
+  </si>
+  <si>
     <t>Analyse du feedback du chef de projet</t>
   </si>
   <si>
@@ -316,6 +322,39 @@
     <t>Déplacement de la logique de merge des séries dans une classe séparée</t>
   </si>
   <si>
+    <t>Explication des détails pour le projet par le chef de projet, et démarage de la journée</t>
+  </si>
+  <si>
+    <t>pour 26.10</t>
+  </si>
+  <si>
+    <t>Création et mise en place de projet de test</t>
+  </si>
+  <si>
+    <t>J'ai rencontré des difficultés lors d'installation des extentions pour les tests</t>
+  </si>
+  <si>
+    <t>Création des tests pour le Parser et le SeriesMerger</t>
+  </si>
+  <si>
+    <t>Disscution sur l'avancement du projet et sur certaines parties du code avec le chef de projet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mise à jour du rapport </t>
+  </si>
+  <si>
+    <t>Analyse des points restants, il faut encore finir le rapport</t>
+  </si>
+  <si>
+    <t>pour 28.10</t>
+  </si>
+  <si>
+    <t>J'ai completé les bilans dans le rapport</t>
+  </si>
+  <si>
+    <t>pour 29.10</t>
+  </si>
+  <si>
     <t>Total heures TPI</t>
   </si>
   <si>
@@ -349,37 +388,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Explication des détails pour le projet par le chef de projet, et démarage de la journée</t>
-  </si>
-  <si>
-    <t>Création et mise en place de projet de test</t>
-  </si>
-  <si>
-    <t>J'ai rencontré des difficultés lors d'installation des extentions pour les tests</t>
-  </si>
-  <si>
-    <t>pour 20.10</t>
-  </si>
-  <si>
-    <t>pour 25.10</t>
-  </si>
-  <si>
-    <t>pour 26.10</t>
-  </si>
-  <si>
-    <t>Création des tests pour le Parser et le SeriesMerger</t>
-  </si>
-  <si>
-    <t>Disscution sur l'avancement du projet et sur certaines parties du code avec le chef de projet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mise à jour du rapport </t>
-  </si>
-  <si>
-    <t>Analyse des points restants, il faut encore finir le rapport</t>
-  </si>
-  <si>
-    <t>J'ai completé les bilans dans le rapport</t>
+    <t>Finalisation de rapport et livraison des fichiers</t>
   </si>
 </sst>
 </file>
@@ -956,7 +965,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F5FE-49EE-BE4F-11D09FE0E927}"/>
+              <c16:uniqueId val="{00000000-70E4-44E3-9C16-24CB42CC8929}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1057,7 +1066,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-52C2-4B5A-983C-EA8938461D4F}"/>
+              <c16:uniqueId val="{00000000-860A-47B4-9A02-12967DE0E791}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1204,7 +1213,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C531-458E-AD92-848B15585BFF}"/>
+              <c16:uniqueId val="{00000000-0068-4B7F-A845-5AD764A336A1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1276,23 +1285,23 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.18471337579617833</c:v>
+                  <c:v>0.18124999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.75159235668789814</c:v>
+                  <c:v>0.75624999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.3694267515923567E-2</c:v>
+                  <c:v>6.25E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C531-458E-AD92-848B15585BFF}"/>
+              <c16:uniqueId val="{00000001-0068-4B7F-A845-5AD764A336A1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1669,7 +1678,7 @@
       <c r="B3" s="85"/>
       <c r="C3" s="65" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>26 heures 10 minutes</v>
+        <v>26 heures 40 minutes</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="3"/>
@@ -1688,11 +1697,11 @@
       </c>
       <c r="D4" s="16">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>1090</v>
+        <v>1120</v>
       </c>
       <c r="E4" s="16">
         <f>SUM(C4:D4)</f>
-        <v>1570</v>
+        <v>1600</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -2926,7 +2935,7 @@
         <v>0 h 55 min</v>
       </c>
       <c r="I50" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -2945,7 +2954,7 @@
         <v>22</v>
       </c>
       <c r="F51" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G51" s="38"/>
       <c r="H51" t="str">
@@ -2969,7 +2978,7 @@
         <v>22</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G52" s="37"/>
       <c r="H52" t="str">
@@ -2977,7 +2986,7 @@
         <v>2 h 40 min</v>
       </c>
       <c r="I52" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="63" x14ac:dyDescent="0.25">
@@ -2996,10 +3005,10 @@
         <v>18</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G53" s="38" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H53" t="str">
         <f t="shared" si="0"/>
@@ -3022,7 +3031,7 @@
         <v>22</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G54" s="37"/>
       <c r="H54" t="str">
@@ -3046,7 +3055,7 @@
         <v>22</v>
       </c>
       <c r="F55" s="21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G55" s="38"/>
       <c r="H55" t="str">
@@ -3070,7 +3079,7 @@
         <v>22</v>
       </c>
       <c r="F56" s="21" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G56" s="37"/>
       <c r="H56" t="str">
@@ -3094,7 +3103,7 @@
         <v>22</v>
       </c>
       <c r="F57" s="21" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G57" s="38"/>
       <c r="H57" t="str">
@@ -3118,7 +3127,7 @@
         <v>18</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="G58" s="37"/>
       <c r="H58" t="str">
@@ -3126,7 +3135,7 @@
         <v>3 h 00 min</v>
       </c>
       <c r="I58" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -3147,10 +3156,10 @@
         <v>22</v>
       </c>
       <c r="F59" s="38" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G59" s="38" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H59" t="str">
         <f t="shared" si="0"/>
@@ -3173,7 +3182,7 @@
         <v>22</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="G60" s="37"/>
       <c r="H60" t="str">
@@ -3197,7 +3206,7 @@
         <v>18</v>
       </c>
       <c r="F61" s="38" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="G61" s="38"/>
       <c r="H61" t="str">
@@ -3221,7 +3230,7 @@
         <v>22</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="G62" s="37"/>
       <c r="H62" t="str">
@@ -3272,14 +3281,17 @@
         <v>32</v>
       </c>
       <c r="G64" s="37" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="H64" t="str">
         <f t="shared" si="0"/>
         <v>1 h 20 min</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I64" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="61">
         <f>IF(ISBLANK(B65),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B65))</f>
         <v>44</v>
@@ -3297,33 +3309,44 @@
         <v>22</v>
       </c>
       <c r="F65" s="38" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="G65" s="38" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="H65" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="60" t="str">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="60">
         <f>IF(ISBLANK(B66),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B66))</f>
-        <v/>
-      </c>
-      <c r="B66" s="28"/>
+        <v>44</v>
+      </c>
+      <c r="B66" s="28">
+        <v>46324</v>
+      </c>
       <c r="C66" s="29"/>
-      <c r="D66" s="30"/>
-      <c r="E66" s="31"/>
-      <c r="F66" s="37"/>
+      <c r="D66" s="30">
+        <v>30</v>
+      </c>
+      <c r="E66" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="F66" s="37" t="s">
+        <v>117</v>
+      </c>
       <c r="G66" s="37"/>
       <c r="H66" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0 h 30 min</v>
+      </c>
+      <c r="I66" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="61" t="str">
         <f>IF(ISBLANK(B67),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B67))</f>
         <v/>
@@ -3339,7 +3362,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="60" t="str">
         <f>IF(ISBLANK(B68),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B68))</f>
         <v/>
@@ -3355,7 +3378,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="61" t="str">
         <f>IF(ISBLANK(B69),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B69))</f>
         <v/>
@@ -3371,7 +3394,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="60" t="str">
         <f>IF(ISBLANK(B70),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B70))</f>
         <v/>
@@ -3387,7 +3410,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="61" t="str">
         <f>IF(ISBLANK(B71),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B71))</f>
         <v/>
@@ -3403,7 +3426,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="60" t="str">
         <f>IF(ISBLANK(B72),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B72))</f>
         <v/>
@@ -3419,7 +3442,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="61" t="str">
         <f>IF(ISBLANK(B73),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B73))</f>
         <v/>
@@ -3435,7 +3458,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="60" t="str">
         <f>IF(ISBLANK(B74),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B74))</f>
         <v/>
@@ -3451,7 +3474,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="61" t="str">
         <f>IF(ISBLANK(B75),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B75))</f>
         <v/>
@@ -3467,7 +3490,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="60" t="str">
         <f>IF(ISBLANK(B76),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B76))</f>
         <v/>
@@ -3483,7 +3506,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="61" t="str">
         <f>IF(ISBLANK(B77),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B77))</f>
         <v/>
@@ -3499,7 +3522,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="60" t="str">
         <f>IF(ISBLANK(B78),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B78))</f>
         <v/>
@@ -3515,7 +3538,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="61" t="str">
         <f>IF(ISBLANK(B79),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B79))</f>
         <v/>
@@ -3531,7 +3554,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="60" t="str">
         <f>IF(ISBLANK(B80),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B80))</f>
         <v/>
@@ -10827,9 +10850,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
-  <pageSetup paperSize="9" scale="45" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="35" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="50" max="16383" man="1"/>
+    <brk id="66" max="16383" man="1"/>
   </rowBreaks>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
@@ -10854,13 +10877,13 @@
   <sheetData>
     <row r="2" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="E2" s="64" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="F2" s="66">
         <v>90</v>
       </c>
       <c r="G2" s="64" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="L2" s="17"/>
       <c r="M2" s="42"/>
@@ -10873,42 +10896,42 @@
     </row>
     <row r="4" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="E4" s="64" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="L4" s="64" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="M4" s="39"/>
       <c r="N4" s="18"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="D5" s="40"/>
       <c r="E5" s="43" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="G5" s="45" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="L5" s="46" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="M5" s="47" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="N5" s="48" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -10934,7 +10957,7 @@
       </c>
       <c r="G6" s="70">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.18471337579617833</v>
+        <v>0.18124999999999999</v>
       </c>
       <c r="L6" s="49" t="str">
         <f>'Journal de travail'!M8</f>
@@ -10955,11 +10978,11 @@
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>760</v>
+        <v>790</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>1180</v>
+        <v>1210</v>
       </c>
       <c r="E7" s="71" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10967,11 +10990,11 @@
       </c>
       <c r="F7" s="72" t="str">
         <f t="shared" si="1"/>
-        <v>19 h 40 min</v>
+        <v>20 h 10 min</v>
       </c>
       <c r="G7" s="73">
         <f>SUM(A7:B7)/$C$11</f>
-        <v>0.75159235668789814</v>
+        <v>0.75624999999999998</v>
       </c>
       <c r="L7" s="51" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11045,7 +11068,7 @@
       </c>
       <c r="G9" s="73">
         <f>SUM(A9:B9)/$C$11</f>
-        <v>6.3694267515923567E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="L9" s="53" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11101,25 +11124,25 @@
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>1090</v>
+        <v>1120</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
-        <v>1570</v>
+        <v>1600</v>
       </c>
       <c r="E11" s="79" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F11" s="69" t="str">
         <f t="shared" si="1"/>
-        <v>26 h 10 min</v>
+        <v>26 h 40 min</v>
       </c>
       <c r="G11" s="80">
         <f>C11/C12</f>
-        <v>0.29074074074074074</v>
+        <v>0.29629629629629628</v>
       </c>
       <c r="L11" s="54" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="M11" s="55"/>
       <c r="N11" s="58">
@@ -11157,6 +11180,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B1120F001D1794FAA6F4057E3355991" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="62349bcdb43c26c508700efba1cb50b1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f20a0681-8b2f-4a46-9dab-cf1520193f81" xmlns:ns3="932fafb7-d8e0-4a14-bee3-33aad5c71309" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0e5d6db3f342a25e0e30f4a2965162e1" ns2:_="" ns3:_="">
     <xsd:import namespace="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
@@ -11345,27 +11388,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f20a0681-8b2f-4a46-9dab-cf1520193f81">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="932fafb7-d8e0-4a14-bee3-33aad5c71309" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1424D28F-D6A9-45ED-AED5-A0D744400EE5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11382,29 +11430,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="f20a0681-8b2f-4a46-9dab-cf1520193f81"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="932fafb7-d8e0-4a14-bee3-33aad5c71309"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>